--- a/database/event/5202/event_5202_evp_summary.xlsx
+++ b/database/event/5202/event_5202_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.0229</v>
+        <v>8.985300000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>2.4841</v>
+        <v>2.4737</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2237</v>
+        <v>3.1358</v>
       </c>
       <c r="E2" t="n">
-        <v>9.0229</v>
+        <v>8.985300000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5286</v>
+        <v>2.4911</v>
       </c>
       <c r="G2" t="n">
         <v>6.4943</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5286</v>
+        <v>2.4911</v>
       </c>
       <c r="I2" t="n">
         <v>2.576</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.7518</v>
+        <v>6.75</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8588</v>
+        <v>1.8583</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3062</v>
+        <v>2.2453</v>
       </c>
       <c r="E3" t="n">
-        <v>6.7518</v>
+        <v>6.75</v>
       </c>
       <c r="F3" t="n">
-        <v>0.241</v>
+        <v>0.2392</v>
       </c>
       <c r="G3" t="n">
         <v>6.5109</v>
       </c>
       <c r="H3" t="n">
-        <v>0.241</v>
+        <v>0.2392</v>
       </c>
       <c r="I3" t="n">
         <v>0.2432</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.6092</v>
+        <v>5.6082</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5443</v>
+        <v>1.544</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8446</v>
+        <v>1.7904</v>
       </c>
       <c r="E4" t="n">
-        <v>5.6092</v>
+        <v>5.6082</v>
       </c>
       <c r="F4" t="n">
-        <v>0.271</v>
+        <v>0.27</v>
       </c>
       <c r="G4" t="n">
         <v>5.3382</v>
       </c>
       <c r="H4" t="n">
-        <v>0.271</v>
+        <v>0.27</v>
       </c>
       <c r="I4" t="n">
         <v>0.2723</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.7608</v>
+        <v>4.7572</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3107</v>
+        <v>1.3097</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5019</v>
+        <v>1.4514</v>
       </c>
       <c r="E5" t="n">
-        <v>4.7608</v>
+        <v>4.7572</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9459</v>
+        <v>0.9424</v>
       </c>
       <c r="G5" t="n">
         <v>3.8149</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9459</v>
+        <v>0.9424</v>
       </c>
       <c r="I5" t="n">
         <v>0.9503</v>
@@ -686,7 +686,7 @@
         <v>1.2472</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4088</v>
+        <v>1.361</v>
       </c>
       <c r="E6" t="n">
         <v>4.5303</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.0798</v>
+        <v>3.0706</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8479</v>
+        <v>0.8454</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8228</v>
+        <v>0.7794</v>
       </c>
       <c r="E7" t="n">
-        <v>3.0798</v>
+        <v>3.0706</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2345</v>
+        <v>1.2253</v>
       </c>
       <c r="G7" t="n">
         <v>1.8453</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2345</v>
+        <v>1.2253</v>
       </c>
       <c r="I7" t="n">
         <v>1.246</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.8471</v>
+        <v>2.8033</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.7718</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7288</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8471</v>
+        <v>2.8033</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9493</v>
+        <v>2.9055</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1022</v>
       </c>
       <c r="H8" t="n">
-        <v>2.9493</v>
+        <v>2.9055</v>
       </c>
       <c r="I8" t="n">
         <v>3.0046</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5148</v>
+        <v>2.5183</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6923</v>
+        <v>0.6933</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5946</v>
+        <v>0.5594</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5148</v>
+        <v>2.5183</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4646</v>
+        <v>-0.4611</v>
       </c>
       <c r="G9" t="n">
         <v>2.9794</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4646</v>
+        <v>-0.4611</v>
       </c>
       <c r="I9" t="n">
         <v>-0.4689</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.2218</v>
+        <v>2.2113</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6117</v>
+        <v>0.6088</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4762</v>
+        <v>0.4371</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2218</v>
+        <v>2.2113</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4205</v>
+        <v>1.41</v>
       </c>
       <c r="G10" t="n">
         <v>0.8013</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4205</v>
+        <v>1.41</v>
       </c>
       <c r="I10" t="n">
         <v>1.4338</v>
@@ -916,7 +916,7 @@
         <v>0.576</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4238</v>
+        <v>0.3896</v>
       </c>
       <c r="E11" t="n">
         <v>2.0922</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.0043</v>
+        <v>1.9988</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5518</v>
+        <v>0.5503</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3883</v>
+        <v>0.3524</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0043</v>
+        <v>1.9988</v>
       </c>
       <c r="F12" t="n">
-        <v>0.373</v>
+        <v>0.3675</v>
       </c>
       <c r="G12" t="n">
         <v>1.6313</v>
       </c>
       <c r="H12" t="n">
-        <v>0.373</v>
+        <v>0.3675</v>
       </c>
       <c r="I12" t="n">
         <v>0.38</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9224</v>
+        <v>1.9095</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5293</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3552</v>
+        <v>0.3168</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9224</v>
+        <v>1.9095</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7269</v>
+        <v>1.714</v>
       </c>
       <c r="G13" t="n">
         <v>0.1955</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7269</v>
+        <v>1.714</v>
       </c>
       <c r="I13" t="n">
         <v>1.743</v>
@@ -1054,7 +1054,7 @@
         <v>0.511</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3285</v>
+        <v>0.2956</v>
       </c>
       <c r="E14" t="n">
         <v>1.8561</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8201</v>
+        <v>1.811</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5011</v>
+        <v>0.4986</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3139</v>
+        <v>0.2776</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8201</v>
+        <v>1.811</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2201</v>
+        <v>1.211</v>
       </c>
       <c r="G15" t="n">
         <v>0.6</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2201</v>
+        <v>1.211</v>
       </c>
       <c r="I15" t="n">
         <v>1.2315</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.7247</v>
+        <v>1.7163</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4748</v>
+        <v>0.4725</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2754</v>
+        <v>0.2399</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7247</v>
+        <v>1.7163</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1179</v>
+        <v>1.1095</v>
       </c>
       <c r="G16" t="n">
         <v>0.6068</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1179</v>
+        <v>1.1095</v>
       </c>
       <c r="I16" t="n">
         <v>1.1283</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.0813</v>
+        <v>1.0767</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2977</v>
+        <v>0.2964</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0155</v>
+        <v>-0.015</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0813</v>
+        <v>1.0767</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6183</v>
+        <v>0.6137</v>
       </c>
       <c r="G17" t="n">
         <v>0.463</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6183</v>
+        <v>0.6137</v>
       </c>
       <c r="I17" t="n">
         <v>0.6241</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9297</v>
+        <v>0.9182</v>
       </c>
       <c r="C18" t="n">
-        <v>0.256</v>
+        <v>0.2528</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0458</v>
+        <v>-0.0781</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9297</v>
+        <v>0.9182</v>
       </c>
       <c r="F18" t="n">
-        <v>1.547</v>
+        <v>1.5355</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6173</v>
       </c>
       <c r="H18" t="n">
-        <v>1.547</v>
+        <v>1.5355</v>
       </c>
       <c r="I18" t="n">
         <v>1.5615</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8731</v>
+        <v>0.8629</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2404</v>
+        <v>0.2376</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.1001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8731</v>
+        <v>0.8629</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3662</v>
+        <v>1.356</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4931</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3662</v>
+        <v>1.356</v>
       </c>
       <c r="I19" t="n">
         <v>1.3789</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8292</v>
+        <v>0.8181</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2283</v>
+        <v>0.2252</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0864</v>
+        <v>-0.118</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8292</v>
+        <v>0.8181</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4943</v>
+        <v>1.4832</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6651</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4943</v>
+        <v>1.4832</v>
       </c>
       <c r="I20" t="n">
         <v>1.5083</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6093</v>
+        <v>0.5976</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1677</v>
+        <v>0.1645</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1752</v>
+        <v>-0.2058</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6093</v>
+        <v>0.5976</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5706</v>
+        <v>1.5589</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9613</v>
       </c>
       <c r="H21" t="n">
-        <v>1.5706</v>
+        <v>1.5589</v>
       </c>
       <c r="I21" t="n">
         <v>1.5853</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3227</v>
+        <v>0.3341</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0888</v>
+        <v>0.092</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.291</v>
+        <v>-0.3108</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3227</v>
+        <v>0.3341</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7694</v>
+        <v>-0.758</v>
       </c>
       <c r="G22" t="n">
         <v>1.092</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7694</v>
+        <v>-0.758</v>
       </c>
       <c r="I22" t="n">
         <v>-0.7838000000000001</v>
@@ -1468,7 +1468,7 @@
         <v>0.0645</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3267</v>
+        <v>-0.3505</v>
       </c>
       <c r="E23" t="n">
         <v>0.2344</v>
@@ -1514,7 +1514,7 @@
         <v>0.0415</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3604</v>
+        <v>-0.3838</v>
       </c>
       <c r="E24" t="n">
         <v>0.1508</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0413</v>
+        <v>0.0284</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0114</v>
+        <v>0.0078</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4047</v>
+        <v>-0.4326</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0413</v>
+        <v>0.0284</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7402</v>
+        <v>1.7273</v>
       </c>
       <c r="G25" t="n">
         <v>-1.6989</v>
       </c>
       <c r="H25" t="n">
-        <v>1.7402</v>
+        <v>1.7273</v>
       </c>
       <c r="I25" t="n">
         <v>1.7565</v>
@@ -1606,7 +1606,7 @@
         <v>-0.012</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.439</v>
+        <v>-0.4613</v>
       </c>
       <c r="E26" t="n">
         <v>-0.0437</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3614</v>
+        <v>-0.3587</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.0988</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5674</v>
+        <v>-0.5868</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3614</v>
+        <v>-0.3587</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.7268</v>
+        <v>-0.7241</v>
       </c>
       <c r="G27" t="n">
         <v>0.3654</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.7268</v>
+        <v>-0.7241</v>
       </c>
       <c r="I27" t="n">
         <v>-0.7302</v>
@@ -1698,7 +1698,7 @@
         <v>-0.1123</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5861</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="E28" t="n">
         <v>-0.4079</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.4446</v>
+        <v>-0.4433</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1224</v>
+        <v>-0.122</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.601</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4446</v>
+        <v>-0.4433</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.3482</v>
+        <v>-0.3469</v>
       </c>
       <c r="G29" t="n">
         <v>-0.0964</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.3482</v>
+        <v>-0.3469</v>
       </c>
       <c r="I29" t="n">
         <v>-0.3498</v>
@@ -1790,7 +1790,7 @@
         <v>-0.1303</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6126</v>
+        <v>-0.6325</v>
       </c>
       <c r="E30" t="n">
         <v>-0.4734</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5665</v>
+        <v>-0.5651</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.156</v>
+        <v>-0.1556</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6502</v>
+        <v>-0.669</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5665</v>
+        <v>-0.5651</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3813</v>
+        <v>-0.3799</v>
       </c>
       <c r="G31" t="n">
         <v>-0.1852</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3813</v>
+        <v>-0.3799</v>
       </c>
       <c r="I31" t="n">
         <v>-0.3831</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6967</v>
+        <v>-0.6978</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1918</v>
+        <v>-0.1921</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7028</v>
+        <v>-0.7219</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6967</v>
+        <v>-0.6978</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3033</v>
+        <v>0.3022</v>
       </c>
       <c r="G32" t="n">
         <v>-1</v>
       </c>
       <c r="H32" t="n">
-        <v>0.3033</v>
+        <v>0.3022</v>
       </c>
       <c r="I32" t="n">
         <v>0.3047</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-0.7857</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2169</v>
+        <v>-0.2163</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7396</v>
+        <v>-0.7569</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-0.7857</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5596</v>
+        <v>-0.5575</v>
       </c>
       <c r="G33" t="n">
         <v>-0.2282</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5596</v>
+        <v>-0.5575</v>
       </c>
       <c r="I33" t="n">
         <v>-0.5622</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9456</v>
+        <v>-0.9466</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2603</v>
+        <v>-0.2606</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8034</v>
+        <v>-0.821</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9456</v>
+        <v>-0.9466</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2569</v>
+        <v>0.2559</v>
       </c>
       <c r="G34" t="n">
         <v>-1.2025</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2569</v>
+        <v>0.2559</v>
       </c>
       <c r="I34" t="n">
         <v>0.2581</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1727</v>
+        <v>-1.1716</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3229</v>
+        <v>-0.3225</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8951</v>
+        <v>-0.9107</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1727</v>
+        <v>-1.1716</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.2976</v>
+        <v>-0.2965</v>
       </c>
       <c r="G35" t="n">
         <v>-0.8751</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.2976</v>
+        <v>-0.2965</v>
       </c>
       <c r="I35" t="n">
         <v>-0.299</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.3109</v>
+        <v>-1.3142</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3609</v>
+        <v>-0.3618</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9509</v>
+        <v>-0.9675</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.3109</v>
+        <v>-1.3142</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4389</v>
+        <v>0.4356</v>
       </c>
       <c r="G36" t="n">
         <v>-1.7498</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4389</v>
+        <v>0.4356</v>
       </c>
       <c r="I36" t="n">
         <v>0.443</v>
@@ -2112,7 +2112,7 @@
         <v>-0.4036</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0136</v>
+        <v>-1.0279</v>
       </c>
       <c r="E37" t="n">
         <v>-1.4659</v>
@@ -2158,7 +2158,7 @@
         <v>-0.4801</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1258</v>
+        <v>-1.1386</v>
       </c>
       <c r="E38" t="n">
         <v>-1.7437</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.2829</v>
+        <v>-2.2751</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.6264</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3436</v>
+        <v>-1.3503</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.2829</v>
+        <v>-2.2751</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0568</v>
+        <v>-1.049</v>
       </c>
       <c r="G39" t="n">
         <v>-1.2261</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0568</v>
+        <v>-1.049</v>
       </c>
       <c r="I39" t="n">
         <v>-1.0667</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.3644</v>
+        <v>-2.3607</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6509</v>
+        <v>-0.6499</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3765</v>
+        <v>-1.3844</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.3644</v>
+        <v>-2.3607</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.9954</v>
+        <v>-0.9917</v>
       </c>
       <c r="G40" t="n">
         <v>-1.369</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.9954</v>
+        <v>-0.9917</v>
       </c>
       <c r="I40" t="n">
         <v>-1</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.3062</v>
+        <v>-3.2785</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.9102</v>
+        <v>-0.9026</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.757</v>
+        <v>-1.7501</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.3062</v>
+        <v>-3.2785</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.8711</v>
+        <v>-1.8434</v>
       </c>
       <c r="G41" t="n">
         <v>-1.4351</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.8711</v>
+        <v>-1.8434</v>
       </c>
       <c r="I41" t="n">
         <v>-1.9062</v>

--- a/database/event/5202/event_5202_evp_summary.xlsx
+++ b/database/event/5202/event_5202_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.985300000000001</v>
+        <v>8.4421</v>
       </c>
       <c r="C2" t="n">
-        <v>2.4737</v>
+        <v>2.3242</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1358</v>
+        <v>3.1732</v>
       </c>
       <c r="E2" t="n">
-        <v>8.985300000000001</v>
+        <v>8.4421</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4911</v>
+        <v>2.4573</v>
       </c>
       <c r="G2" t="n">
-        <v>6.4943</v>
+        <v>5.9848</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4911</v>
+        <v>2.4573</v>
       </c>
       <c r="I2" t="n">
-        <v>2.576</v>
+        <v>2.8872</v>
       </c>
       <c r="J2" t="n">
-        <v>6.5912</v>
+        <v>5.9848</v>
       </c>
       <c r="K2" t="n">
         <v>139</v>
@@ -529,7 +529,7 @@
         <v>250</v>
       </c>
       <c r="M2" t="n">
-        <v>9.167199999999999</v>
+        <v>8.872</v>
       </c>
       <c r="N2" t="n">
         <v>389</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.75</v>
+        <v>6.0031</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8583</v>
+        <v>1.6527</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2453</v>
+        <v>2.0721</v>
       </c>
       <c r="E3" t="n">
-        <v>6.75</v>
+        <v>6.0031</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2392</v>
+        <v>0.2797</v>
       </c>
       <c r="G3" t="n">
-        <v>6.5109</v>
+        <v>5.7234</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2392</v>
+        <v>0.2797</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2432</v>
+        <v>0.3032</v>
       </c>
       <c r="J3" t="n">
-        <v>6.7574</v>
+        <v>5.7234</v>
       </c>
       <c r="K3" t="n">
         <v>57</v>
@@ -575,7 +575,7 @@
         <v>222</v>
       </c>
       <c r="M3" t="n">
-        <v>7.000599999999999</v>
+        <v>6.0266</v>
       </c>
       <c r="N3" t="n">
         <v>279</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.6082</v>
+        <v>4.2846</v>
       </c>
       <c r="C4" t="n">
-        <v>1.544</v>
+        <v>1.1796</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7904</v>
+        <v>1.2963</v>
       </c>
       <c r="E4" t="n">
-        <v>5.6082</v>
+        <v>4.2846</v>
       </c>
       <c r="F4" t="n">
-        <v>0.27</v>
+        <v>0.3566</v>
       </c>
       <c r="G4" t="n">
-        <v>5.3382</v>
+        <v>3.9279</v>
       </c>
       <c r="H4" t="n">
-        <v>0.27</v>
+        <v>0.3566</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2723</v>
+        <v>0.3713</v>
       </c>
       <c r="J4" t="n">
-        <v>5.3382</v>
+        <v>3.9279</v>
       </c>
       <c r="K4" t="n">
         <v>75</v>
@@ -621,7 +621,7 @@
         <v>193</v>
       </c>
       <c r="M4" t="n">
-        <v>5.6105</v>
+        <v>4.2992</v>
       </c>
       <c r="N4" t="n">
         <v>268</v>
@@ -630,185 +630,185 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.7572</v>
+        <v>4.0399</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3097</v>
+        <v>1.1122</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4514</v>
+        <v>1.1858</v>
       </c>
       <c r="E5" t="n">
-        <v>4.7572</v>
+        <v>4.0399</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9424</v>
+        <v>1.3035</v>
       </c>
       <c r="G5" t="n">
-        <v>3.8149</v>
+        <v>2.7364</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9424</v>
+        <v>1.3035</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9503</v>
+        <v>1.3035</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8149</v>
+        <v>2.7364</v>
       </c>
       <c r="K5" t="n">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="L5" t="n">
-        <v>193</v>
+        <v>138</v>
       </c>
       <c r="M5" t="n">
-        <v>4.7652</v>
+        <v>4.0399</v>
       </c>
       <c r="N5" t="n">
-        <v>268</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5303</v>
+        <v>3.7529</v>
       </c>
       <c r="C6" t="n">
-        <v>1.2472</v>
+        <v>1.0332</v>
       </c>
       <c r="D6" t="n">
-        <v>1.361</v>
+        <v>1.0562</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5303</v>
+        <v>3.7529</v>
       </c>
       <c r="F6" t="n">
-        <v>0.992</v>
+        <v>0.9787</v>
       </c>
       <c r="G6" t="n">
-        <v>3.5383</v>
+        <v>2.7743</v>
       </c>
       <c r="H6" t="n">
-        <v>0.992</v>
+        <v>0.9787</v>
       </c>
       <c r="I6" t="n">
-        <v>0.992</v>
+        <v>1.0189</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5383</v>
+        <v>2.7743</v>
       </c>
       <c r="K6" t="n">
-        <v>121</v>
+        <v>75</v>
       </c>
       <c r="L6" t="n">
-        <v>138</v>
+        <v>193</v>
       </c>
       <c r="M6" t="n">
-        <v>4.5303</v>
+        <v>3.7932</v>
       </c>
       <c r="N6" t="n">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.0706</v>
+        <v>3.1438</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8454</v>
+        <v>0.8655</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7794</v>
+        <v>0.7813</v>
       </c>
       <c r="E7" t="n">
-        <v>3.0706</v>
+        <v>3.1438</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2253</v>
+        <v>2.9708</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8453</v>
+        <v>0.173</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2253</v>
+        <v>3.1637</v>
       </c>
       <c r="I7" t="n">
-        <v>1.246</v>
+        <v>3.7171</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8453</v>
+        <v>0.173</v>
       </c>
       <c r="K7" t="n">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="L7" t="n">
-        <v>222</v>
+        <v>250</v>
       </c>
       <c r="M7" t="n">
-        <v>3.0913</v>
+        <v>3.8901</v>
       </c>
       <c r="N7" t="n">
-        <v>279</v>
+        <v>389</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.8033</v>
+        <v>2.9303</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7718</v>
+        <v>0.8067</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.6849</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8033</v>
+        <v>2.9303</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9055</v>
+        <v>1.1479</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1022</v>
+        <v>1.7824</v>
       </c>
       <c r="H8" t="n">
-        <v>2.9055</v>
+        <v>1.1479</v>
       </c>
       <c r="I8" t="n">
-        <v>3.0046</v>
+        <v>1.2443</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1022</v>
+        <v>1.7824</v>
       </c>
       <c r="K8" t="n">
-        <v>139</v>
+        <v>57</v>
       </c>
       <c r="L8" t="n">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9024</v>
+        <v>3.0267</v>
       </c>
       <c r="N8" t="n">
-        <v>389</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5183</v>
+        <v>2.474</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6933</v>
+        <v>0.6811</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5594</v>
+        <v>0.4789</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5183</v>
+        <v>2.474</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4611</v>
+        <v>-0.3125</v>
       </c>
       <c r="G9" t="n">
-        <v>2.9794</v>
+        <v>2.7865</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4611</v>
+        <v>-0.3125</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4689</v>
+        <v>-0.3387</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9794</v>
+        <v>2.7865</v>
       </c>
       <c r="K9" t="n">
         <v>57</v>
@@ -851,7 +851,7 @@
         <v>222</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5105</v>
+        <v>2.4478</v>
       </c>
       <c r="N9" t="n">
         <v>279</v>
@@ -860,403 +860,403 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>oBo</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.2113</v>
+        <v>2.3139</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6088</v>
+        <v>0.637</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4371</v>
+        <v>0.4066</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2113</v>
+        <v>2.3139</v>
       </c>
       <c r="F10" t="n">
-        <v>1.41</v>
+        <v>2.0176</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8013</v>
+        <v>0.2963</v>
       </c>
       <c r="H10" t="n">
-        <v>1.41</v>
+        <v>2.0176</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4338</v>
+        <v>2.187</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8013</v>
+        <v>0.2963</v>
       </c>
       <c r="K10" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="L10" t="n">
-        <v>222</v>
+        <v>138</v>
       </c>
       <c r="M10" t="n">
-        <v>2.2351</v>
+        <v>2.4833</v>
       </c>
       <c r="N10" t="n">
-        <v>279</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>oBo</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.0922</v>
+        <v>2.1501</v>
       </c>
       <c r="C11" t="n">
-        <v>0.576</v>
+        <v>0.5919</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3896</v>
+        <v>0.3326</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0922</v>
+        <v>2.1501</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9964</v>
+        <v>1.2979</v>
       </c>
       <c r="G11" t="n">
-        <v>3.0886</v>
+        <v>0.8522</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9964</v>
+        <v>1.2979</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9964</v>
+        <v>1.4068</v>
       </c>
       <c r="J11" t="n">
-        <v>3.0886</v>
+        <v>0.8522</v>
       </c>
       <c r="K11" t="n">
-        <v>121</v>
+        <v>57</v>
       </c>
       <c r="L11" t="n">
-        <v>138</v>
+        <v>222</v>
       </c>
       <c r="M11" t="n">
-        <v>2.0922</v>
+        <v>2.259</v>
       </c>
       <c r="N11" t="n">
-        <v>259</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.9988</v>
+        <v>2.024</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5503</v>
+        <v>0.5572</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3524</v>
+        <v>0.2757</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9988</v>
+        <v>2.024</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3675</v>
+        <v>1.323</v>
       </c>
       <c r="G12" t="n">
-        <v>1.6313</v>
+        <v>0.701</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3675</v>
+        <v>1.323</v>
       </c>
       <c r="I12" t="n">
-        <v>0.38</v>
+        <v>1.4341</v>
       </c>
       <c r="J12" t="n">
-        <v>1.6313</v>
+        <v>0.701</v>
       </c>
       <c r="K12" t="n">
-        <v>139</v>
+        <v>68</v>
       </c>
       <c r="L12" t="n">
-        <v>250</v>
+        <v>138</v>
       </c>
       <c r="M12" t="n">
-        <v>2.0113</v>
+        <v>2.1351</v>
       </c>
       <c r="N12" t="n">
-        <v>389</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9095</v>
+        <v>1.9954</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5256999999999999</v>
+        <v>0.5493</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3168</v>
+        <v>0.2628</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9095</v>
+        <v>1.9954</v>
       </c>
       <c r="F13" t="n">
-        <v>1.714</v>
+        <v>0.6096</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1955</v>
+        <v>1.3858</v>
       </c>
       <c r="H13" t="n">
-        <v>1.714</v>
+        <v>0.6096</v>
       </c>
       <c r="I13" t="n">
-        <v>1.743</v>
+        <v>0.6096</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1955</v>
+        <v>1.3858</v>
       </c>
       <c r="K13" t="n">
-        <v>68</v>
+        <v>121</v>
       </c>
       <c r="L13" t="n">
         <v>138</v>
       </c>
       <c r="M13" t="n">
-        <v>1.9385</v>
+        <v>1.9954</v>
       </c>
       <c r="N13" t="n">
-        <v>206</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.8561</v>
+        <v>1.9339</v>
       </c>
       <c r="C14" t="n">
-        <v>0.511</v>
+        <v>0.5324</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2956</v>
+        <v>0.235</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8561</v>
+        <v>1.9339</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4659</v>
+        <v>0.4393</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3902</v>
+        <v>1.4946</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4659</v>
+        <v>0.4393</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4659</v>
+        <v>0.5162</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3902</v>
+        <v>1.4946</v>
       </c>
       <c r="K14" t="n">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="L14" t="n">
-        <v>138</v>
+        <v>250</v>
       </c>
       <c r="M14" t="n">
-        <v>1.8561</v>
+        <v>2.0108</v>
       </c>
       <c r="N14" t="n">
-        <v>259</v>
+        <v>389</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.811</v>
+        <v>1.8985</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4986</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2776</v>
+        <v>0.2191</v>
       </c>
       <c r="E15" t="n">
-        <v>1.811</v>
+        <v>1.8985</v>
       </c>
       <c r="F15" t="n">
-        <v>1.211</v>
+        <v>1.0319</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6</v>
+        <v>0.8666</v>
       </c>
       <c r="H15" t="n">
-        <v>1.211</v>
+        <v>1.0319</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2315</v>
+        <v>1.1185</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6</v>
+        <v>0.8666</v>
       </c>
       <c r="K15" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="L15" t="n">
-        <v>138</v>
+        <v>222</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8315</v>
+        <v>1.9851</v>
       </c>
       <c r="N15" t="n">
-        <v>206</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.7163</v>
+        <v>1.83</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4725</v>
+        <v>0.5038</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2399</v>
+        <v>0.1881</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7163</v>
+        <v>1.83</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1095</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6068</v>
+        <v>2.4162</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1095</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1283</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6068</v>
+        <v>2.4162</v>
       </c>
       <c r="K16" t="n">
-        <v>57</v>
+        <v>121</v>
       </c>
       <c r="L16" t="n">
-        <v>222</v>
+        <v>138</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7351</v>
+        <v>1.83</v>
       </c>
       <c r="N16" t="n">
-        <v>279</v>
+        <v>259</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Plopski</t>
+          <t>JACKZ</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.0767</v>
+        <v>1.2873</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2964</v>
+        <v>0.3544</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.015</v>
+        <v>-0.0569</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0767</v>
+        <v>1.2873</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6137</v>
+        <v>1.4009</v>
       </c>
       <c r="G17" t="n">
-        <v>0.463</v>
+        <v>-0.1136</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6137</v>
+        <v>1.4009</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6241</v>
+        <v>1.5185</v>
       </c>
       <c r="J17" t="n">
-        <v>0.463</v>
+        <v>-0.1136</v>
       </c>
       <c r="K17" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="L17" t="n">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0871</v>
+        <v>1.4049</v>
       </c>
       <c r="N17" t="n">
-        <v>152</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>Plopski</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9182</v>
+        <v>1.2762</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2528</v>
+        <v>0.3513</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0781</v>
+        <v>-0.0619</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9182</v>
+        <v>1.2762</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5355</v>
+        <v>0.7141</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6173</v>
+        <v>0.5621</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5355</v>
+        <v>0.7141</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5615</v>
+        <v>0.774</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6173</v>
+        <v>0.5621</v>
       </c>
       <c r="K18" t="n">
         <v>44</v>
@@ -1265,7 +1265,7 @@
         <v>108</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9442000000000002</v>
+        <v>1.3361</v>
       </c>
       <c r="N18" t="n">
         <v>152</v>
@@ -1274,35 +1274,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JACKZ</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8629</v>
+        <v>1.1633</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2376</v>
+        <v>0.3203</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1001</v>
+        <v>-0.1128</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8629</v>
+        <v>1.1633</v>
       </c>
       <c r="F19" t="n">
-        <v>1.356</v>
+        <v>2.2669</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4931</v>
+        <v>-1.1036</v>
       </c>
       <c r="H19" t="n">
-        <v>1.356</v>
+        <v>2.2669</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3789</v>
+        <v>2.4572</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4931</v>
+        <v>-1.1036</v>
       </c>
       <c r="K19" t="n">
         <v>68</v>
@@ -1311,7 +1311,7 @@
         <v>138</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8858</v>
+        <v>1.3536</v>
       </c>
       <c r="N19" t="n">
         <v>206</v>
@@ -1320,35 +1320,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>nawwk</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8181</v>
+        <v>1.161</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2252</v>
+        <v>0.3196</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.118</v>
+        <v>-0.1139</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8181</v>
+        <v>1.161</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4832</v>
+        <v>1.4375</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6651</v>
+        <v>-0.2765</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4832</v>
+        <v>1.4375</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5083</v>
+        <v>1.5582</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6651</v>
+        <v>-0.2765</v>
       </c>
       <c r="K20" t="n">
         <v>44</v>
@@ -1357,7 +1357,7 @@
         <v>108</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8431999999999999</v>
+        <v>1.2817</v>
       </c>
       <c r="N20" t="n">
         <v>152</v>
@@ -1366,35 +1366,35 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>nawwk</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5976</v>
+        <v>1.0873</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1645</v>
+        <v>0.2993</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2058</v>
+        <v>-0.1472</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5976</v>
+        <v>1.0873</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5589</v>
+        <v>1.4271</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9613</v>
+        <v>-0.3398</v>
       </c>
       <c r="H21" t="n">
-        <v>1.5589</v>
+        <v>1.4271</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5853</v>
+        <v>1.5469</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9613</v>
+        <v>-0.3398</v>
       </c>
       <c r="K21" t="n">
         <v>44</v>
@@ -1403,7 +1403,7 @@
         <v>108</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6239999999999999</v>
+        <v>1.2071</v>
       </c>
       <c r="N21" t="n">
         <v>152</v>
@@ -1412,185 +1412,185 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3341</v>
+        <v>0.9183</v>
       </c>
       <c r="C22" t="n">
-        <v>0.092</v>
+        <v>0.2528</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3108</v>
+        <v>-0.2234</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3341</v>
+        <v>0.9183</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.758</v>
+        <v>1.5065</v>
       </c>
       <c r="G22" t="n">
-        <v>1.092</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.758</v>
+        <v>1.5065</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7838000000000001</v>
+        <v>1.633</v>
       </c>
       <c r="J22" t="n">
-        <v>1.092</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>139</v>
+        <v>44</v>
       </c>
       <c r="L22" t="n">
-        <v>250</v>
+        <v>108</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3082</v>
+        <v>1.0448</v>
       </c>
       <c r="N22" t="n">
-        <v>389</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2344</v>
+        <v>0.615</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0645</v>
+        <v>0.1693</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3505</v>
+        <v>-0.3604</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2344</v>
+        <v>0.615</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0474</v>
+        <v>-0.3957</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2818</v>
+        <v>1.0107</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0474</v>
+        <v>-0.3957</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0474</v>
+        <v>-0.4649</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2818</v>
+        <v>1.0107</v>
       </c>
       <c r="K23" t="n">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="L23" t="n">
-        <v>138</v>
+        <v>250</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2344</v>
+        <v>0.5458</v>
       </c>
       <c r="N23" t="n">
-        <v>259</v>
+        <v>389</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1508</v>
+        <v>0.5571</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0415</v>
+        <v>0.1534</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3838</v>
+        <v>-0.3865</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1508</v>
+        <v>0.5571</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.228</v>
+        <v>0.2867</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3788</v>
+        <v>0.2704</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.228</v>
+        <v>0.2867</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.228</v>
+        <v>0.2867</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3788</v>
+        <v>0.2704</v>
       </c>
       <c r="K24" t="n">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="L24" t="n">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1508</v>
+        <v>0.5570999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>121</v>
+        <v>259</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0284</v>
+        <v>0.3027</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0078</v>
+        <v>0.0833</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4326</v>
+        <v>-0.5014</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0284</v>
+        <v>0.3027</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7273</v>
+        <v>-0.1172</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.6989</v>
+        <v>0.4199</v>
       </c>
       <c r="H25" t="n">
-        <v>1.7273</v>
+        <v>-0.1172</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7565</v>
+        <v>-0.1172</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.6989</v>
+        <v>0.4199</v>
       </c>
       <c r="K25" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="L25" t="n">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="M25" t="n">
-        <v>0.05759999999999987</v>
+        <v>0.3027</v>
       </c>
       <c r="N25" t="n">
-        <v>206</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26">
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.0437</v>
+        <v>0.2128</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.012</v>
+        <v>0.0586</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4613</v>
+        <v>-0.5419</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0437</v>
+        <v>0.2128</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.2232</v>
+        <v>0.0395</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1795</v>
+        <v>0.1733</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2232</v>
+        <v>0.0395</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2232</v>
+        <v>0.0395</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1795</v>
+        <v>0.1733</v>
       </c>
       <c r="K26" t="n">
         <v>44</v>
@@ -1633,7 +1633,7 @@
         <v>77</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.04370000000000002</v>
+        <v>0.2128</v>
       </c>
       <c r="N26" t="n">
         <v>121</v>
@@ -1642,93 +1642,93 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>Bymas</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3587</v>
+        <v>0.1073</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0988</v>
+        <v>0.0295</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5868</v>
+        <v>-0.5896</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3587</v>
+        <v>0.1073</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.7241</v>
+        <v>-0.6442</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3654</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.7241</v>
+        <v>-0.6442</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.7302</v>
+        <v>-0.6442</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3654</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>68</v>
+        <v>121</v>
       </c>
       <c r="L27" t="n">
-        <v>86</v>
+        <v>138</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.3648</v>
+        <v>0.1073</v>
       </c>
       <c r="N27" t="n">
-        <v>154</v>
+        <v>259</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Bymas</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.4079</v>
+        <v>-0.0413</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1123</v>
+        <v>-0.0114</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.6567</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.4079</v>
+        <v>-0.0413</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.0509</v>
+        <v>-0.4115</v>
       </c>
       <c r="G28" t="n">
-        <v>0.643</v>
+        <v>0.3702</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.0509</v>
+        <v>-0.4115</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.0509</v>
+        <v>-0.4284</v>
       </c>
       <c r="J28" t="n">
-        <v>0.643</v>
+        <v>0.3702</v>
       </c>
       <c r="K28" t="n">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="L28" t="n">
-        <v>138</v>
+        <v>86</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.4078999999999999</v>
+        <v>-0.05820000000000003</v>
       </c>
       <c r="N28" t="n">
-        <v>259</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29">
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.4433</v>
+        <v>-0.2043</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.122</v>
+        <v>-0.0562</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6205000000000001</v>
+        <v>-0.7302</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4433</v>
+        <v>-0.2043</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.3469</v>
+        <v>-0.1464</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0964</v>
+        <v>-0.0579</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.3469</v>
+        <v>-0.1464</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3498</v>
+        <v>-0.1524</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.0964</v>
+        <v>-0.0579</v>
       </c>
       <c r="K29" t="n">
         <v>68</v>
@@ -1771,7 +1771,7 @@
         <v>86</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.4462</v>
+        <v>-0.2103</v>
       </c>
       <c r="N29" t="n">
         <v>154</v>
@@ -1780,139 +1780,139 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4734</v>
+        <v>-0.2842</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1303</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6325</v>
+        <v>-0.7663</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4734</v>
+        <v>-0.2842</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1627</v>
+        <v>-0.1673</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.3107</v>
+        <v>-0.1169</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1627</v>
+        <v>-0.1673</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1627</v>
+        <v>-0.1742</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.3107</v>
+        <v>-0.1169</v>
       </c>
       <c r="K30" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="L30" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4734</v>
+        <v>-0.2911</v>
       </c>
       <c r="N30" t="n">
-        <v>121</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5651</v>
+        <v>-0.3031</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1556</v>
+        <v>-0.0834</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.669</v>
+        <v>-0.7748</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5651</v>
+        <v>-0.3031</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3799</v>
+        <v>0.5738</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.1852</v>
+        <v>-0.8769</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3799</v>
+        <v>0.5738</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3831</v>
+        <v>0.5974</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.1852</v>
+        <v>-0.8769</v>
       </c>
       <c r="K31" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="L31" t="n">
-        <v>86</v>
+        <v>193</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.5683</v>
+        <v>-0.2795</v>
       </c>
       <c r="N31" t="n">
-        <v>154</v>
+        <v>268</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Aerial</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6978</v>
+        <v>-0.356</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1921</v>
+        <v>-0.098</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7219</v>
+        <v>-0.7987</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6978</v>
+        <v>-0.356</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3022</v>
+        <v>-0.1527</v>
       </c>
       <c r="G32" t="n">
-        <v>-1</v>
+        <v>-0.2033</v>
       </c>
       <c r="H32" t="n">
-        <v>0.3022</v>
+        <v>-0.1527</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3047</v>
+        <v>-0.1527</v>
       </c>
       <c r="J32" t="n">
-        <v>-1</v>
+        <v>-0.2033</v>
       </c>
       <c r="K32" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="L32" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.6953</v>
+        <v>-0.356</v>
       </c>
       <c r="N32" t="n">
-        <v>154</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33">
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7857</v>
+        <v>-0.4414</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2163</v>
+        <v>-0.1215</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7569</v>
+        <v>-0.8373</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7857</v>
+        <v>-0.4414</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5575</v>
+        <v>-0.301</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.2282</v>
+        <v>-0.1404</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5575</v>
+        <v>-0.301</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5622</v>
+        <v>-0.3134</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.2282</v>
+        <v>-0.1404</v>
       </c>
       <c r="K33" t="n">
         <v>75</v>
@@ -1955,7 +1955,7 @@
         <v>193</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.7904</v>
+        <v>-0.4538</v>
       </c>
       <c r="N33" t="n">
         <v>268</v>
@@ -1964,47 +1964,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>Aerial</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9466</v>
+        <v>-0.5016</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2606</v>
+        <v>-0.1381</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.821</v>
+        <v>-0.8645</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9466</v>
+        <v>-0.5016</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2559</v>
+        <v>0.4164</v>
       </c>
       <c r="G34" t="n">
-        <v>-1.2025</v>
+        <v>-0.918</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2559</v>
+        <v>0.4164</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2581</v>
+        <v>0.4335</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.2025</v>
+        <v>-0.918</v>
       </c>
       <c r="K34" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="L34" t="n">
-        <v>193</v>
+        <v>86</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.9443999999999999</v>
+        <v>-0.4845</v>
       </c>
       <c r="N34" t="n">
-        <v>268</v>
+        <v>154</v>
       </c>
     </row>
     <row r="35">
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1716</v>
+        <v>-0.6399</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3225</v>
+        <v>-0.1762</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9107</v>
+        <v>-0.9268999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1716</v>
+        <v>-0.6399</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.2965</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.8751</v>
+        <v>-0.553</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.2965</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.299</v>
+        <v>-0.0905</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.8751</v>
+        <v>-0.553</v>
       </c>
       <c r="K35" t="n">
         <v>68</v>
@@ -2047,7 +2047,7 @@
         <v>86</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.1741</v>
+        <v>-0.6435000000000001</v>
       </c>
       <c r="N35" t="n">
         <v>154</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.3142</v>
+        <v>-0.6523</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3618</v>
+        <v>-0.1796</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9675</v>
+        <v>-0.9325</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.3142</v>
+        <v>-0.6523</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4356</v>
+        <v>0.4856</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.7498</v>
+        <v>-1.1379</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4356</v>
+        <v>0.4856</v>
       </c>
       <c r="I36" t="n">
-        <v>0.443</v>
+        <v>0.5264</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.7498</v>
+        <v>-1.1379</v>
       </c>
       <c r="K36" t="n">
         <v>44</v>
@@ -2093,7 +2093,7 @@
         <v>108</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.3068</v>
+        <v>-0.6114999999999999</v>
       </c>
       <c r="N36" t="n">
         <v>152</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.4659</v>
+        <v>-1.0167</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4036</v>
+        <v>-0.2799</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0279</v>
+        <v>-1.097</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.4659</v>
+        <v>-1.0167</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.4659</v>
+        <v>-0.3307</v>
       </c>
       <c r="G37" t="n">
-        <v>-1</v>
+        <v>-0.6860000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.4659</v>
+        <v>-0.3307</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.4659</v>
+        <v>-0.3307</v>
       </c>
       <c r="J37" t="n">
-        <v>-1</v>
+        <v>-0.6860000000000001</v>
       </c>
       <c r="K37" t="n">
         <v>44</v>
@@ -2139,7 +2139,7 @@
         <v>77</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.4659</v>
+        <v>-1.0167</v>
       </c>
       <c r="N37" t="n">
         <v>121</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.7437</v>
+        <v>-1.1479</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4801</v>
+        <v>-0.316</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1386</v>
+        <v>-1.1562</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.7437</v>
+        <v>-1.1479</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.9046999999999999</v>
+        <v>-0.6388</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.839</v>
+        <v>-0.5091</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9046999999999999</v>
+        <v>-0.6388</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9046999999999999</v>
+        <v>-0.6388</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.839</v>
+        <v>-0.5091</v>
       </c>
       <c r="K38" t="n">
         <v>44</v>
@@ -2185,7 +2185,7 @@
         <v>77</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.7437</v>
+        <v>-1.1479</v>
       </c>
       <c r="N38" t="n">
         <v>121</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.2751</v>
+        <v>-1.3344</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.6264</v>
+        <v>-0.3674</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3503</v>
+        <v>-1.2404</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.2751</v>
+        <v>-1.3344</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.049</v>
+        <v>-0.6335</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.2261</v>
+        <v>-0.7009</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.049</v>
+        <v>-0.6335</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.0667</v>
+        <v>-0.6867</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.2261</v>
+        <v>-0.7009</v>
       </c>
       <c r="K39" t="n">
         <v>68</v>
@@ -2231,7 +2231,7 @@
         <v>138</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.2928</v>
+        <v>-1.3876</v>
       </c>
       <c r="N39" t="n">
         <v>206</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.3607</v>
+        <v>-1.9054</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6499</v>
+        <v>-0.5246</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3844</v>
+        <v>-1.4982</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.3607</v>
+        <v>-1.9054</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.9917</v>
+        <v>-0.9176</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.369</v>
+        <v>-0.9878</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.9917</v>
+        <v>-0.9176</v>
       </c>
       <c r="I40" t="n">
-        <v>-1</v>
+        <v>-0.9553</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.369</v>
+        <v>-0.9878</v>
       </c>
       <c r="K40" t="n">
         <v>75</v>
@@ -2277,7 +2277,7 @@
         <v>193</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.369</v>
+        <v>-1.9431</v>
       </c>
       <c r="N40" t="n">
         <v>268</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.2785</v>
+        <v>-1.9414</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.9026</v>
+        <v>-0.5345</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7501</v>
+        <v>-1.5145</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.2785</v>
+        <v>-1.9414</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.8434</v>
+        <v>-1.2144</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.4351</v>
+        <v>-0.727</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.8434</v>
+        <v>-1.2144</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.9062</v>
+        <v>-1.4268</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.4351</v>
+        <v>-0.727</v>
       </c>
       <c r="K41" t="n">
         <v>139</v>
@@ -2323,7 +2323,7 @@
         <v>250</v>
       </c>
       <c r="M41" t="n">
-        <v>-3.3413</v>
+        <v>-2.1538</v>
       </c>
       <c r="N41" t="n">
         <v>389</v>
@@ -2429,10 +2429,10 @@
         <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>0.261</v>
+        <v>0.2055</v>
       </c>
       <c r="J2" t="n">
-        <v>4.698</v>
+        <v>3.699</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.82</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1877</v>
+        <v>-0.1691</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.3786</v>
+        <v>-3.0438</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.49</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7143</v>
+        <v>-0.4858</v>
       </c>
       <c r="J4" t="n">
-        <v>-12.8574</v>
+        <v>-8.744400000000001</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.49</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7143</v>
+        <v>-0.4858</v>
       </c>
       <c r="J5" t="n">
-        <v>-12.8574</v>
+        <v>-8.744400000000001</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.47</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7406</v>
+        <v>-0.5046</v>
       </c>
       <c r="J6" t="n">
-        <v>-13.3308</v>
+        <v>-9.082800000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>2.01</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1673</v>
+        <v>1.0522</v>
       </c>
       <c r="J7" t="n">
-        <v>21.0114</v>
+        <v>18.9396</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.51</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6441</v>
+        <v>0.5971</v>
       </c>
       <c r="J8" t="n">
-        <v>11.5938</v>
+        <v>10.7478</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.3</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3627</v>
+        <v>0.3756</v>
       </c>
       <c r="J9" t="n">
-        <v>6.5286</v>
+        <v>6.7608</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.29</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3498</v>
+        <v>0.3641</v>
       </c>
       <c r="J10" t="n">
-        <v>6.2964</v>
+        <v>6.5538</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.12</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1173</v>
+        <v>0.1522</v>
       </c>
       <c r="J11" t="n">
-        <v>2.1114</v>
+        <v>2.7396</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.26</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7235</v>
+        <v>0.7131</v>
       </c>
       <c r="J12" t="n">
-        <v>25.3225</v>
+        <v>24.9585</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.17</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4863</v>
+        <v>0.4946</v>
       </c>
       <c r="J13" t="n">
-        <v>17.0205</v>
+        <v>17.311</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.15</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4158</v>
+        <v>0.4454</v>
       </c>
       <c r="J14" t="n">
-        <v>14.553</v>
+        <v>15.589</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.1</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2617</v>
+        <v>0.313</v>
       </c>
       <c r="J15" t="n">
-        <v>9.1595</v>
+        <v>10.955</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.09</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2313</v>
+        <v>0.2847</v>
       </c>
       <c r="J16" t="n">
-        <v>8.095499999999999</v>
+        <v>9.964499999999999</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.58</v>
       </c>
       <c r="I17" t="n">
-        <v>0.888</v>
+        <v>1.0832</v>
       </c>
       <c r="J17" t="n">
-        <v>31.08</v>
+        <v>37.912</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.89</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2063</v>
+        <v>-0.1352</v>
       </c>
       <c r="J18" t="n">
-        <v>-7.2205</v>
+        <v>-4.732</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.84</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2946</v>
+        <v>-0.1873</v>
       </c>
       <c r="J19" t="n">
-        <v>-10.311</v>
+        <v>-6.5555</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.76</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.417</v>
+        <v>-0.2671</v>
       </c>
       <c r="J20" t="n">
-        <v>-14.595</v>
+        <v>-9.3485</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.46</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7986</v>
+        <v>-0.5461</v>
       </c>
       <c r="J21" t="n">
-        <v>-27.951</v>
+        <v>-19.1135</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.67</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5898</v>
+        <v>1.3829</v>
       </c>
       <c r="J22" t="n">
-        <v>44.5144</v>
+        <v>38.7212</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.25</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7205</v>
+        <v>0.7005</v>
       </c>
       <c r="J23" t="n">
-        <v>20.174</v>
+        <v>19.614</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.01</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0292</v>
+        <v>0.0272</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.8176</v>
+        <v>0.7616000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.85</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5836</v>
+        <v>-0.5221</v>
       </c>
       <c r="J25" t="n">
-        <v>-16.3408</v>
+        <v>-14.6188</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6837</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>-19.1436</v>
+        <v>-17.598</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.26</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4598</v>
+        <v>0.5393</v>
       </c>
       <c r="J27" t="n">
-        <v>12.8744</v>
+        <v>15.1004</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.13</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2693</v>
+        <v>0.3005</v>
       </c>
       <c r="J28" t="n">
-        <v>7.5404</v>
+        <v>8.414</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.11</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2363</v>
+        <v>0.2612</v>
       </c>
       <c r="J29" t="n">
-        <v>6.6164</v>
+        <v>7.3136</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.86</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2993</v>
+        <v>-0.18</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.3804</v>
+        <v>-5.04</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.75</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.458</v>
+        <v>-0.2908</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.824</v>
+        <v>-8.1424</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.24</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4277</v>
+        <v>0.4995</v>
       </c>
       <c r="J32" t="n">
-        <v>14.5418</v>
+        <v>16.983</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.03</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0653</v>
+        <v>0.0872</v>
       </c>
       <c r="J33" t="n">
-        <v>2.2202</v>
+        <v>2.9648</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.99</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0584</v>
+        <v>-0.0236</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.9856</v>
+        <v>-0.8024</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.96</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1284</v>
+        <v>-0.0668</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.3656</v>
+        <v>-2.2712</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.96</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1284</v>
+        <v>-0.0668</v>
       </c>
       <c r="J36" t="n">
-        <v>-4.3656</v>
+        <v>-2.2712</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.36</v>
       </c>
       <c r="I37" t="n">
-        <v>1.0198</v>
+        <v>0.9912</v>
       </c>
       <c r="J37" t="n">
-        <v>34.6732</v>
+        <v>33.7008</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.02</v>
       </c>
       <c r="I38" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0882</v>
       </c>
       <c r="J38" t="n">
-        <v>2.4956</v>
+        <v>2.9988</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.01</v>
       </c>
       <c r="I39" t="n">
-        <v>0.026</v>
+        <v>0.0481</v>
       </c>
       <c r="J39" t="n">
-        <v>0.884</v>
+        <v>1.6354</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.96</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.221</v>
+        <v>-0.1726</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.514</v>
+        <v>-5.8684</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6549</v>
+        <v>-0.6046</v>
       </c>
       <c r="J41" t="n">
-        <v>-22.2666</v>
+        <v>-20.5564</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.27</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4567</v>
+        <v>0.5411</v>
       </c>
       <c r="J42" t="n">
-        <v>13.701</v>
+        <v>16.233</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.26</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4431</v>
+        <v>0.5239</v>
       </c>
       <c r="J43" t="n">
-        <v>13.293</v>
+        <v>15.717</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.05</v>
       </c>
       <c r="I44" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.129</v>
       </c>
       <c r="J44" t="n">
-        <v>2.697</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.95</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1594</v>
+        <v>-0.0833</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.782</v>
+        <v>-2.499</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.83</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3558</v>
+        <v>-0.2167</v>
       </c>
       <c r="J46" t="n">
-        <v>-10.674</v>
+        <v>-6.501</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.26</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7826</v>
+        <v>0.75</v>
       </c>
       <c r="J47" t="n">
-        <v>23.478</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.17</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5584</v>
+        <v>0.5221</v>
       </c>
       <c r="J48" t="n">
-        <v>16.752</v>
+        <v>15.663</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.06</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2244</v>
+        <v>0.2164</v>
       </c>
       <c r="J49" t="n">
-        <v>6.732</v>
+        <v>6.492</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.89</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.451</v>
+        <v>-0.3925</v>
       </c>
       <c r="J50" t="n">
-        <v>-13.53</v>
+        <v>-11.775</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.88</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.479</v>
+        <v>-0.4209</v>
       </c>
       <c r="J51" t="n">
-        <v>-14.37</v>
+        <v>-12.627</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.47</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7045</v>
+        <v>0.6202</v>
       </c>
       <c r="J52" t="n">
-        <v>18.317</v>
+        <v>16.1252</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.06</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1088</v>
+        <v>0.1071</v>
       </c>
       <c r="J53" t="n">
-        <v>2.8288</v>
+        <v>2.7846</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.99</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.0728</v>
+        <v>-0.0275</v>
       </c>
       <c r="J54" t="n">
-        <v>-1.8928</v>
+        <v>-0.715</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1794</v>
+        <v>-0.0961</v>
       </c>
       <c r="J55" t="n">
-        <v>-4.6644</v>
+        <v>-2.4986</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.92</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.215</v>
+        <v>-0.1199</v>
       </c>
       <c r="J56" t="n">
-        <v>-5.59</v>
+        <v>-3.1174</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5676</v>
+        <v>0.5214</v>
       </c>
       <c r="J57" t="n">
-        <v>14.7576</v>
+        <v>13.5564</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.32</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5421</v>
+        <v>0.4952</v>
       </c>
       <c r="J58" t="n">
-        <v>14.0946</v>
+        <v>12.8752</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.17</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3352</v>
+        <v>0.2903</v>
       </c>
       <c r="J59" t="n">
-        <v>8.715199999999999</v>
+        <v>7.5478</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.67</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5609</v>
+        <v>-0.3658</v>
       </c>
       <c r="J60" t="n">
-        <v>-14.5834</v>
+        <v>-9.5108</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6953</v>
+        <v>-0.4667</v>
       </c>
       <c r="J61" t="n">
-        <v>-18.0778</v>
+        <v>-12.1342</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.22</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4523</v>
+        <v>0.5204</v>
       </c>
       <c r="J62" t="n">
-        <v>9.9506</v>
+        <v>11.4488</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.08</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2364</v>
+        <v>0.2386</v>
       </c>
       <c r="J63" t="n">
-        <v>5.2008</v>
+        <v>5.2492</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.79</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.3669</v>
+        <v>-0.2353</v>
       </c>
       <c r="J64" t="n">
-        <v>-8.0718</v>
+        <v>-5.1766</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.77</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.397</v>
+        <v>-0.255</v>
       </c>
       <c r="J65" t="n">
-        <v>-8.734</v>
+        <v>-5.61</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.58</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6522</v>
+        <v>-0.435</v>
       </c>
       <c r="J66" t="n">
-        <v>-14.3484</v>
+        <v>-9.57</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.7</v>
       </c>
       <c r="I67" t="n">
-        <v>1.5742</v>
+        <v>1.3745</v>
       </c>
       <c r="J67" t="n">
-        <v>34.6324</v>
+        <v>30.239</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.37</v>
       </c>
       <c r="I68" t="n">
-        <v>0.9172</v>
+        <v>0.9328</v>
       </c>
       <c r="J68" t="n">
-        <v>20.1784</v>
+        <v>20.5216</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.24</v>
       </c>
       <c r="I69" t="n">
-        <v>0.5809</v>
+        <v>0.6445</v>
       </c>
       <c r="J69" t="n">
-        <v>12.7798</v>
+        <v>14.179</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.1</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2089</v>
+        <v>0.2879</v>
       </c>
       <c r="J70" t="n">
-        <v>4.5958</v>
+        <v>6.3338</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.9</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4934</v>
+        <v>-0.4184</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.8548</v>
+        <v>-9.204800000000001</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.44</v>
       </c>
       <c r="I72" t="n">
-        <v>0.6978</v>
+        <v>0.8602</v>
       </c>
       <c r="J72" t="n">
-        <v>18.8406</v>
+        <v>23.2254</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.09</v>
       </c>
       <c r="I73" t="n">
-        <v>0.2153</v>
+        <v>0.2288</v>
       </c>
       <c r="J73" t="n">
-        <v>5.8131</v>
+        <v>6.1776</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.91</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2065</v>
+        <v>-0.1217</v>
       </c>
       <c r="J74" t="n">
-        <v>-5.5755</v>
+        <v>-3.2859</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.87</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.274</v>
+        <v>-0.1655</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.398</v>
+        <v>-4.4685</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.63</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6072</v>
+        <v>-0.4004</v>
       </c>
       <c r="J76" t="n">
-        <v>-16.3944</v>
+        <v>-10.8108</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.32</v>
       </c>
       <c r="I77" t="n">
-        <v>0.9046999999999999</v>
+        <v>0.8831</v>
       </c>
       <c r="J77" t="n">
-        <v>24.4269</v>
+        <v>23.8437</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.22</v>
       </c>
       <c r="I78" t="n">
-        <v>0.6694</v>
+        <v>0.6398</v>
       </c>
       <c r="J78" t="n">
-        <v>18.0738</v>
+        <v>17.2746</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.98</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1724</v>
+        <v>-0.1134</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.6548</v>
+        <v>-3.0618</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3139</v>
+        <v>-0.2509</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.475300000000001</v>
+        <v>-6.7743</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3139</v>
+        <v>-0.2509</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.475300000000001</v>
+        <v>-6.7743</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.44</v>
       </c>
       <c r="I82" t="n">
-        <v>1.1009</v>
+        <v>1.0645</v>
       </c>
       <c r="J82" t="n">
-        <v>29.7243</v>
+        <v>28.7415</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.3</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7931</v>
+        <v>0.7941</v>
       </c>
       <c r="J83" t="n">
-        <v>21.4137</v>
+        <v>21.4407</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.22</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5917</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="J84" t="n">
-        <v>15.9759</v>
+        <v>16.3998</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.04</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0509</v>
+        <v>0.1197</v>
       </c>
       <c r="J85" t="n">
-        <v>1.3743</v>
+        <v>3.2319</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.99</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.1811</v>
+        <v>-0.1031</v>
       </c>
       <c r="J86" t="n">
-        <v>-4.8897</v>
+        <v>-2.7837</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.17</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3903</v>
+        <v>0.4362</v>
       </c>
       <c r="J87" t="n">
-        <v>10.5381</v>
+        <v>11.7774</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.95</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0558</v>
+        <v>-0.0615</v>
       </c>
       <c r="J88" t="n">
-        <v>-1.5066</v>
+        <v>-1.6605</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.84</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2739</v>
+        <v>-0.1824</v>
       </c>
       <c r="J89" t="n">
-        <v>-7.3953</v>
+        <v>-4.9248</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.72</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4613</v>
+        <v>-0.3</v>
       </c>
       <c r="J90" t="n">
-        <v>-12.4551</v>
+        <v>-8.1</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.63</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5833</v>
+        <v>-0.3852</v>
       </c>
       <c r="J91" t="n">
-        <v>-15.7491</v>
+        <v>-10.4004</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.21</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6407</v>
+        <v>0.6127</v>
       </c>
       <c r="J92" t="n">
-        <v>19.221</v>
+        <v>18.381</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.17</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5366</v>
+        <v>0.5111</v>
       </c>
       <c r="J93" t="n">
-        <v>16.098</v>
+        <v>15.333</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.13</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4243</v>
+        <v>0.4063</v>
       </c>
       <c r="J94" t="n">
-        <v>12.729</v>
+        <v>12.189</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.05</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1451</v>
+        <v>0.1798</v>
       </c>
       <c r="J95" t="n">
-        <v>4.353</v>
+        <v>5.394</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.87</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5198</v>
+        <v>-0.4584</v>
       </c>
       <c r="J96" t="n">
-        <v>-15.594</v>
+        <v>-13.752</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.24</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4524</v>
+        <v>0.5245</v>
       </c>
       <c r="J97" t="n">
-        <v>13.572</v>
+        <v>15.735</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.08</v>
       </c>
       <c r="I98" t="n">
-        <v>0.207</v>
+        <v>0.214</v>
       </c>
       <c r="J98" t="n">
-        <v>6.21</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.88</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2498</v>
+        <v>-0.1521</v>
       </c>
       <c r="J99" t="n">
-        <v>-7.494</v>
+        <v>-4.563</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.86</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2827</v>
+        <v>-0.1733</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.481</v>
+        <v>-5.199</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.76</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.432</v>
+        <v>-0.2743</v>
       </c>
       <c r="J101" t="n">
-        <v>-12.96</v>
+        <v>-8.228999999999999</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.08</v>
       </c>
       <c r="I102" t="n">
-        <v>0.2627</v>
+        <v>0.2665</v>
       </c>
       <c r="J102" t="n">
-        <v>6.5675</v>
+        <v>6.6625</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.3035</v>
+        <v>-0.2079</v>
       </c>
       <c r="J103" t="n">
-        <v>-7.5875</v>
+        <v>-5.1975</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.76</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3879</v>
+        <v>-0.2561</v>
       </c>
       <c r="J104" t="n">
-        <v>-9.6975</v>
+        <v>-6.4025</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.74</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4186</v>
+        <v>-0.2754</v>
       </c>
       <c r="J105" t="n">
-        <v>-10.465</v>
+        <v>-6.885</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.72</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4484</v>
+        <v>-0.2946</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.21</v>
+        <v>-7.365</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.63</v>
       </c>
       <c r="I107" t="n">
-        <v>1.4808</v>
+        <v>1.0361</v>
       </c>
       <c r="J107" t="n">
-        <v>37.02</v>
+        <v>25.9025</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.27</v>
       </c>
       <c r="I108" t="n">
-        <v>0.7285</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="J108" t="n">
-        <v>18.2125</v>
+        <v>14.15</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.21</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5738</v>
+        <v>0.4824</v>
       </c>
       <c r="J109" t="n">
-        <v>14.345</v>
+        <v>12.06</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3553</v>
+        <v>-0.2791</v>
       </c>
       <c r="J110" t="n">
-        <v>-8.8825</v>
+        <v>-6.9775</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.88</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5262</v>
+        <v>-0.457</v>
       </c>
       <c r="J111" t="n">
-        <v>-13.155</v>
+        <v>-11.425</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.15</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3163</v>
+        <v>0.3431</v>
       </c>
       <c r="J112" t="n">
-        <v>9.172700000000001</v>
+        <v>9.9499</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.13</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2849</v>
+        <v>0.3114</v>
       </c>
       <c r="J113" t="n">
-        <v>8.2621</v>
+        <v>9.0306</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.06</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1637</v>
+        <v>0.1663</v>
       </c>
       <c r="J114" t="n">
-        <v>4.7473</v>
+        <v>4.8227</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.83</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3343</v>
+        <v>-0.2063</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.694699999999999</v>
+        <v>-5.9827</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.73</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4766</v>
+        <v>-0.3053</v>
       </c>
       <c r="J116" t="n">
-        <v>-13.8214</v>
+        <v>-8.8537</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.73</v>
       </c>
       <c r="I117" t="n">
-        <v>1.678</v>
+        <v>1.1722</v>
       </c>
       <c r="J117" t="n">
-        <v>48.662</v>
+        <v>33.9938</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.07</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1704</v>
+        <v>0.2265</v>
       </c>
       <c r="J118" t="n">
-        <v>4.9416</v>
+        <v>6.5685</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.02</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0026</v>
+        <v>0.0595</v>
       </c>
       <c r="J119" t="n">
-        <v>-0.07539999999999999</v>
+        <v>1.7255</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.97</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2433</v>
+        <v>-0.1697</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.0557</v>
+        <v>-4.9213</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.97</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2433</v>
+        <v>-0.1697</v>
       </c>
       <c r="J121" t="n">
-        <v>-7.0557</v>
+        <v>-4.9213</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.1</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3221</v>
+        <v>0.3382</v>
       </c>
       <c r="J122" t="n">
-        <v>6.1199</v>
+        <v>6.4258</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.77</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.327</v>
+        <v>-0.2403</v>
       </c>
       <c r="J123" t="n">
-        <v>-6.213</v>
+        <v>-4.5657</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.75</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.3717</v>
+        <v>-0.2584</v>
       </c>
       <c r="J124" t="n">
-        <v>-7.0623</v>
+        <v>-4.9096</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.6</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.5972</v>
+        <v>-0.3991</v>
       </c>
       <c r="J125" t="n">
-        <v>-11.3468</v>
+        <v>-7.5829</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.59</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6107</v>
+        <v>-0.4084</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.6033</v>
+        <v>-7.7596</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.74</v>
       </c>
       <c r="I127" t="n">
-        <v>1.5968</v>
+        <v>1.121</v>
       </c>
       <c r="J127" t="n">
-        <v>30.3392</v>
+        <v>21.299</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.57</v>
       </c>
       <c r="I128" t="n">
-        <v>1.2781</v>
+        <v>0.9188</v>
       </c>
       <c r="J128" t="n">
-        <v>24.2839</v>
+        <v>17.4572</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.37</v>
       </c>
       <c r="I129" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="J129" t="n">
-        <v>15.8498</v>
+        <v>12.8231</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.29</v>
       </c>
       <c r="I130" t="n">
-        <v>0.6388</v>
+        <v>0.5723</v>
       </c>
       <c r="J130" t="n">
-        <v>12.1372</v>
+        <v>10.8737</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.9</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5192</v>
+        <v>-0.443</v>
       </c>
       <c r="J131" t="n">
-        <v>-9.864800000000001</v>
+        <v>-8.417</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.43</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6524</v>
+        <v>0.4731</v>
       </c>
       <c r="J132" t="n">
-        <v>17.6148</v>
+        <v>12.7737</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.21</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3661</v>
+        <v>0.3069</v>
       </c>
       <c r="J133" t="n">
-        <v>9.8847</v>
+        <v>8.286300000000001</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.03</v>
       </c>
       <c r="I134" t="n">
-        <v>0.039</v>
+        <v>0.056</v>
       </c>
       <c r="J134" t="n">
-        <v>1.053</v>
+        <v>1.512</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.98</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1026</v>
+        <v>-0.0449</v>
       </c>
       <c r="J135" t="n">
-        <v>-2.7702</v>
+        <v>-1.2123</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3883</v>
+        <v>-0.2392</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.4841</v>
+        <v>-6.4584</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.08</v>
       </c>
       <c r="I137" t="n">
-        <v>0.2155</v>
+        <v>0.1686</v>
       </c>
       <c r="J137" t="n">
-        <v>5.8185</v>
+        <v>4.5522</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.07</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1975</v>
+        <v>0.1519</v>
       </c>
       <c r="J138" t="n">
-        <v>5.3325</v>
+        <v>4.1013</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.01</v>
       </c>
       <c r="I139" t="n">
-        <v>0.0699</v>
+        <v>0.0374</v>
       </c>
       <c r="J139" t="n">
-        <v>1.8873</v>
+        <v>1.0098</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.91</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1876</v>
+        <v>-0.1169</v>
       </c>
       <c r="J140" t="n">
-        <v>-5.0652</v>
+        <v>-3.1563</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.64</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5868</v>
+        <v>-0.3859</v>
       </c>
       <c r="J141" t="n">
-        <v>-15.8436</v>
+        <v>-10.4193</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.03</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1124</v>
+        <v>0.101</v>
       </c>
       <c r="J142" t="n">
-        <v>3.2596</v>
+        <v>2.929</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.02</v>
       </c>
       <c r="I143" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.0746</v>
       </c>
       <c r="J143" t="n">
-        <v>2.5926</v>
+        <v>2.1634</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.95</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1123</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="J144" t="n">
-        <v>-3.2567</v>
+        <v>-2.088</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1348</v>
+        <v>-0.0839</v>
       </c>
       <c r="J145" t="n">
-        <v>-3.9092</v>
+        <v>-2.4331</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.84</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.312</v>
+        <v>-0.1932</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.048</v>
+        <v>-5.6028</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.5</v>
       </c>
       <c r="I147" t="n">
-        <v>1.2775</v>
+        <v>0.8983</v>
       </c>
       <c r="J147" t="n">
-        <v>37.0475</v>
+        <v>26.0507</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.14</v>
       </c>
       <c r="I148" t="n">
-        <v>0.449</v>
+        <v>0.3914</v>
       </c>
       <c r="J148" t="n">
-        <v>13.021</v>
+        <v>11.3506</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.07</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2103</v>
+        <v>0.2399</v>
       </c>
       <c r="J149" t="n">
-        <v>6.0987</v>
+        <v>6.9571</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.89</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4674</v>
+        <v>-0.4038</v>
       </c>
       <c r="J150" t="n">
-        <v>-13.5546</v>
+        <v>-11.7102</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.86</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5486</v>
+        <v>-0.4877</v>
       </c>
       <c r="J151" t="n">
-        <v>-15.9094</v>
+        <v>-14.1433</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.26</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4824</v>
+        <v>0.4694</v>
       </c>
       <c r="J152" t="n">
-        <v>13.0248</v>
+        <v>12.6738</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.96</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.0599</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.2707</v>
+        <v>-1.6173</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.93</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1556</v>
+        <v>-0.0956</v>
       </c>
       <c r="J154" t="n">
-        <v>-4.2012</v>
+        <v>-2.5812</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.89</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2298</v>
+        <v>-0.1404</v>
       </c>
       <c r="J155" t="n">
-        <v>-6.2046</v>
+        <v>-3.7908</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.74</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4578</v>
+        <v>-0.2928</v>
       </c>
       <c r="J156" t="n">
-        <v>-12.3606</v>
+        <v>-7.9056</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.34</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9328</v>
+        <v>0.6777</v>
       </c>
       <c r="J157" t="n">
-        <v>25.1856</v>
+        <v>18.2979</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.25</v>
       </c>
       <c r="I158" t="n">
-        <v>0.7251</v>
+        <v>0.5515</v>
       </c>
       <c r="J158" t="n">
-        <v>19.5777</v>
+        <v>14.8905</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.08</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2293</v>
+        <v>0.2655</v>
       </c>
       <c r="J159" t="n">
-        <v>6.1911</v>
+        <v>7.1685</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.04</v>
       </c>
       <c r="I160" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.1415</v>
       </c>
       <c r="J160" t="n">
-        <v>2.5326</v>
+        <v>3.8205</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.84</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.6065</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="J161" t="n">
-        <v>-16.3755</v>
+        <v>-14.7663</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.1</v>
       </c>
       <c r="I162" t="n">
-        <v>0.25</v>
+        <v>0.2628</v>
       </c>
       <c r="J162" t="n">
-        <v>6.25</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.95</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0973</v>
+        <v>-0.0712</v>
       </c>
       <c r="J163" t="n">
-        <v>-2.4325</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1243</v>
+        <v>-0.083</v>
       </c>
       <c r="J164" t="n">
-        <v>-3.1075</v>
+        <v>-2.075</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.93</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1475</v>
+        <v>-0.0944</v>
       </c>
       <c r="J165" t="n">
-        <v>-3.6875</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.79</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3835</v>
+        <v>-0.242</v>
       </c>
       <c r="J166" t="n">
-        <v>-9.5875</v>
+        <v>-6.05</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.49</v>
       </c>
       <c r="I167" t="n">
-        <v>1.2242</v>
+        <v>0.8662</v>
       </c>
       <c r="J167" t="n">
-        <v>30.605</v>
+        <v>21.655</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.16</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4523</v>
+        <v>0.4139</v>
       </c>
       <c r="J168" t="n">
-        <v>11.3075</v>
+        <v>10.3475</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.08</v>
       </c>
       <c r="I169" t="n">
-        <v>0.1994</v>
+        <v>0.2553</v>
       </c>
       <c r="J169" t="n">
-        <v>4.985</v>
+        <v>6.3825</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.06</v>
       </c>
       <c r="I170" t="n">
-        <v>0.1363</v>
+        <v>0.1949</v>
       </c>
       <c r="J170" t="n">
-        <v>3.4075</v>
+        <v>4.8725</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.99</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.1649</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="J171" t="n">
-        <v>-4.1225</v>
+        <v>-2.3075</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.86</v>
       </c>
       <c r="I172" t="n">
-        <v>1.0573</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="J172" t="n">
-        <v>22.2033</v>
+        <v>14.9562</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.71</v>
       </c>
       <c r="I173" t="n">
-        <v>0.9046999999999999</v>
+        <v>0.6226</v>
       </c>
       <c r="J173" t="n">
-        <v>18.9987</v>
+        <v>13.0746</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.08</v>
       </c>
       <c r="I174" t="n">
-        <v>0.0789</v>
+        <v>0.1109</v>
       </c>
       <c r="J174" t="n">
-        <v>1.6569</v>
+        <v>2.3289</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.96</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1874</v>
+        <v>-0.093</v>
       </c>
       <c r="J175" t="n">
-        <v>-3.9354</v>
+        <v>-1.953</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.9</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2892</v>
+        <v>-0.1645</v>
       </c>
       <c r="J176" t="n">
-        <v>-6.0732</v>
+        <v>-3.4545</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.24</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4845</v>
+        <v>0.3915</v>
       </c>
       <c r="J177" t="n">
-        <v>10.1745</v>
+        <v>8.221500000000001</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.99</v>
       </c>
       <c r="I178" t="n">
-        <v>0.0282</v>
+        <v>-0.0062</v>
       </c>
       <c r="J178" t="n">
-        <v>0.5921999999999999</v>
+        <v>-0.1302</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.83</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2985</v>
+        <v>-0.1939</v>
       </c>
       <c r="J179" t="n">
-        <v>-6.2685</v>
+        <v>-4.0719</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.71</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4793</v>
+        <v>-0.3115</v>
       </c>
       <c r="J180" t="n">
-        <v>-10.0653</v>
+        <v>-6.5415</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.61</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6121</v>
+        <v>-0.4057</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.8541</v>
+        <v>-8.5197</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.98</v>
       </c>
       <c r="I182" t="n">
-        <v>0.0414</v>
+        <v>-0.0042</v>
       </c>
       <c r="J182" t="n">
-        <v>0.9936</v>
+        <v>-0.1008</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.87</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1668</v>
+        <v>-0.1423</v>
       </c>
       <c r="J183" t="n">
-        <v>-4.0032</v>
+        <v>-3.4152</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.78</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.3333</v>
+        <v>-0.2329</v>
       </c>
       <c r="J184" t="n">
-        <v>-7.9992</v>
+        <v>-5.5896</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.7</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4644</v>
+        <v>-0.3085</v>
       </c>
       <c r="J185" t="n">
-        <v>-11.1456</v>
+        <v>-7.404</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.6</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.604</v>
+        <v>-0.4027</v>
       </c>
       <c r="J186" t="n">
-        <v>-14.496</v>
+        <v>-9.6648</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.57</v>
       </c>
       <c r="I187" t="n">
-        <v>1.3244</v>
+        <v>0.9385</v>
       </c>
       <c r="J187" t="n">
-        <v>31.7856</v>
+        <v>22.524</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.56</v>
       </c>
       <c r="I188" t="n">
-        <v>1.305</v>
+        <v>0.9261</v>
       </c>
       <c r="J188" t="n">
-        <v>31.32</v>
+        <v>22.2264</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.14</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3132</v>
+        <v>0.3697</v>
       </c>
       <c r="J189" t="n">
-        <v>7.5168</v>
+        <v>8.8728</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.09</v>
       </c>
       <c r="I190" t="n">
-        <v>0.1759</v>
+        <v>0.2564</v>
       </c>
       <c r="J190" t="n">
-        <v>4.2216</v>
+        <v>6.1536</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.01</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.0902</v>
+        <v>-0.0118</v>
       </c>
       <c r="J191" t="n">
-        <v>-2.1648</v>
+        <v>-0.2832</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>0.67</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.3379</v>
+        <v>-0.2839</v>
       </c>
       <c r="J192" t="n">
-        <v>-6.4201</v>
+        <v>-5.3941</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.55</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.5278</v>
+        <v>-0.4054</v>
       </c>
       <c r="J193" t="n">
-        <v>-10.0282</v>
+        <v>-7.7026</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.48</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.6666</v>
+        <v>-0.4675</v>
       </c>
       <c r="J194" t="n">
-        <v>-12.6654</v>
+        <v>-8.8825</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.45</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.714</v>
+        <v>-0.4957</v>
       </c>
       <c r="J195" t="n">
-        <v>-13.566</v>
+        <v>-9.4183</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.45</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.714</v>
+        <v>-0.4957</v>
       </c>
       <c r="J196" t="n">
-        <v>-13.566</v>
+        <v>-9.4183</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>2.35</v>
       </c>
       <c r="I197" t="n">
-        <v>2.154</v>
+        <v>1.7432</v>
       </c>
       <c r="J197" t="n">
-        <v>40.926</v>
+        <v>33.1208</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.63</v>
       </c>
       <c r="I198" t="n">
-        <v>1.2844</v>
+        <v>0.9597</v>
       </c>
       <c r="J198" t="n">
-        <v>24.4036</v>
+        <v>18.2343</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.6</v>
       </c>
       <c r="I199" t="n">
-        <v>1.2106</v>
+        <v>0.9267</v>
       </c>
       <c r="J199" t="n">
-        <v>23.0014</v>
+        <v>17.6073</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.39</v>
       </c>
       <c r="I200" t="n">
-        <v>0.7708</v>
+        <v>0.6765</v>
       </c>
       <c r="J200" t="n">
-        <v>14.6452</v>
+        <v>12.8535</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.04</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.0556</v>
+        <v>0.0336</v>
       </c>
       <c r="J201" t="n">
-        <v>-1.0564</v>
+        <v>0.6384</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.52</v>
       </c>
       <c r="I202" t="n">
-        <v>1.2243</v>
+        <v>1.1493</v>
       </c>
       <c r="J202" t="n">
-        <v>26.9346</v>
+        <v>25.2846</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.45</v>
       </c>
       <c r="I203" t="n">
-        <v>1.0815</v>
+        <v>1.0611</v>
       </c>
       <c r="J203" t="n">
-        <v>23.793</v>
+        <v>23.3442</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.33</v>
       </c>
       <c r="I204" t="n">
-        <v>0.8156</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="J204" t="n">
-        <v>17.9432</v>
+        <v>18.5284</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.16</v>
       </c>
       <c r="I205" t="n">
-        <v>0.3641</v>
+        <v>0.4459</v>
       </c>
       <c r="J205" t="n">
-        <v>8.010199999999999</v>
+        <v>9.809799999999999</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.93</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4128</v>
+        <v>-0.3328</v>
       </c>
       <c r="J206" t="n">
-        <v>-9.0816</v>
+        <v>-7.3216</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.18</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4081</v>
+        <v>0.4599</v>
       </c>
       <c r="J207" t="n">
-        <v>8.978199999999999</v>
+        <v>10.1178</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.03</v>
       </c>
       <c r="I208" t="n">
-        <v>0.1542</v>
+        <v>0.1324</v>
       </c>
       <c r="J208" t="n">
-        <v>3.3924</v>
+        <v>2.9128</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.87</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2036</v>
+        <v>-0.1519</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.4792</v>
+        <v>-3.3418</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.72</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.4589</v>
+        <v>-0.2989</v>
       </c>
       <c r="J210" t="n">
-        <v>-10.0958</v>
+        <v>-6.5758</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.47</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.7798</v>
+        <v>-0.5315</v>
       </c>
       <c r="J211" t="n">
-        <v>-17.1556</v>
+        <v>-11.693</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.33</v>
       </c>
       <c r="I212" t="n">
-        <v>0.8558</v>
+        <v>0.8592</v>
       </c>
       <c r="J212" t="n">
-        <v>18.8276</v>
+        <v>18.9024</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.3</v>
       </c>
       <c r="I213" t="n">
-        <v>0.786</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="J213" t="n">
-        <v>17.292</v>
+        <v>17.3976</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.17</v>
       </c>
       <c r="I214" t="n">
-        <v>0.4271</v>
+        <v>0.4858</v>
       </c>
       <c r="J214" t="n">
-        <v>9.3962</v>
+        <v>10.6876</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.14</v>
       </c>
       <c r="I215" t="n">
-        <v>0.3442</v>
+        <v>0.4089</v>
       </c>
       <c r="J215" t="n">
-        <v>7.5724</v>
+        <v>8.995799999999999</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.11</v>
       </c>
       <c r="I216" t="n">
-        <v>0.26</v>
+        <v>0.3281</v>
       </c>
       <c r="J216" t="n">
-        <v>5.72</v>
+        <v>7.2182</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.99</v>
       </c>
       <c r="I217" t="n">
-        <v>0.0409</v>
+        <v>-0.0008</v>
       </c>
       <c r="J217" t="n">
-        <v>0.8998</v>
+        <v>-0.0176</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.97</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.007</v>
+        <v>-0.0318</v>
       </c>
       <c r="J218" t="n">
-        <v>-0.154</v>
+        <v>-0.6996</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.91</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1249</v>
+        <v>-0.1073</v>
       </c>
       <c r="J219" t="n">
-        <v>-2.7478</v>
+        <v>-2.3606</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.77</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3822</v>
+        <v>-0.2496</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.4084</v>
+        <v>-5.4912</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.59</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6313</v>
+        <v>-0.4204</v>
       </c>
       <c r="J221" t="n">
-        <v>-13.8886</v>
+        <v>-9.248799999999999</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.68</v>
       </c>
       <c r="I222" t="n">
-        <v>1.4587</v>
+        <v>1.3116</v>
       </c>
       <c r="J222" t="n">
-        <v>32.0914</v>
+        <v>28.8552</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.57</v>
       </c>
       <c r="I223" t="n">
-        <v>1.2471</v>
+        <v>1.1824</v>
       </c>
       <c r="J223" t="n">
-        <v>27.4362</v>
+        <v>26.0128</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.52</v>
       </c>
       <c r="I224" t="n">
-        <v>1.1451</v>
+        <v>1.123</v>
       </c>
       <c r="J224" t="n">
-        <v>25.1922</v>
+        <v>24.706</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.5</v>
       </c>
       <c r="I225" t="n">
-        <v>1.1026</v>
+        <v>1.0992</v>
       </c>
       <c r="J225" t="n">
-        <v>24.2572</v>
+        <v>24.1824</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.93</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4493</v>
+        <v>-0.3673</v>
       </c>
       <c r="J226" t="n">
-        <v>-9.884600000000001</v>
+        <v>-8.0806</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.1953</v>
+        <v>-0.1754</v>
       </c>
       <c r="J227" t="n">
-        <v>-4.2966</v>
+        <v>-3.8588</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.68</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.4019</v>
+        <v>-0.3086</v>
       </c>
       <c r="J228" t="n">
-        <v>-8.841799999999999</v>
+        <v>-6.7892</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.61</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.5352</v>
+        <v>-0.3711</v>
       </c>
       <c r="J229" t="n">
-        <v>-11.7744</v>
+        <v>-8.164199999999999</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.58</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.582</v>
+        <v>-0.3987</v>
       </c>
       <c r="J230" t="n">
-        <v>-12.804</v>
+        <v>-8.7714</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.55</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6261</v>
+        <v>-0.4266</v>
       </c>
       <c r="J231" t="n">
-        <v>-13.7742</v>
+        <v>-9.385199999999999</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.07</v>
       </c>
       <c r="I232" t="n">
-        <v>0.2811</v>
+        <v>0.2216</v>
       </c>
       <c r="J232" t="n">
-        <v>6.7464</v>
+        <v>5.3184</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.77</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.3098</v>
+        <v>-0.2373</v>
       </c>
       <c r="J233" t="n">
-        <v>-7.4352</v>
+        <v>-5.6952</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.73</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.3903</v>
+        <v>-0.2742</v>
       </c>
       <c r="J234" t="n">
-        <v>-9.3672</v>
+        <v>-6.5808</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.57</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.4234</v>
       </c>
       <c r="J235" t="n">
-        <v>-15.132</v>
+        <v>-10.1616</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.55</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.657</v>
+        <v>-0.4421</v>
       </c>
       <c r="J236" t="n">
-        <v>-15.768</v>
+        <v>-10.6104</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.46</v>
       </c>
       <c r="I237" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.5579</v>
       </c>
       <c r="J237" t="n">
-        <v>14.8176</v>
+        <v>13.3896</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.46</v>
       </c>
       <c r="I238" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.5579</v>
       </c>
       <c r="J238" t="n">
-        <v>14.8176</v>
+        <v>13.3896</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.31</v>
       </c>
       <c r="I239" t="n">
-        <v>0.4082</v>
+        <v>0.3974</v>
       </c>
       <c r="J239" t="n">
-        <v>9.796799999999999</v>
+        <v>9.537599999999999</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.29</v>
       </c>
       <c r="I240" t="n">
-        <v>0.3795</v>
+        <v>0.3751</v>
       </c>
       <c r="J240" t="n">
-        <v>9.108000000000001</v>
+        <v>9.0024</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>1.15</v>
       </c>
       <c r="I241" t="n">
-        <v>0.1815</v>
+        <v>0.2049</v>
       </c>
       <c r="J241" t="n">
-        <v>4.356</v>
+        <v>4.9176</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.65</v>
       </c>
       <c r="I242" t="n">
-        <v>1.4537</v>
+        <v>1.2988</v>
       </c>
       <c r="J242" t="n">
-        <v>31.9814</v>
+        <v>28.5736</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.45</v>
       </c>
       <c r="I243" t="n">
-        <v>1.0582</v>
+        <v>1.0532</v>
       </c>
       <c r="J243" t="n">
-        <v>23.2804</v>
+        <v>23.1704</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.24</v>
       </c>
       <c r="I244" t="n">
-        <v>0.5436</v>
+        <v>0.6328</v>
       </c>
       <c r="J244" t="n">
-        <v>11.9592</v>
+        <v>13.9216</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.23</v>
       </c>
       <c r="I245" t="n">
-        <v>0.5192</v>
+        <v>0.6091</v>
       </c>
       <c r="J245" t="n">
-        <v>11.4224</v>
+        <v>13.4002</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>1.05</v>
       </c>
       <c r="I246" t="n">
-        <v>0.0396</v>
+        <v>0.1227</v>
       </c>
       <c r="J246" t="n">
-        <v>0.8712</v>
+        <v>2.6994</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.08</v>
       </c>
       <c r="I247" t="n">
-        <v>0.2693</v>
+        <v>0.2743</v>
       </c>
       <c r="J247" t="n">
-        <v>5.9246</v>
+        <v>6.0346</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.86</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.1941</v>
+        <v>-0.1564</v>
       </c>
       <c r="J248" t="n">
-        <v>-4.2702</v>
+        <v>-3.4408</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2856</v>
+        <v>-0.2067</v>
       </c>
       <c r="J249" t="n">
-        <v>-6.2832</v>
+        <v>-4.5474</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.67</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.5145</v>
+        <v>-0.3398</v>
       </c>
       <c r="J250" t="n">
-        <v>-11.319</v>
+        <v>-7.4756</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.61</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.596</v>
+        <v>-0.3962</v>
       </c>
       <c r="J251" t="n">
-        <v>-13.112</v>
+        <v>-8.7164</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.69</v>
       </c>
       <c r="I252" t="n">
-        <v>1.5163</v>
+        <v>1.0672</v>
       </c>
       <c r="J252" t="n">
-        <v>34.8749</v>
+        <v>24.5456</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.38</v>
       </c>
       <c r="I253" t="n">
-        <v>0.8871</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="J253" t="n">
-        <v>20.4033</v>
+        <v>15.847</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.26</v>
       </c>
       <c r="I254" t="n">
-        <v>0.5793</v>
+        <v>0.5345</v>
       </c>
       <c r="J254" t="n">
-        <v>13.3239</v>
+        <v>12.2935</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.25</v>
       </c>
       <c r="I255" t="n">
-        <v>0.5554</v>
+        <v>0.5208</v>
       </c>
       <c r="J255" t="n">
-        <v>12.7742</v>
+        <v>11.9784</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1.17</v>
       </c>
       <c r="I256" t="n">
-        <v>0.3606</v>
+        <v>0.4056</v>
       </c>
       <c r="J256" t="n">
-        <v>8.293799999999999</v>
+        <v>9.328799999999999</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.01</v>
       </c>
       <c r="I257" t="n">
-        <v>0.1502</v>
+        <v>0.1208</v>
       </c>
       <c r="J257" t="n">
-        <v>3.4546</v>
+        <v>2.7784</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.9</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.0989</v>
+        <v>-0.1013</v>
       </c>
       <c r="J258" t="n">
-        <v>-2.2747</v>
+        <v>-2.3299</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.66</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.5099</v>
+        <v>-0.3413</v>
       </c>
       <c r="J259" t="n">
-        <v>-11.7277</v>
+        <v>-7.8499</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.63</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.5528</v>
+        <v>-0.3694</v>
       </c>
       <c r="J260" t="n">
-        <v>-12.7144</v>
+        <v>-8.4962</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.6476</v>
+        <v>-0.4349</v>
       </c>
       <c r="J261" t="n">
-        <v>-14.8948</v>
+        <v>-10.0027</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.24</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4482</v>
+        <v>0.3716</v>
       </c>
       <c r="J262" t="n">
-        <v>11.6532</v>
+        <v>9.6616</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.19</v>
       </c>
       <c r="I263" t="n">
-        <v>0.3776</v>
+        <v>0.3254</v>
       </c>
       <c r="J263" t="n">
-        <v>9.817600000000001</v>
+        <v>8.4604</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.87</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2703</v>
+        <v>-0.1641</v>
       </c>
       <c r="J264" t="n">
-        <v>-7.0278</v>
+        <v>-4.2666</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.86</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2865</v>
+        <v>-0.1747</v>
       </c>
       <c r="J265" t="n">
-        <v>-7.449</v>
+        <v>-4.5422</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.72</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4892</v>
+        <v>-0.3144</v>
       </c>
       <c r="J266" t="n">
-        <v>-12.7192</v>
+        <v>-8.1744</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.41</v>
       </c>
       <c r="I267" t="n">
-        <v>0.6284</v>
+        <v>0.4595</v>
       </c>
       <c r="J267" t="n">
-        <v>16.3384</v>
+        <v>11.947</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.08</v>
       </c>
       <c r="I268" t="n">
-        <v>0.1409</v>
+        <v>0.1353</v>
       </c>
       <c r="J268" t="n">
-        <v>3.6634</v>
+        <v>3.5178</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.03</v>
       </c>
       <c r="I269" t="n">
-        <v>0.039</v>
+        <v>0.056</v>
       </c>
       <c r="J269" t="n">
-        <v>1.014</v>
+        <v>1.456</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.99</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.07779999999999999</v>
+        <v>-0.0291</v>
       </c>
       <c r="J270" t="n">
-        <v>-2.0228</v>
+        <v>-0.7566000000000001</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.95</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.1649</v>
+        <v>-0.0854</v>
       </c>
       <c r="J271" t="n">
-        <v>-4.2874</v>
+        <v>-2.2204</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.67</v>
       </c>
       <c r="I272" t="n">
-        <v>1.5877</v>
+        <v>1.1078</v>
       </c>
       <c r="J272" t="n">
-        <v>44.4556</v>
+        <v>31.0184</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.16</v>
       </c>
       <c r="I273" t="n">
-        <v>0.4839</v>
+        <v>0.4177</v>
       </c>
       <c r="J273" t="n">
-        <v>13.5492</v>
+        <v>11.6956</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.03</v>
       </c>
       <c r="I274" t="n">
-        <v>0.0506</v>
+        <v>0.104</v>
       </c>
       <c r="J274" t="n">
-        <v>1.4168</v>
+        <v>2.912</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.91</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.4221</v>
+        <v>-0.3539</v>
       </c>
       <c r="J275" t="n">
-        <v>-11.8188</v>
+        <v>-9.9092</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.84</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.5502</v>
       </c>
       <c r="J276" t="n">
-        <v>-17.0912</v>
+        <v>-15.4056</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.13</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3064</v>
+        <v>0.3282</v>
       </c>
       <c r="J277" t="n">
-        <v>8.5792</v>
+        <v>9.1896</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.02</v>
       </c>
       <c r="I278" t="n">
-        <v>0.1039</v>
+        <v>0.0832</v>
       </c>
       <c r="J278" t="n">
-        <v>2.9092</v>
+        <v>2.3296</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.87</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.2508</v>
+        <v>-0.158</v>
       </c>
       <c r="J279" t="n">
-        <v>-7.0224</v>
+        <v>-4.424</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.82</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3323</v>
+        <v>-0.2095</v>
       </c>
       <c r="J280" t="n">
-        <v>-9.304399999999999</v>
+        <v>-5.866</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.77</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4071</v>
+        <v>-0.2593</v>
       </c>
       <c r="J281" t="n">
-        <v>-11.3988</v>
+        <v>-7.2604</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.75</v>
       </c>
       <c r="I282" t="n">
-        <v>1.654</v>
+        <v>1.1555</v>
       </c>
       <c r="J282" t="n">
-        <v>47.966</v>
+        <v>33.5095</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.48</v>
       </c>
       <c r="I283" t="n">
-        <v>1.1416</v>
+        <v>0.8246</v>
       </c>
       <c r="J283" t="n">
-        <v>33.1064</v>
+        <v>23.9134</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.32</v>
       </c>
       <c r="I284" t="n">
-        <v>0.7887</v>
+        <v>0.6199</v>
       </c>
       <c r="J284" t="n">
-        <v>22.8723</v>
+        <v>17.9771</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.384</v>
+        <v>-0.3025</v>
       </c>
       <c r="J285" t="n">
-        <v>-11.136</v>
+        <v>-8.772500000000001</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.92</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4428</v>
+        <v>-0.3641</v>
       </c>
       <c r="J286" t="n">
-        <v>-12.8412</v>
+        <v>-10.5589</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.35</v>
       </c>
       <c r="I287" t="n">
-        <v>0.6381</v>
+        <v>0.5967</v>
       </c>
       <c r="J287" t="n">
-        <v>18.5049</v>
+        <v>17.3043</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.95</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.0513</v>
+        <v>-0.0599</v>
       </c>
       <c r="J288" t="n">
-        <v>-1.4877</v>
+        <v>-1.7371</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.75</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.4146</v>
+        <v>-0.2698</v>
       </c>
       <c r="J289" t="n">
-        <v>-12.0234</v>
+        <v>-7.8242</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.73</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4439</v>
+        <v>-0.2891</v>
       </c>
       <c r="J290" t="n">
-        <v>-12.8731</v>
+        <v>-8.383900000000001</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.48</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.7675999999999999</v>
+        <v>-0.5222</v>
       </c>
       <c r="J291" t="n">
-        <v>-22.2604</v>
+        <v>-15.1438</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.87</v>
       </c>
       <c r="I292" t="n">
-        <v>1.8082</v>
+        <v>1.3072</v>
       </c>
       <c r="J292" t="n">
-        <v>45.205</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.34</v>
       </c>
       <c r="I293" t="n">
-        <v>0.8537</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="J293" t="n">
-        <v>21.3425</v>
+        <v>16.2425</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.33</v>
       </c>
       <c r="I294" t="n">
-        <v>0.8304</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="J294" t="n">
-        <v>20.76</v>
+        <v>15.915</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.93</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.4063</v>
+        <v>-0.3272</v>
       </c>
       <c r="J295" t="n">
-        <v>-10.1575</v>
+        <v>-8.18</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.8</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.7423</v>
+        <v>-0.6875</v>
       </c>
       <c r="J296" t="n">
-        <v>-18.5575</v>
+        <v>-17.1875</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.02</v>
       </c>
       <c r="I297" t="n">
-        <v>0.1375</v>
+        <v>0.1105</v>
       </c>
       <c r="J297" t="n">
-        <v>3.4375</v>
+        <v>2.7625</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.92</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.1035</v>
+        <v>-0.0948</v>
       </c>
       <c r="J298" t="n">
-        <v>-2.5875</v>
+        <v>-2.37</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.85</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.2327</v>
+        <v>-0.1708</v>
       </c>
       <c r="J299" t="n">
-        <v>-5.8175</v>
+        <v>-4.27</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.73</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.44</v>
+        <v>-0.2874</v>
       </c>
       <c r="J300" t="n">
-        <v>-11</v>
+        <v>-7.185</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.68</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5108</v>
+        <v>-0.3352</v>
       </c>
       <c r="J301" t="n">
-        <v>-12.77</v>
+        <v>-8.380000000000001</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.33</v>
       </c>
       <c r="I302" t="n">
-        <v>0.9215</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="J302" t="n">
-        <v>27.645</v>
+        <v>20.067</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.21</v>
       </c>
       <c r="I303" t="n">
-        <v>0.6383</v>
+        <v>0.4974</v>
       </c>
       <c r="J303" t="n">
-        <v>19.149</v>
+        <v>14.922</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.07</v>
       </c>
       <c r="I304" t="n">
-        <v>0.212</v>
+        <v>0.2402</v>
       </c>
       <c r="J304" t="n">
-        <v>6.36</v>
+        <v>7.206</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.93</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.3498</v>
+        <v>-0.2849</v>
       </c>
       <c r="J305" t="n">
-        <v>-10.494</v>
+        <v>-8.547000000000001</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.91</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4097</v>
+        <v>-0.3452</v>
       </c>
       <c r="J306" t="n">
-        <v>-12.291</v>
+        <v>-10.356</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.17</v>
       </c>
       <c r="I307" t="n">
-        <v>0.3728</v>
+        <v>0.3821</v>
       </c>
       <c r="J307" t="n">
-        <v>11.184</v>
+        <v>11.463</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.9</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.1874</v>
+        <v>-0.1248</v>
       </c>
       <c r="J308" t="n">
-        <v>-5.622</v>
+        <v>-3.744</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.87</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.2445</v>
+        <v>-0.1565</v>
       </c>
       <c r="J309" t="n">
-        <v>-7.335</v>
+        <v>-4.695</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.86</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2619</v>
+        <v>-0.1669</v>
       </c>
       <c r="J310" t="n">
-        <v>-7.857</v>
+        <v>-5.007</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.74</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.446</v>
+        <v>-0.2868</v>
       </c>
       <c r="J311" t="n">
-        <v>-13.38</v>
+        <v>-8.603999999999999</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.37</v>
       </c>
       <c r="I312" t="n">
-        <v>0.5782</v>
+        <v>0.4536</v>
       </c>
       <c r="J312" t="n">
-        <v>20.237</v>
+        <v>15.876</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.37</v>
       </c>
       <c r="I313" t="n">
-        <v>0.5782</v>
+        <v>0.4536</v>
       </c>
       <c r="J313" t="n">
-        <v>20.237</v>
+        <v>15.876</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.06</v>
       </c>
       <c r="I314" t="n">
-        <v>0.0992</v>
+        <v>0.1129</v>
       </c>
       <c r="J314" t="n">
-        <v>3.472</v>
+        <v>3.9515</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.86</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.3161</v>
+        <v>-0.1881</v>
       </c>
       <c r="J315" t="n">
-        <v>-11.0635</v>
+        <v>-6.5835</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.82</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.3749</v>
+        <v>-0.2295</v>
       </c>
       <c r="J316" t="n">
-        <v>-13.1215</v>
+        <v>-8.032500000000001</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.16</v>
       </c>
       <c r="I317" t="n">
-        <v>0.2982</v>
+        <v>0.2461</v>
       </c>
       <c r="J317" t="n">
-        <v>10.437</v>
+        <v>8.6135</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.13</v>
       </c>
       <c r="I318" t="n">
-        <v>0.2498</v>
+        <v>0.2062</v>
       </c>
       <c r="J318" t="n">
-        <v>8.743</v>
+        <v>7.217</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.06</v>
       </c>
       <c r="I319" t="n">
-        <v>0.1111</v>
+        <v>0.1074</v>
       </c>
       <c r="J319" t="n">
-        <v>3.8885</v>
+        <v>3.759</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.04</v>
       </c>
       <c r="I320" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.0756</v>
       </c>
       <c r="J320" t="n">
-        <v>2.3975</v>
+        <v>2.646</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.97</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.119</v>
+        <v>-0.0571</v>
       </c>
       <c r="J321" t="n">
-        <v>-4.165</v>
+        <v>-1.9985</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.67</v>
       </c>
       <c r="I322" t="n">
-        <v>1.4609</v>
+        <v>1.0349</v>
       </c>
       <c r="J322" t="n">
-        <v>30.6789</v>
+        <v>21.7329</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.54</v>
       </c>
       <c r="I323" t="n">
-        <v>1.21</v>
+        <v>0.8798</v>
       </c>
       <c r="J323" t="n">
-        <v>25.41</v>
+        <v>18.4758</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.34</v>
       </c>
       <c r="I324" t="n">
-        <v>0.7465000000000001</v>
+        <v>0.6357</v>
       </c>
       <c r="J324" t="n">
-        <v>15.6765</v>
+        <v>13.3497</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.21</v>
       </c>
       <c r="I325" t="n">
-        <v>0.4432</v>
+        <v>0.4591</v>
       </c>
       <c r="J325" t="n">
-        <v>9.3072</v>
+        <v>9.6411</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>1.2</v>
       </c>
       <c r="I326" t="n">
-        <v>0.4192</v>
+        <v>0.4446</v>
       </c>
       <c r="J326" t="n">
-        <v>8.8032</v>
+        <v>9.336600000000001</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>0.88</v>
       </c>
       <c r="I327" t="n">
-        <v>-0.1017</v>
+        <v>-0.1076</v>
       </c>
       <c r="J327" t="n">
-        <v>-2.1357</v>
+        <v>-2.2596</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>0.87</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.1185</v>
+        <v>-0.1193</v>
       </c>
       <c r="J328" t="n">
-        <v>-2.4885</v>
+        <v>-2.5053</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.76</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.296</v>
+        <v>-0.2382</v>
       </c>
       <c r="J329" t="n">
-        <v>-6.216</v>
+        <v>-5.0022</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.52</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.6817</v>
+        <v>-0.4617</v>
       </c>
       <c r="J330" t="n">
-        <v>-14.3157</v>
+        <v>-9.6957</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.4</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.8349</v>
+        <v>-0.5741000000000001</v>
       </c>
       <c r="J331" t="n">
-        <v>-17.5329</v>
+        <v>-12.0561</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>0.99</v>
       </c>
       <c r="I332" t="n">
-        <v>0.1044</v>
+        <v>0.0684</v>
       </c>
       <c r="J332" t="n">
-        <v>2.1924</v>
+        <v>1.4364</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>0.72</v>
       </c>
       <c r="I333" t="n">
-        <v>-0.3726</v>
+        <v>-0.2798</v>
       </c>
       <c r="J333" t="n">
-        <v>-7.8246</v>
+        <v>-5.8758</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>0.65</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.5029</v>
+        <v>-0.343</v>
       </c>
       <c r="J334" t="n">
-        <v>-10.5609</v>
+        <v>-7.203</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.61</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.5626</v>
+        <v>-0.3802</v>
       </c>
       <c r="J335" t="n">
-        <v>-11.8146</v>
+        <v>-7.9842</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.54</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.6598000000000001</v>
+        <v>-0.4457</v>
       </c>
       <c r="J336" t="n">
-        <v>-13.8558</v>
+        <v>-9.3597</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>2.02</v>
       </c>
       <c r="I337" t="n">
-        <v>1.9137</v>
+        <v>1.4395</v>
       </c>
       <c r="J337" t="n">
-        <v>40.1877</v>
+        <v>30.2295</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.6</v>
       </c>
       <c r="I338" t="n">
-        <v>1.3291</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="J338" t="n">
-        <v>27.9111</v>
+        <v>19.9941</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.18</v>
       </c>
       <c r="I339" t="n">
-        <v>0.3714</v>
+        <v>0.4155</v>
       </c>
       <c r="J339" t="n">
-        <v>7.7994</v>
+        <v>8.7255</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>1.11</v>
       </c>
       <c r="I340" t="n">
-        <v>0.1932</v>
+        <v>0.287</v>
       </c>
       <c r="J340" t="n">
-        <v>4.0572</v>
+        <v>6.027</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>1.04</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.0109</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="J341" t="n">
-        <v>-0.2289</v>
+        <v>1.5729</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.24</v>
       </c>
       <c r="I342" t="n">
-        <v>0.4109</v>
+        <v>0.4232</v>
       </c>
       <c r="J342" t="n">
-        <v>17.2578</v>
+        <v>17.7744</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.17</v>
       </c>
       <c r="I343" t="n">
-        <v>0.3084</v>
+        <v>0.3497</v>
       </c>
       <c r="J343" t="n">
-        <v>12.9528</v>
+        <v>14.6874</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.14</v>
       </c>
       <c r="I344" t="n">
-        <v>0.2606</v>
+        <v>0.3055</v>
       </c>
       <c r="J344" t="n">
-        <v>10.9452</v>
+        <v>12.831</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>1.11</v>
       </c>
       <c r="I345" t="n">
-        <v>0.2088</v>
+        <v>0.2489</v>
       </c>
       <c r="J345" t="n">
-        <v>8.769600000000001</v>
+        <v>10.4538</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.77</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.4426</v>
+        <v>-0.2782</v>
       </c>
       <c r="J346" t="n">
-        <v>-18.5892</v>
+        <v>-11.6844</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.54</v>
       </c>
       <c r="I347" t="n">
-        <v>1.3884</v>
+        <v>0.9724</v>
       </c>
       <c r="J347" t="n">
-        <v>58.3128</v>
+        <v>40.8408</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.26</v>
       </c>
       <c r="I348" t="n">
-        <v>0.793</v>
+        <v>0.5838</v>
       </c>
       <c r="J348" t="n">
-        <v>33.306</v>
+        <v>24.5196</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>0.93</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.323</v>
+        <v>-0.2694</v>
       </c>
       <c r="J349" t="n">
-        <v>-13.566</v>
+        <v>-11.3148</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.89</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.4429</v>
+        <v>-0.3874</v>
       </c>
       <c r="J350" t="n">
-        <v>-18.6018</v>
+        <v>-16.2708</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.55</v>
       </c>
       <c r="I351" t="n">
-        <v>-1.235</v>
+        <v>-1.2417</v>
       </c>
       <c r="J351" t="n">
-        <v>-51.87</v>
+        <v>-52.1514</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5202/event_5202_evp_summary.xlsx
+++ b/database/event/5202/event_5202_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.4421</v>
+        <v>8.657999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3242</v>
+        <v>2.3836</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1732</v>
+        <v>3.3171</v>
       </c>
       <c r="E2" t="n">
-        <v>8.4421</v>
+        <v>8.657999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4573</v>
+        <v>2.3849</v>
       </c>
       <c r="G2" t="n">
-        <v>5.9848</v>
+        <v>6.2731</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4573</v>
+        <v>2.4948</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8872</v>
+        <v>2.7621</v>
       </c>
       <c r="J2" t="n">
-        <v>5.9848</v>
+        <v>6.2731</v>
       </c>
       <c r="K2" t="n">
         <v>139</v>
@@ -529,7 +529,7 @@
         <v>250</v>
       </c>
       <c r="M2" t="n">
-        <v>8.872</v>
+        <v>9.0352</v>
       </c>
       <c r="N2" t="n">
         <v>389</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.0031</v>
+        <v>6.4627</v>
       </c>
       <c r="C3" t="n">
-        <v>1.6527</v>
+        <v>1.7792</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0721</v>
+        <v>2.3178</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0031</v>
+        <v>6.4627</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2797</v>
+        <v>0.2922</v>
       </c>
       <c r="G3" t="n">
-        <v>5.7234</v>
+        <v>6.1705</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2797</v>
+        <v>0.2922</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3032</v>
+        <v>0.3075</v>
       </c>
       <c r="J3" t="n">
-        <v>5.7234</v>
+        <v>6.1705</v>
       </c>
       <c r="K3" t="n">
         <v>57</v>
@@ -575,7 +575,7 @@
         <v>222</v>
       </c>
       <c r="M3" t="n">
-        <v>6.0266</v>
+        <v>6.478</v>
       </c>
       <c r="N3" t="n">
         <v>279</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.2846</v>
+        <v>4.7042</v>
       </c>
       <c r="C4" t="n">
-        <v>1.1796</v>
+        <v>1.2951</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2963</v>
+        <v>1.5172</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2846</v>
+        <v>4.7042</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3566</v>
+        <v>0.3573</v>
       </c>
       <c r="G4" t="n">
-        <v>3.9279</v>
+        <v>4.3469</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3566</v>
+        <v>0.3573</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3713</v>
+        <v>0.3665</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9279</v>
+        <v>4.3469</v>
       </c>
       <c r="K4" t="n">
         <v>75</v>
@@ -621,7 +621,7 @@
         <v>193</v>
       </c>
       <c r="M4" t="n">
-        <v>4.2992</v>
+        <v>4.7134</v>
       </c>
       <c r="N4" t="n">
         <v>268</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.0399</v>
+        <v>4.2614</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1122</v>
+        <v>1.1732</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1858</v>
+        <v>1.3157</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0399</v>
+        <v>4.2614</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3035</v>
+        <v>1.2576</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7364</v>
+        <v>3.0038</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3035</v>
+        <v>1.2576</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3035</v>
+        <v>1.2576</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7364</v>
+        <v>3.0038</v>
       </c>
       <c r="K5" t="n">
         <v>121</v>
@@ -667,7 +667,7 @@
         <v>138</v>
       </c>
       <c r="M5" t="n">
-        <v>4.0399</v>
+        <v>4.2614</v>
       </c>
       <c r="N5" t="n">
         <v>259</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.7529</v>
+        <v>4.1226</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0332</v>
+        <v>1.135</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0562</v>
+        <v>1.2525</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7529</v>
+        <v>4.1226</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9787</v>
+        <v>0.9586</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7743</v>
+        <v>3.164</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9787</v>
+        <v>0.9586</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0189</v>
+        <v>0.9833</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7743</v>
+        <v>3.164</v>
       </c>
       <c r="K6" t="n">
         <v>75</v>
@@ -713,7 +713,7 @@
         <v>193</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7932</v>
+        <v>4.1473</v>
       </c>
       <c r="N6" t="n">
         <v>268</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.1438</v>
+        <v>3.2164</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8655</v>
+        <v>0.8855</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7813</v>
+        <v>0.84</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1438</v>
+        <v>3.2164</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9708</v>
+        <v>1.1463</v>
       </c>
       <c r="G7" t="n">
-        <v>0.173</v>
+        <v>2.0701</v>
       </c>
       <c r="H7" t="n">
-        <v>3.1637</v>
+        <v>1.1463</v>
       </c>
       <c r="I7" t="n">
-        <v>3.7171</v>
+        <v>1.2061</v>
       </c>
       <c r="J7" t="n">
-        <v>0.173</v>
+        <v>2.0701</v>
       </c>
       <c r="K7" t="n">
-        <v>139</v>
+        <v>57</v>
       </c>
       <c r="L7" t="n">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8901</v>
+        <v>3.2762</v>
       </c>
       <c r="N7" t="n">
-        <v>389</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.9303</v>
+        <v>3.1983</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8067</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6849</v>
+        <v>0.8317</v>
       </c>
       <c r="E8" t="n">
-        <v>2.9303</v>
+        <v>3.1983</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1479</v>
+        <v>2.7303</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7824</v>
+        <v>0.468</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1479</v>
+        <v>3.2508</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2443</v>
+        <v>3.5991</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7824</v>
+        <v>0.468</v>
       </c>
       <c r="K8" t="n">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="L8" t="n">
-        <v>222</v>
+        <v>250</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0267</v>
+        <v>4.0671</v>
       </c>
       <c r="N8" t="n">
-        <v>279</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.474</v>
+        <v>2.6224</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6811</v>
+        <v>0.722</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4789</v>
+        <v>0.5696</v>
       </c>
       <c r="E9" t="n">
-        <v>2.474</v>
+        <v>2.6224</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3125</v>
+        <v>-0.2838</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7865</v>
+        <v>2.9062</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3125</v>
+        <v>-0.2838</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3387</v>
+        <v>-0.2986</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7865</v>
+        <v>2.9062</v>
       </c>
       <c r="K9" t="n">
         <v>57</v>
@@ -851,7 +851,7 @@
         <v>222</v>
       </c>
       <c r="M9" t="n">
-        <v>2.4478</v>
+        <v>2.6076</v>
       </c>
       <c r="N9" t="n">
         <v>279</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.3139</v>
+        <v>2.3653</v>
       </c>
       <c r="C10" t="n">
-        <v>0.637</v>
+        <v>0.6512</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4066</v>
+        <v>0.4525</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3139</v>
+        <v>2.3653</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0176</v>
+        <v>2.0299</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2963</v>
+        <v>0.3354</v>
       </c>
       <c r="H10" t="n">
-        <v>2.0176</v>
+        <v>2.0299</v>
       </c>
       <c r="I10" t="n">
-        <v>2.187</v>
+        <v>2.1359</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2963</v>
+        <v>0.3354</v>
       </c>
       <c r="K10" t="n">
         <v>68</v>
@@ -897,7 +897,7 @@
         <v>138</v>
       </c>
       <c r="M10" t="n">
-        <v>2.4833</v>
+        <v>2.4713</v>
       </c>
       <c r="N10" t="n">
         <v>206</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1501</v>
+        <v>2.3437</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5919</v>
+        <v>0.6452</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3326</v>
+        <v>0.4427</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1501</v>
+        <v>2.3437</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2979</v>
+        <v>1.2732</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8522</v>
+        <v>1.0705</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2979</v>
+        <v>1.2732</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4068</v>
+        <v>1.3397</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8522</v>
+        <v>1.0705</v>
       </c>
       <c r="K11" t="n">
         <v>57</v>
@@ -943,7 +943,7 @@
         <v>222</v>
       </c>
       <c r="M11" t="n">
-        <v>2.259</v>
+        <v>2.4102</v>
       </c>
       <c r="N11" t="n">
         <v>279</v>
@@ -952,415 +952,415 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.024</v>
+        <v>2.1276</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5572</v>
+        <v>0.5857</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2757</v>
+        <v>0.3443</v>
       </c>
       <c r="E12" t="n">
-        <v>2.024</v>
+        <v>2.1276</v>
       </c>
       <c r="F12" t="n">
-        <v>1.323</v>
+        <v>1.0295</v>
       </c>
       <c r="G12" t="n">
-        <v>0.701</v>
+        <v>1.0981</v>
       </c>
       <c r="H12" t="n">
-        <v>1.323</v>
+        <v>1.0295</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4341</v>
+        <v>1.0832</v>
       </c>
       <c r="J12" t="n">
-        <v>0.701</v>
+        <v>1.0981</v>
       </c>
       <c r="K12" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="L12" t="n">
-        <v>138</v>
+        <v>222</v>
       </c>
       <c r="M12" t="n">
-        <v>2.1351</v>
+        <v>2.1813</v>
       </c>
       <c r="N12" t="n">
-        <v>206</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9954</v>
+        <v>2.1173</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5493</v>
+        <v>0.5829</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2628</v>
+        <v>0.3396</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9954</v>
+        <v>2.1173</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6096</v>
+        <v>0.4373</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3858</v>
+        <v>1.68</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6096</v>
+        <v>0.4373</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6096</v>
+        <v>0.4842</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3858</v>
+        <v>1.68</v>
       </c>
       <c r="K13" t="n">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="L13" t="n">
-        <v>138</v>
+        <v>250</v>
       </c>
       <c r="M13" t="n">
-        <v>1.9954</v>
+        <v>2.1642</v>
       </c>
       <c r="N13" t="n">
-        <v>259</v>
+        <v>389</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.9339</v>
+        <v>2.0981</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5324</v>
+        <v>0.5776</v>
       </c>
       <c r="D14" t="n">
-        <v>0.235</v>
+        <v>0.3309</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9339</v>
+        <v>2.0981</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4393</v>
+        <v>0.5851</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4946</v>
+        <v>1.513</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4393</v>
+        <v>0.5851</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5162</v>
+        <v>0.5851</v>
       </c>
       <c r="J14" t="n">
-        <v>1.4946</v>
+        <v>1.513</v>
       </c>
       <c r="K14" t="n">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="L14" t="n">
-        <v>250</v>
+        <v>138</v>
       </c>
       <c r="M14" t="n">
-        <v>2.0108</v>
+        <v>2.0981</v>
       </c>
       <c r="N14" t="n">
-        <v>389</v>
+        <v>259</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8985</v>
+        <v>2.0732</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.5708</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2191</v>
+        <v>0.3196</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8985</v>
+        <v>2.0732</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0319</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8666</v>
+        <v>2.6927</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0319</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1185</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8666</v>
+        <v>2.6927</v>
       </c>
       <c r="K15" t="n">
-        <v>57</v>
+        <v>121</v>
       </c>
       <c r="L15" t="n">
-        <v>222</v>
+        <v>138</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9851</v>
+        <v>2.0732</v>
       </c>
       <c r="N15" t="n">
-        <v>279</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.83</v>
+        <v>1.9827</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5038</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1881</v>
+        <v>0.2784</v>
       </c>
       <c r="E16" t="n">
-        <v>1.83</v>
+        <v>1.9827</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5862000000000001</v>
+        <v>1.2993</v>
       </c>
       <c r="G16" t="n">
-        <v>2.4162</v>
+        <v>0.6834</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5862000000000001</v>
+        <v>1.2993</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5862000000000001</v>
+        <v>1.3671</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4162</v>
+        <v>0.6834</v>
       </c>
       <c r="K16" t="n">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="L16" t="n">
         <v>138</v>
       </c>
       <c r="M16" t="n">
-        <v>1.83</v>
+        <v>2.0505</v>
       </c>
       <c r="N16" t="n">
-        <v>259</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JACKZ</t>
+          <t>Plopski</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2873</v>
+        <v>1.323</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3544</v>
+        <v>0.3642</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0569</v>
+        <v>-0.0219</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2873</v>
+        <v>1.323</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4009</v>
+        <v>0.741</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1136</v>
+        <v>0.582</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4009</v>
+        <v>0.741</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5185</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1136</v>
+        <v>0.582</v>
       </c>
       <c r="K17" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="L17" t="n">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4049</v>
+        <v>1.3617</v>
       </c>
       <c r="N17" t="n">
-        <v>206</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Plopski</t>
+          <t>JACKZ</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2762</v>
+        <v>1.2724</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3513</v>
+        <v>0.3503</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0619</v>
+        <v>-0.045</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2762</v>
+        <v>1.2724</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7141</v>
+        <v>1.3787</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5621</v>
+        <v>-0.1063</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7141</v>
+        <v>1.3787</v>
       </c>
       <c r="I18" t="n">
-        <v>0.774</v>
+        <v>1.4507</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5621</v>
+        <v>-0.1063</v>
       </c>
       <c r="K18" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="L18" t="n">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3361</v>
+        <v>1.3444</v>
       </c>
       <c r="N18" t="n">
-        <v>152</v>
+        <v>206</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1633</v>
+        <v>1.1509</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3203</v>
+        <v>0.3169</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1128</v>
+        <v>-0.1003</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1633</v>
+        <v>1.1509</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2669</v>
+        <v>1.4488</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1036</v>
+        <v>-0.2979</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2669</v>
+        <v>1.4488</v>
       </c>
       <c r="I19" t="n">
-        <v>2.4572</v>
+        <v>1.5244</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1036</v>
+        <v>-0.2979</v>
       </c>
       <c r="K19" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="L19" t="n">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3536</v>
+        <v>1.2265</v>
       </c>
       <c r="N19" t="n">
-        <v>206</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.161</v>
+        <v>1.1077</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3196</v>
+        <v>0.305</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1139</v>
+        <v>-0.12</v>
       </c>
       <c r="E20" t="n">
-        <v>1.161</v>
+        <v>1.1077</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4375</v>
+        <v>2.2599</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2765</v>
+        <v>-1.1522</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4375</v>
+        <v>2.2599</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5582</v>
+        <v>2.3779</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2765</v>
+        <v>-1.1522</v>
       </c>
       <c r="K20" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="L20" t="n">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2817</v>
+        <v>1.2257</v>
       </c>
       <c r="N20" t="n">
-        <v>152</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21">
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0873</v>
+        <v>1.0371</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2993</v>
+        <v>0.2855</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1472</v>
+        <v>-0.1521</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0873</v>
+        <v>1.0371</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4271</v>
+        <v>1.4214</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3398</v>
+        <v>-0.3843</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4271</v>
+        <v>1.4214</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5469</v>
+        <v>1.4956</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3398</v>
+        <v>-0.3843</v>
       </c>
       <c r="K21" t="n">
         <v>44</v>
@@ -1403,7 +1403,7 @@
         <v>108</v>
       </c>
       <c r="M21" t="n">
-        <v>1.2071</v>
+        <v>1.1113</v>
       </c>
       <c r="N21" t="n">
         <v>152</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9183</v>
+        <v>0.8418</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2528</v>
+        <v>0.2318</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2234</v>
+        <v>-0.241</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9183</v>
+        <v>0.8418</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5065</v>
+        <v>1.4735</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5881999999999999</v>
+        <v>-0.6317</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5065</v>
+        <v>1.4735</v>
       </c>
       <c r="I22" t="n">
-        <v>1.633</v>
+        <v>1.5504</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5881999999999999</v>
+        <v>-0.6317</v>
       </c>
       <c r="K22" t="n">
         <v>44</v>
@@ -1449,7 +1449,7 @@
         <v>108</v>
       </c>
       <c r="M22" t="n">
-        <v>1.0448</v>
+        <v>0.9187</v>
       </c>
       <c r="N22" t="n">
         <v>152</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.615</v>
+        <v>0.7774</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1693</v>
+        <v>0.214</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3604</v>
+        <v>-0.2703</v>
       </c>
       <c r="E23" t="n">
-        <v>0.615</v>
+        <v>0.7774</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3957</v>
+        <v>-0.4101</v>
       </c>
       <c r="G23" t="n">
-        <v>1.0107</v>
+        <v>1.1875</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3957</v>
+        <v>-0.4101</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4649</v>
+        <v>-0.454</v>
       </c>
       <c r="J23" t="n">
-        <v>1.0107</v>
+        <v>1.1875</v>
       </c>
       <c r="K23" t="n">
         <v>139</v>
@@ -1495,7 +1495,7 @@
         <v>250</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5458</v>
+        <v>0.7335</v>
       </c>
       <c r="N23" t="n">
         <v>389</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5571</v>
+        <v>0.7027</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1534</v>
+        <v>0.1935</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3865</v>
+        <v>-0.3043</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5571</v>
+        <v>0.7027</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2867</v>
+        <v>0.26</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2704</v>
+        <v>0.4427</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2867</v>
+        <v>0.26</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2867</v>
+        <v>0.26</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2704</v>
+        <v>0.4427</v>
       </c>
       <c r="K24" t="n">
         <v>121</v>
@@ -1541,7 +1541,7 @@
         <v>138</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5570999999999999</v>
+        <v>0.7027</v>
       </c>
       <c r="N24" t="n">
         <v>259</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3027</v>
+        <v>0.2626</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0833</v>
+        <v>0.0723</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5014</v>
+        <v>-0.5047</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3027</v>
+        <v>0.2626</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1172</v>
+        <v>-0.1373</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4199</v>
+        <v>0.3999</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1172</v>
+        <v>-0.1373</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1172</v>
+        <v>-0.1373</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4199</v>
+        <v>0.3999</v>
       </c>
       <c r="K25" t="n">
         <v>44</v>
@@ -1587,7 +1587,7 @@
         <v>77</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3027</v>
+        <v>0.2625999999999999</v>
       </c>
       <c r="N25" t="n">
         <v>121</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2128</v>
+        <v>0.231</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0586</v>
+        <v>0.0636</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5419</v>
+        <v>-0.519</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2128</v>
+        <v>0.231</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0395</v>
+        <v>0.0103</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1733</v>
+        <v>0.2207</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0395</v>
+        <v>0.0103</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0395</v>
+        <v>0.0103</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1733</v>
+        <v>0.2207</v>
       </c>
       <c r="K26" t="n">
         <v>44</v>
@@ -1633,7 +1633,7 @@
         <v>77</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2128</v>
+        <v>0.231</v>
       </c>
       <c r="N26" t="n">
         <v>121</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1073</v>
+        <v>0.1855</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0295</v>
+        <v>0.0511</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5896</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1073</v>
+        <v>0.1855</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.6442</v>
+        <v>-0.6833</v>
       </c>
       <c r="G27" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.8688</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.6442</v>
+        <v>-0.6833</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.6442</v>
+        <v>-0.6833</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.8688</v>
       </c>
       <c r="K27" t="n">
         <v>121</v>
@@ -1679,7 +1679,7 @@
         <v>138</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1073</v>
+        <v>0.1855</v>
       </c>
       <c r="N27" t="n">
         <v>259</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0413</v>
+        <v>-0.0476</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0114</v>
+        <v>-0.0131</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6567</v>
+        <v>-0.6459</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0413</v>
+        <v>-0.0476</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.4115</v>
+        <v>-0.4304</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3702</v>
+        <v>0.3828</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.4115</v>
+        <v>-0.4304</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.4284</v>
+        <v>-0.4415</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3702</v>
+        <v>0.3828</v>
       </c>
       <c r="K28" t="n">
         <v>68</v>
@@ -1725,7 +1725,7 @@
         <v>86</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.05820000000000003</v>
+        <v>-0.05870000000000003</v>
       </c>
       <c r="N28" t="n">
         <v>154</v>
@@ -1734,81 +1734,81 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jamppi</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2043</v>
+        <v>-0.2236</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0562</v>
+        <v>-0.0616</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7302</v>
+        <v>-0.726</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2043</v>
+        <v>-0.2236</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1464</v>
+        <v>0.5195</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0579</v>
+        <v>-0.7431</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1464</v>
+        <v>0.5195</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1524</v>
+        <v>0.5329</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.0579</v>
+        <v>-0.7431</v>
       </c>
       <c r="K29" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="L29" t="n">
-        <v>86</v>
+        <v>193</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2103</v>
+        <v>-0.2101999999999999</v>
       </c>
       <c r="N29" t="n">
-        <v>154</v>
+        <v>268</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>Jamppi</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2842</v>
+        <v>-0.2506</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7663</v>
+        <v>-0.7383</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2842</v>
+        <v>-0.2506</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1673</v>
+        <v>-0.1678</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.1169</v>
+        <v>-0.0828</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1673</v>
+        <v>-0.1678</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1742</v>
+        <v>-0.1721</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.1169</v>
+        <v>-0.0828</v>
       </c>
       <c r="K30" t="n">
         <v>68</v>
@@ -1817,7 +1817,7 @@
         <v>86</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2911</v>
+        <v>-0.2549</v>
       </c>
       <c r="N30" t="n">
         <v>154</v>
@@ -1826,35 +1826,35 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3031</v>
+        <v>-0.278</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0834</v>
+        <v>-0.0765</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7748</v>
+        <v>-0.7508</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3031</v>
+        <v>-0.278</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5738</v>
+        <v>-0.3214</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.8769</v>
+        <v>0.0434</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5738</v>
+        <v>-0.3214</v>
       </c>
       <c r="I31" t="n">
-        <v>0.5974</v>
+        <v>-0.3297</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.8769</v>
+        <v>0.0434</v>
       </c>
       <c r="K31" t="n">
         <v>75</v>
@@ -1863,7 +1863,7 @@
         <v>193</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2795</v>
+        <v>-0.2863</v>
       </c>
       <c r="N31" t="n">
         <v>268</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.356</v>
+        <v>-0.3309</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.098</v>
+        <v>-0.0911</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7987</v>
+        <v>-0.7748</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.356</v>
+        <v>-0.3309</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1527</v>
+        <v>-0.1915</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.2033</v>
+        <v>-0.1394</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1527</v>
+        <v>-0.1915</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1527</v>
+        <v>-0.1964</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.2033</v>
+        <v>-0.1394</v>
       </c>
       <c r="K32" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="L32" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.356</v>
+        <v>-0.3358</v>
       </c>
       <c r="N32" t="n">
-        <v>121</v>
+        <v>154</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4414</v>
+        <v>-0.4062</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1215</v>
+        <v>-0.1118</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8373</v>
+        <v>-0.8091</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4414</v>
+        <v>-0.4062</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.301</v>
+        <v>-0.1787</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.1404</v>
+        <v>-0.2275</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.301</v>
+        <v>-0.1787</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3134</v>
+        <v>-0.1787</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.1404</v>
+        <v>-0.2275</v>
       </c>
       <c r="K33" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="L33" t="n">
-        <v>193</v>
+        <v>77</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4538</v>
+        <v>-0.4062</v>
       </c>
       <c r="N33" t="n">
-        <v>268</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34">
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5016</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1381</v>
+        <v>-0.1489</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8645</v>
+        <v>-0.8704</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5016</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4164</v>
+        <v>0.4039</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.918</v>
+        <v>-0.9447</v>
       </c>
       <c r="H34" t="n">
-        <v>0.4164</v>
+        <v>0.4039</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4335</v>
+        <v>0.4143</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.918</v>
+        <v>-0.9447</v>
       </c>
       <c r="K34" t="n">
         <v>68</v>
@@ -2001,7 +2001,7 @@
         <v>86</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4845</v>
+        <v>-0.5304</v>
       </c>
       <c r="N34" t="n">
         <v>154</v>
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6399</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1762</v>
+        <v>-0.1886</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9268999999999999</v>
+        <v>-0.9360000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6399</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.1151</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.553</v>
+        <v>-0.5699</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.1151</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0905</v>
+        <v>-0.1181</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.553</v>
+        <v>-0.5699</v>
       </c>
       <c r="K35" t="n">
         <v>68</v>
@@ -2047,7 +2047,7 @@
         <v>86</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6435000000000001</v>
+        <v>-0.6879999999999999</v>
       </c>
       <c r="N35" t="n">
         <v>154</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6523</v>
+        <v>-0.7255</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1796</v>
+        <v>-0.1997</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9325</v>
+        <v>-0.9545</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6523</v>
+        <v>-0.7255</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4856</v>
+        <v>0.4759</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.1379</v>
+        <v>-1.2014</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4856</v>
+        <v>0.4759</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5264</v>
+        <v>0.5007</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.1379</v>
+        <v>-1.2014</v>
       </c>
       <c r="K36" t="n">
         <v>44</v>
@@ -2093,7 +2093,7 @@
         <v>108</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6114999999999999</v>
+        <v>-0.7007</v>
       </c>
       <c r="N36" t="n">
         <v>152</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0167</v>
+        <v>-1.0854</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2799</v>
+        <v>-0.2988</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.097</v>
+        <v>-1.1183</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0167</v>
+        <v>-1.0854</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.3307</v>
+        <v>-0.3591</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.6860000000000001</v>
+        <v>-0.7262999999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.3307</v>
+        <v>-0.3591</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.3307</v>
+        <v>-0.3591</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.6860000000000001</v>
+        <v>-0.7262999999999999</v>
       </c>
       <c r="K37" t="n">
         <v>44</v>
@@ -2139,7 +2139,7 @@
         <v>77</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.0167</v>
+        <v>-1.0854</v>
       </c>
       <c r="N37" t="n">
         <v>121</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1479</v>
+        <v>-1.1829</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.316</v>
+        <v>-0.3257</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1562</v>
+        <v>-1.1627</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1479</v>
+        <v>-1.1829</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.6388</v>
+        <v>-0.66</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.5091</v>
+        <v>-0.5229</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.6388</v>
+        <v>-0.66</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.6388</v>
+        <v>-0.66</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.5091</v>
+        <v>-0.5229</v>
       </c>
       <c r="K38" t="n">
         <v>44</v>
@@ -2185,7 +2185,7 @@
         <v>77</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.1479</v>
+        <v>-1.1829</v>
       </c>
       <c r="N38" t="n">
         <v>121</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3344</v>
+        <v>-1.3583</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3674</v>
+        <v>-0.3739</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2404</v>
+        <v>-1.2425</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3344</v>
+        <v>-1.3583</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.6335</v>
+        <v>-0.609</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.7009</v>
+        <v>-0.7493</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.6335</v>
+        <v>-0.609</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.6867</v>
+        <v>-0.6408</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.7009</v>
+        <v>-0.7493</v>
       </c>
       <c r="K39" t="n">
         <v>68</v>
@@ -2231,7 +2231,7 @@
         <v>138</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.3876</v>
+        <v>-1.3901</v>
       </c>
       <c r="N39" t="n">
         <v>206</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.9054</v>
+        <v>-1.7889</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5246</v>
+        <v>-0.4925</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4982</v>
+        <v>-1.4385</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.9054</v>
+        <v>-1.7889</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.9176</v>
+        <v>-0.9599</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.9878</v>
+        <v>-0.829</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.9176</v>
+        <v>-0.9599</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.9553</v>
+        <v>-0.9846</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.9878</v>
+        <v>-0.829</v>
       </c>
       <c r="K40" t="n">
         <v>75</v>
@@ -2277,7 +2277,7 @@
         <v>193</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.9431</v>
+        <v>-1.8136</v>
       </c>
       <c r="N40" t="n">
         <v>268</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.9414</v>
+        <v>-1.9501</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5345</v>
+        <v>-0.5369</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5145</v>
+        <v>-1.5119</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.9414</v>
+        <v>-1.9501</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.2144</v>
+        <v>-1.2355</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.727</v>
+        <v>-0.7146</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.2144</v>
+        <v>-1.2355</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.4268</v>
+        <v>-1.3679</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.727</v>
+        <v>-0.7146</v>
       </c>
       <c r="K41" t="n">
         <v>139</v>
@@ -2323,7 +2323,7 @@
         <v>250</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.1538</v>
+        <v>-2.0825</v>
       </c>
       <c r="N41" t="n">
         <v>389</v>
@@ -2429,10 +2429,10 @@
         <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2055</v>
+        <v>0.1854</v>
       </c>
       <c r="J2" t="n">
-        <v>3.699</v>
+        <v>3.3372</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.82</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1691</v>
+        <v>-0.1939</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.0438</v>
+        <v>-3.4902</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.49</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4858</v>
+        <v>-0.4978</v>
       </c>
       <c r="J4" t="n">
-        <v>-8.744400000000001</v>
+        <v>-8.9604</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.49</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4858</v>
+        <v>-0.4978</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.744400000000001</v>
+        <v>-8.9604</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.47</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5046</v>
+        <v>-0.5154</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.082800000000001</v>
+        <v>-9.277200000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>2.01</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0522</v>
+        <v>1.0606</v>
       </c>
       <c r="J7" t="n">
-        <v>18.9396</v>
+        <v>19.0908</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.51</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5971</v>
+        <v>0.6069</v>
       </c>
       <c r="J8" t="n">
-        <v>10.7478</v>
+        <v>10.9242</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.3</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3756</v>
+        <v>0.3956</v>
       </c>
       <c r="J9" t="n">
-        <v>6.7608</v>
+        <v>7.1208</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.29</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3641</v>
+        <v>0.3845</v>
       </c>
       <c r="J10" t="n">
-        <v>6.5538</v>
+        <v>6.921</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.12</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1522</v>
+        <v>0.1771</v>
       </c>
       <c r="J11" t="n">
-        <v>2.7396</v>
+        <v>3.1878</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.26</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7131</v>
+        <v>0.6796</v>
       </c>
       <c r="J12" t="n">
-        <v>24.9585</v>
+        <v>23.786</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.17</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4946</v>
+        <v>0.4842</v>
       </c>
       <c r="J13" t="n">
-        <v>17.311</v>
+        <v>16.947</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.15</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4454</v>
+        <v>0.4392</v>
       </c>
       <c r="J14" t="n">
-        <v>15.589</v>
+        <v>15.372</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.1</v>
       </c>
       <c r="I15" t="n">
-        <v>0.313</v>
+        <v>0.3175</v>
       </c>
       <c r="J15" t="n">
-        <v>10.955</v>
+        <v>11.1125</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.09</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2847</v>
+        <v>0.2912</v>
       </c>
       <c r="J16" t="n">
-        <v>9.964499999999999</v>
+        <v>10.192</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.58</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0832</v>
+        <v>1.0563</v>
       </c>
       <c r="J17" t="n">
-        <v>37.912</v>
+        <v>36.9705</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.89</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1352</v>
+        <v>-0.1505</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.732</v>
+        <v>-5.2675</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.84</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1873</v>
+        <v>-0.2033</v>
       </c>
       <c r="J19" t="n">
-        <v>-6.5555</v>
+        <v>-7.1155</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.76</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2671</v>
+        <v>-0.2824</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.3485</v>
+        <v>-9.884</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.46</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5461</v>
+        <v>-0.5495</v>
       </c>
       <c r="J21" t="n">
-        <v>-19.1135</v>
+        <v>-19.2325</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.67</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3829</v>
+        <v>1.4771</v>
       </c>
       <c r="J22" t="n">
-        <v>38.7212</v>
+        <v>41.3588</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.25</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7005</v>
+        <v>0.6663</v>
       </c>
       <c r="J23" t="n">
-        <v>19.614</v>
+        <v>18.6564</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.01</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0272</v>
+        <v>0.0408</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7616000000000001</v>
+        <v>1.1424</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.85</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5221</v>
+        <v>-0.4924</v>
       </c>
       <c r="J25" t="n">
-        <v>-14.6188</v>
+        <v>-13.7872</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.5877</v>
       </c>
       <c r="J26" t="n">
-        <v>-17.598</v>
+        <v>-16.4556</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.26</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5393</v>
+        <v>0.5278</v>
       </c>
       <c r="J27" t="n">
-        <v>15.1004</v>
+        <v>14.7784</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.13</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3005</v>
+        <v>0.3055</v>
       </c>
       <c r="J28" t="n">
-        <v>8.414</v>
+        <v>8.554</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.11</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2612</v>
+        <v>0.268</v>
       </c>
       <c r="J29" t="n">
-        <v>7.3136</v>
+        <v>7.504</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.86</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.18</v>
+        <v>-0.1929</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.04</v>
+        <v>-5.4012</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.75</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2908</v>
+        <v>-0.3029</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.1424</v>
+        <v>-8.481199999999999</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.24</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4995</v>
+        <v>0.4921</v>
       </c>
       <c r="J32" t="n">
-        <v>16.983</v>
+        <v>16.7314</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.03</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0872</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>2.9648</v>
+        <v>3.2878</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.99</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0236</v>
+        <v>-0.0275</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.8024</v>
+        <v>-0.9350000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.96</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0668</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.2712</v>
+        <v>-2.5602</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.96</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.0668</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>-2.2712</v>
+        <v>-2.5602</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.36</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9912</v>
+        <v>0.9222</v>
       </c>
       <c r="J37" t="n">
-        <v>33.7008</v>
+        <v>31.3548</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.02</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0882</v>
+        <v>0.0959</v>
       </c>
       <c r="J38" t="n">
-        <v>2.9988</v>
+        <v>3.2606</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.01</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0481</v>
+        <v>0.0552</v>
       </c>
       <c r="J39" t="n">
-        <v>1.6354</v>
+        <v>1.8768</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.96</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1726</v>
+        <v>-0.1744</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.8684</v>
+        <v>-5.9296</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6046</v>
+        <v>-0.5709</v>
       </c>
       <c r="J41" t="n">
-        <v>-20.5564</v>
+        <v>-19.4106</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.27</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5411</v>
+        <v>0.5323</v>
       </c>
       <c r="J42" t="n">
-        <v>16.233</v>
+        <v>15.969</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.26</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5239</v>
+        <v>0.5165</v>
       </c>
       <c r="J43" t="n">
-        <v>15.717</v>
+        <v>15.495</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.05</v>
       </c>
       <c r="I44" t="n">
-        <v>0.129</v>
+        <v>0.1406</v>
       </c>
       <c r="J44" t="n">
-        <v>3.87</v>
+        <v>4.218</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.95</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0833</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>-2.499</v>
+        <v>-2.754</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.83</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2167</v>
+        <v>-0.2285</v>
       </c>
       <c r="J46" t="n">
-        <v>-6.501</v>
+        <v>-6.855</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.26</v>
       </c>
       <c r="I47" t="n">
-        <v>0.75</v>
+        <v>0.7053</v>
       </c>
       <c r="J47" t="n">
-        <v>22.5</v>
+        <v>21.159</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.17</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5221</v>
+        <v>0.5031</v>
       </c>
       <c r="J48" t="n">
-        <v>15.663</v>
+        <v>15.093</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.06</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2164</v>
+        <v>0.2218</v>
       </c>
       <c r="J49" t="n">
-        <v>6.492</v>
+        <v>6.654</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.89</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3925</v>
+        <v>-0.3787</v>
       </c>
       <c r="J50" t="n">
-        <v>-11.775</v>
+        <v>-11.361</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.88</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4209</v>
+        <v>-0.4045</v>
       </c>
       <c r="J51" t="n">
-        <v>-12.627</v>
+        <v>-12.135</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.47</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6202</v>
+        <v>0.617</v>
       </c>
       <c r="J52" t="n">
-        <v>16.1252</v>
+        <v>16.042</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.06</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1071</v>
+        <v>0.1204</v>
       </c>
       <c r="J53" t="n">
-        <v>2.7846</v>
+        <v>3.1304</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.99</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.0275</v>
+        <v>-0.0305</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.715</v>
+        <v>-0.793</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0961</v>
+        <v>-0.1052</v>
       </c>
       <c r="J55" t="n">
-        <v>-2.4986</v>
+        <v>-2.7352</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.92</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1199</v>
+        <v>-0.13</v>
       </c>
       <c r="J56" t="n">
-        <v>-3.1174</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5214</v>
+        <v>0.5141</v>
       </c>
       <c r="J57" t="n">
-        <v>13.5564</v>
+        <v>13.3666</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.32</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4952</v>
+        <v>0.4898</v>
       </c>
       <c r="J58" t="n">
-        <v>12.8752</v>
+        <v>12.7348</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.17</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2903</v>
+        <v>0.297</v>
       </c>
       <c r="J59" t="n">
-        <v>7.5478</v>
+        <v>7.722</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.67</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3658</v>
+        <v>-0.3761</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.5108</v>
+        <v>-9.778600000000001</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4667</v>
+        <v>-0.4728</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.1342</v>
+        <v>-12.2928</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.22</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5204</v>
+        <v>0.5007</v>
       </c>
       <c r="J62" t="n">
-        <v>11.4488</v>
+        <v>11.0154</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.08</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2386</v>
+        <v>0.2369</v>
       </c>
       <c r="J63" t="n">
-        <v>5.2492</v>
+        <v>5.2118</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.79</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2353</v>
+        <v>-0.2516</v>
       </c>
       <c r="J64" t="n">
-        <v>-5.1766</v>
+        <v>-5.5352</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.77</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.255</v>
+        <v>-0.271</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.61</v>
+        <v>-5.962</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.58</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.435</v>
+        <v>-0.4448</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.57</v>
+        <v>-9.785600000000001</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.7</v>
       </c>
       <c r="I67" t="n">
-        <v>1.3745</v>
+        <v>1.3552</v>
       </c>
       <c r="J67" t="n">
-        <v>30.239</v>
+        <v>29.8144</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.37</v>
       </c>
       <c r="I68" t="n">
-        <v>0.9328</v>
+        <v>0.8792</v>
       </c>
       <c r="J68" t="n">
-        <v>20.5216</v>
+        <v>19.3424</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.24</v>
       </c>
       <c r="I69" t="n">
-        <v>0.6445</v>
+        <v>0.6231</v>
       </c>
       <c r="J69" t="n">
-        <v>14.179</v>
+        <v>13.7082</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.1</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2879</v>
+        <v>0.3001</v>
       </c>
       <c r="J70" t="n">
-        <v>6.3338</v>
+        <v>6.6022</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.9</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4184</v>
+        <v>-0.3906</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.204800000000001</v>
+        <v>-8.5932</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.44</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8602</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="J72" t="n">
-        <v>23.2254</v>
+        <v>22.005</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.09</v>
       </c>
       <c r="I73" t="n">
-        <v>0.2288</v>
+        <v>0.2348</v>
       </c>
       <c r="J73" t="n">
-        <v>6.1776</v>
+        <v>6.3396</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.91</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1217</v>
+        <v>-0.1344</v>
       </c>
       <c r="J74" t="n">
-        <v>-3.2859</v>
+        <v>-3.6288</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.87</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1655</v>
+        <v>-0.1791</v>
       </c>
       <c r="J75" t="n">
-        <v>-4.4685</v>
+        <v>-4.8357</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.63</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4004</v>
+        <v>-0.4098</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.8108</v>
+        <v>-11.0646</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.32</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8831</v>
+        <v>0.8237</v>
       </c>
       <c r="J77" t="n">
-        <v>23.8437</v>
+        <v>22.2399</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.22</v>
       </c>
       <c r="I78" t="n">
-        <v>0.6398</v>
+        <v>0.6101</v>
       </c>
       <c r="J78" t="n">
-        <v>17.2746</v>
+        <v>16.4727</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.98</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1134</v>
+        <v>-0.1131</v>
       </c>
       <c r="J79" t="n">
-        <v>-3.0618</v>
+        <v>-3.0537</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2509</v>
+        <v>-0.2456</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.7743</v>
+        <v>-6.6312</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2509</v>
+        <v>-0.2456</v>
       </c>
       <c r="J81" t="n">
-        <v>-6.7743</v>
+        <v>-6.6312</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.44</v>
       </c>
       <c r="I82" t="n">
-        <v>1.0645</v>
+        <v>1.0176</v>
       </c>
       <c r="J82" t="n">
-        <v>28.7415</v>
+        <v>27.4752</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.3</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7941</v>
+        <v>0.7533</v>
       </c>
       <c r="J83" t="n">
-        <v>21.4407</v>
+        <v>20.3391</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.22</v>
       </c>
       <c r="I84" t="n">
-        <v>0.6074000000000001</v>
+        <v>0.5877</v>
       </c>
       <c r="J84" t="n">
-        <v>16.3998</v>
+        <v>15.8679</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.04</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1197</v>
+        <v>0.1381</v>
       </c>
       <c r="J85" t="n">
-        <v>3.2319</v>
+        <v>3.7287</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.99</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.1031</v>
+        <v>-0.093</v>
       </c>
       <c r="J86" t="n">
-        <v>-2.7837</v>
+        <v>-2.511</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.17</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4362</v>
+        <v>0.4209</v>
       </c>
       <c r="J87" t="n">
-        <v>11.7774</v>
+        <v>11.3643</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.95</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0615</v>
+        <v>-0.0751</v>
       </c>
       <c r="J88" t="n">
-        <v>-1.6605</v>
+        <v>-2.0277</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.84</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1824</v>
+        <v>-0.1996</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.9248</v>
+        <v>-5.3892</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.72</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3</v>
+        <v>-0.3157</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.1</v>
+        <v>-8.523899999999999</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.63</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3852</v>
+        <v>-0.3979</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.4004</v>
+        <v>-10.7433</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.21</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6127</v>
+        <v>0.5864</v>
       </c>
       <c r="J92" t="n">
-        <v>18.381</v>
+        <v>17.592</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.17</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5111</v>
+        <v>0.4955</v>
       </c>
       <c r="J93" t="n">
-        <v>15.333</v>
+        <v>14.865</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.13</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4063</v>
+        <v>0.4005</v>
       </c>
       <c r="J94" t="n">
-        <v>12.189</v>
+        <v>12.015</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.05</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1798</v>
+        <v>0.1885</v>
       </c>
       <c r="J95" t="n">
-        <v>5.394</v>
+        <v>5.655</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.87</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4584</v>
+        <v>-0.4367</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.752</v>
+        <v>-13.101</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.24</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5245</v>
+        <v>0.5104</v>
       </c>
       <c r="J97" t="n">
-        <v>15.735</v>
+        <v>15.312</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.08</v>
       </c>
       <c r="I98" t="n">
-        <v>0.214</v>
+        <v>0.219</v>
       </c>
       <c r="J98" t="n">
-        <v>6.42</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.88</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1521</v>
+        <v>-0.1661</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.563</v>
+        <v>-4.983</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.86</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1733</v>
+        <v>-0.1877</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.199</v>
+        <v>-5.631</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.76</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2743</v>
+        <v>-0.2881</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.228999999999999</v>
+        <v>-8.643000000000001</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.08</v>
       </c>
       <c r="I102" t="n">
-        <v>0.2665</v>
+        <v>0.2574</v>
       </c>
       <c r="J102" t="n">
-        <v>6.6625</v>
+        <v>6.435</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.2079</v>
+        <v>-0.2261</v>
       </c>
       <c r="J103" t="n">
-        <v>-5.1975</v>
+        <v>-5.6525</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.76</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2561</v>
+        <v>-0.2739</v>
       </c>
       <c r="J104" t="n">
-        <v>-6.4025</v>
+        <v>-6.8475</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.74</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2754</v>
+        <v>-0.2928</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.885</v>
+        <v>-7.32</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.72</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2946</v>
+        <v>-0.3115</v>
       </c>
       <c r="J106" t="n">
-        <v>-7.365</v>
+        <v>-7.7875</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.63</v>
       </c>
       <c r="I107" t="n">
-        <v>1.0361</v>
+        <v>1.1358</v>
       </c>
       <c r="J107" t="n">
-        <v>25.9025</v>
+        <v>28.395</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.27</v>
       </c>
       <c r="I108" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.6276</v>
       </c>
       <c r="J108" t="n">
-        <v>14.15</v>
+        <v>15.69</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.21</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4824</v>
+        <v>0.5342</v>
       </c>
       <c r="J109" t="n">
-        <v>12.06</v>
+        <v>13.355</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2791</v>
+        <v>-0.2653</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.9775</v>
+        <v>-6.6325</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.88</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.457</v>
+        <v>-0.4299</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.425</v>
+        <v>-10.7475</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.15</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3431</v>
+        <v>0.3505</v>
       </c>
       <c r="J112" t="n">
-        <v>9.9499</v>
+        <v>10.1645</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.13</v>
       </c>
       <c r="I113" t="n">
-        <v>0.3114</v>
+        <v>0.3137</v>
       </c>
       <c r="J113" t="n">
-        <v>9.0306</v>
+        <v>9.097300000000001</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.06</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1663</v>
+        <v>0.1734</v>
       </c>
       <c r="J114" t="n">
-        <v>4.8227</v>
+        <v>5.0286</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.83</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2063</v>
+        <v>-0.2204</v>
       </c>
       <c r="J115" t="n">
-        <v>-5.9827</v>
+        <v>-6.3916</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.73</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3053</v>
+        <v>-0.318</v>
       </c>
       <c r="J116" t="n">
-        <v>-8.8537</v>
+        <v>-9.222</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.73</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1722</v>
+        <v>1.2775</v>
       </c>
       <c r="J117" t="n">
-        <v>33.9938</v>
+        <v>37.0475</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.07</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2265</v>
+        <v>0.2367</v>
       </c>
       <c r="J118" t="n">
-        <v>6.5685</v>
+        <v>6.8643</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.02</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0595</v>
+        <v>0.0761</v>
       </c>
       <c r="J119" t="n">
-        <v>1.7255</v>
+        <v>2.2069</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.97</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1697</v>
+        <v>-0.1629</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.9213</v>
+        <v>-4.7241</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.97</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1697</v>
+        <v>-0.1629</v>
       </c>
       <c r="J121" t="n">
-        <v>-4.9213</v>
+        <v>-4.7241</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.1</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3382</v>
+        <v>0.3241</v>
       </c>
       <c r="J122" t="n">
-        <v>6.4258</v>
+        <v>6.1579</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.77</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.2403</v>
+        <v>-0.2597</v>
       </c>
       <c r="J123" t="n">
-        <v>-4.5657</v>
+        <v>-4.9343</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.75</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2584</v>
+        <v>-0.2777</v>
       </c>
       <c r="J124" t="n">
-        <v>-4.9096</v>
+        <v>-5.2763</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.6</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3991</v>
+        <v>-0.4135</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.5829</v>
+        <v>-7.8565</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.59</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4084</v>
+        <v>-0.4224</v>
       </c>
       <c r="J126" t="n">
-        <v>-7.7596</v>
+        <v>-8.025600000000001</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.74</v>
       </c>
       <c r="I127" t="n">
-        <v>1.121</v>
+        <v>1.2342</v>
       </c>
       <c r="J127" t="n">
-        <v>21.299</v>
+        <v>23.4498</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.57</v>
       </c>
       <c r="I128" t="n">
-        <v>0.9188</v>
+        <v>1.0188</v>
       </c>
       <c r="J128" t="n">
-        <v>17.4572</v>
+        <v>19.3572</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.37</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="J129" t="n">
-        <v>12.8231</v>
+        <v>14.3165</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.29</v>
       </c>
       <c r="I130" t="n">
-        <v>0.5723</v>
+        <v>0.6399</v>
       </c>
       <c r="J130" t="n">
-        <v>10.8737</v>
+        <v>12.1581</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.9</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.443</v>
+        <v>-0.4079</v>
       </c>
       <c r="J131" t="n">
-        <v>-8.417</v>
+        <v>-7.7501</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.43</v>
       </c>
       <c r="I132" t="n">
-        <v>0.4731</v>
+        <v>0.5365</v>
       </c>
       <c r="J132" t="n">
-        <v>12.7737</v>
+        <v>14.4855</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.21</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3069</v>
+        <v>0.321</v>
       </c>
       <c r="J133" t="n">
-        <v>8.286300000000001</v>
+        <v>8.667</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.03</v>
       </c>
       <c r="I134" t="n">
-        <v>0.056</v>
+        <v>0.0674</v>
       </c>
       <c r="J134" t="n">
-        <v>1.512</v>
+        <v>1.8198</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.98</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0449</v>
+        <v>-0.0495</v>
       </c>
       <c r="J135" t="n">
-        <v>-1.2123</v>
+        <v>-1.3365</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2392</v>
+        <v>-0.2504</v>
       </c>
       <c r="J136" t="n">
-        <v>-6.4584</v>
+        <v>-6.7608</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.08</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1686</v>
+        <v>0.1752</v>
       </c>
       <c r="J137" t="n">
-        <v>4.5522</v>
+        <v>4.7304</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.07</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1519</v>
+        <v>0.1586</v>
       </c>
       <c r="J138" t="n">
-        <v>4.1013</v>
+        <v>4.2822</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.01</v>
       </c>
       <c r="I139" t="n">
-        <v>0.0374</v>
+        <v>0.0402</v>
       </c>
       <c r="J139" t="n">
-        <v>1.0098</v>
+        <v>1.0854</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.91</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1169</v>
+        <v>-0.1307</v>
       </c>
       <c r="J140" t="n">
-        <v>-3.1563</v>
+        <v>-3.5289</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.64</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3859</v>
+        <v>-0.3968</v>
       </c>
       <c r="J141" t="n">
-        <v>-10.4193</v>
+        <v>-10.7136</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.03</v>
       </c>
       <c r="I142" t="n">
-        <v>0.101</v>
+        <v>0.1066</v>
       </c>
       <c r="J142" t="n">
-        <v>2.929</v>
+        <v>3.0914</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.02</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0746</v>
+        <v>0.0795</v>
       </c>
       <c r="J143" t="n">
-        <v>2.1634</v>
+        <v>2.3055</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.95</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.088</v>
+        <v>-2.4099</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0839</v>
+        <v>-0.0958</v>
       </c>
       <c r="J145" t="n">
-        <v>-2.4331</v>
+        <v>-2.7782</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.84</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1932</v>
+        <v>-0.2079</v>
       </c>
       <c r="J146" t="n">
-        <v>-5.6028</v>
+        <v>-6.0291</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.5</v>
       </c>
       <c r="I147" t="n">
-        <v>0.8983</v>
+        <v>0.984</v>
       </c>
       <c r="J147" t="n">
-        <v>26.0507</v>
+        <v>28.536</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.14</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3914</v>
+        <v>0.4224</v>
       </c>
       <c r="J148" t="n">
-        <v>11.3506</v>
+        <v>12.2496</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.07</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2399</v>
+        <v>0.2458</v>
       </c>
       <c r="J149" t="n">
-        <v>6.9571</v>
+        <v>7.1282</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.89</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4038</v>
+        <v>-0.3866</v>
       </c>
       <c r="J150" t="n">
-        <v>-11.7102</v>
+        <v>-11.2114</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.86</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4877</v>
+        <v>-0.4628</v>
       </c>
       <c r="J151" t="n">
-        <v>-14.1433</v>
+        <v>-13.4212</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.26</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4694</v>
+        <v>0.5179</v>
       </c>
       <c r="J152" t="n">
-        <v>12.6738</v>
+        <v>13.9833</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.96</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0599</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J153" t="n">
-        <v>-1.6173</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.93</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0956</v>
+        <v>-0.1081</v>
       </c>
       <c r="J154" t="n">
-        <v>-2.5812</v>
+        <v>-2.9187</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.89</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1404</v>
+        <v>-0.1544</v>
       </c>
       <c r="J155" t="n">
-        <v>-3.7908</v>
+        <v>-4.1688</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.74</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2928</v>
+        <v>-0.3063</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.9056</v>
+        <v>-8.270099999999999</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.34</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6777</v>
+        <v>0.747</v>
       </c>
       <c r="J157" t="n">
-        <v>18.2979</v>
+        <v>20.169</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.25</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5515</v>
+        <v>0.6083</v>
       </c>
       <c r="J158" t="n">
-        <v>14.8905</v>
+        <v>16.4241</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.08</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2655</v>
+        <v>0.2709</v>
       </c>
       <c r="J159" t="n">
-        <v>7.1685</v>
+        <v>7.3143</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.04</v>
       </c>
       <c r="I160" t="n">
-        <v>0.1415</v>
+        <v>0.1533</v>
       </c>
       <c r="J160" t="n">
-        <v>3.8205</v>
+        <v>4.1391</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.84</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5469000000000001</v>
+        <v>-0.5152</v>
       </c>
       <c r="J161" t="n">
-        <v>-14.7663</v>
+        <v>-13.9104</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.1</v>
       </c>
       <c r="I162" t="n">
-        <v>0.2628</v>
+        <v>0.2644</v>
       </c>
       <c r="J162" t="n">
-        <v>6.57</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.95</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0712</v>
+        <v>-0.0825</v>
       </c>
       <c r="J163" t="n">
-        <v>-1.78</v>
+        <v>-2.0625</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.083</v>
+        <v>-0.0951</v>
       </c>
       <c r="J164" t="n">
-        <v>-2.075</v>
+        <v>-2.3775</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.93</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.0944</v>
+        <v>-0.1072</v>
       </c>
       <c r="J165" t="n">
-        <v>-2.36</v>
+        <v>-2.68</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.79</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.242</v>
+        <v>-0.2569</v>
       </c>
       <c r="J166" t="n">
-        <v>-6.05</v>
+        <v>-6.4225</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.49</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8662</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="J167" t="n">
-        <v>21.655</v>
+        <v>23.8275</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.16</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4139</v>
+        <v>0.4548</v>
       </c>
       <c r="J168" t="n">
-        <v>10.3475</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.08</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2553</v>
+        <v>0.2639</v>
       </c>
       <c r="J169" t="n">
-        <v>6.3825</v>
+        <v>6.5975</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.06</v>
       </c>
       <c r="I170" t="n">
-        <v>0.1949</v>
+        <v>0.2071</v>
       </c>
       <c r="J170" t="n">
-        <v>4.8725</v>
+        <v>5.1775</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.99</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.0856</v>
       </c>
       <c r="J171" t="n">
-        <v>-2.3075</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.86</v>
       </c>
       <c r="I172" t="n">
-        <v>0.7122000000000001</v>
+        <v>0.819</v>
       </c>
       <c r="J172" t="n">
-        <v>14.9562</v>
+        <v>17.199</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.71</v>
       </c>
       <c r="I173" t="n">
-        <v>0.6226</v>
+        <v>0.7161</v>
       </c>
       <c r="J173" t="n">
-        <v>13.0746</v>
+        <v>15.0381</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.08</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1109</v>
+        <v>0.1316</v>
       </c>
       <c r="J174" t="n">
-        <v>2.3289</v>
+        <v>2.7636</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.96</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.093</v>
+        <v>-0.0956</v>
       </c>
       <c r="J175" t="n">
-        <v>-1.953</v>
+        <v>-2.0076</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.9</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1645</v>
+        <v>-0.1706</v>
       </c>
       <c r="J176" t="n">
-        <v>-3.4545</v>
+        <v>-3.5826</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.24</v>
       </c>
       <c r="I177" t="n">
-        <v>0.3915</v>
+        <v>0.4215</v>
       </c>
       <c r="J177" t="n">
-        <v>8.221500000000001</v>
+        <v>8.8515</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.99</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.0062</v>
+        <v>-0.0142</v>
       </c>
       <c r="J178" t="n">
-        <v>-0.1302</v>
+        <v>-0.2982</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.83</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1939</v>
+        <v>-0.2108</v>
       </c>
       <c r="J179" t="n">
-        <v>-4.0719</v>
+        <v>-4.4268</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.71</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3115</v>
+        <v>-0.3265</v>
       </c>
       <c r="J180" t="n">
-        <v>-6.5415</v>
+        <v>-6.8565</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.61</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4057</v>
+        <v>-0.4171</v>
       </c>
       <c r="J181" t="n">
-        <v>-8.5197</v>
+        <v>-8.7591</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.98</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.0042</v>
+        <v>-0.0181</v>
       </c>
       <c r="J182" t="n">
-        <v>-0.1008</v>
+        <v>-0.4344</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.87</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1423</v>
+        <v>-0.1614</v>
       </c>
       <c r="J183" t="n">
-        <v>-3.4152</v>
+        <v>-3.8736</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.78</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2329</v>
+        <v>-0.2519</v>
       </c>
       <c r="J184" t="n">
-        <v>-5.5896</v>
+        <v>-6.0456</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.7</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3085</v>
+        <v>-0.326</v>
       </c>
       <c r="J185" t="n">
-        <v>-7.404</v>
+        <v>-7.824</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.6</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4027</v>
+        <v>-0.4163</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.6648</v>
+        <v>-9.991199999999999</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.57</v>
       </c>
       <c r="I187" t="n">
-        <v>0.9385</v>
+        <v>1.036</v>
       </c>
       <c r="J187" t="n">
-        <v>22.524</v>
+        <v>24.864</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.56</v>
       </c>
       <c r="I188" t="n">
-        <v>0.9261</v>
+        <v>1.0228</v>
       </c>
       <c r="J188" t="n">
-        <v>22.2264</v>
+        <v>24.5472</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.14</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3697</v>
+        <v>0.3984</v>
       </c>
       <c r="J189" t="n">
-        <v>8.8728</v>
+        <v>9.5616</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.09</v>
       </c>
       <c r="I190" t="n">
-        <v>0.2564</v>
+        <v>0.2716</v>
       </c>
       <c r="J190" t="n">
-        <v>6.1536</v>
+        <v>6.5184</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.01</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.0118</v>
+        <v>0.0136</v>
       </c>
       <c r="J191" t="n">
-        <v>-0.2832</v>
+        <v>0.3264</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>0.67</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.2839</v>
+        <v>-0.3123</v>
       </c>
       <c r="J192" t="n">
-        <v>-5.3941</v>
+        <v>-5.9337</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.55</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.4054</v>
+        <v>-0.4265</v>
       </c>
       <c r="J193" t="n">
-        <v>-7.7026</v>
+        <v>-8.1035</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.48</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.4675</v>
+        <v>-0.485</v>
       </c>
       <c r="J194" t="n">
-        <v>-8.8825</v>
+        <v>-9.215</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.45</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4957</v>
+        <v>-0.5112</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.4183</v>
+        <v>-9.7128</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.45</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4957</v>
+        <v>-0.5112</v>
       </c>
       <c r="J196" t="n">
-        <v>-9.4183</v>
+        <v>-9.7128</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>2.35</v>
       </c>
       <c r="I197" t="n">
-        <v>1.7432</v>
+        <v>1.8921</v>
       </c>
       <c r="J197" t="n">
-        <v>33.1208</v>
+        <v>35.9499</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.63</v>
       </c>
       <c r="I198" t="n">
-        <v>0.9597</v>
+        <v>1.0687</v>
       </c>
       <c r="J198" t="n">
-        <v>18.2343</v>
+        <v>20.3053</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.6</v>
       </c>
       <c r="I199" t="n">
-        <v>0.9267</v>
+        <v>1.033</v>
       </c>
       <c r="J199" t="n">
-        <v>17.6073</v>
+        <v>19.627</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.39</v>
       </c>
       <c r="I200" t="n">
-        <v>0.6765</v>
+        <v>0.7609</v>
       </c>
       <c r="J200" t="n">
-        <v>12.8535</v>
+        <v>14.4571</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.04</v>
       </c>
       <c r="I201" t="n">
-        <v>0.0336</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="J201" t="n">
-        <v>0.6384</v>
+        <v>1.4763</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.52</v>
       </c>
       <c r="I202" t="n">
-        <v>1.1493</v>
+        <v>1.116</v>
       </c>
       <c r="J202" t="n">
-        <v>25.2846</v>
+        <v>24.552</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.45</v>
       </c>
       <c r="I203" t="n">
-        <v>1.0611</v>
+        <v>1.0173</v>
       </c>
       <c r="J203" t="n">
-        <v>23.3442</v>
+        <v>22.3806</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.33</v>
       </c>
       <c r="I204" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.7993</v>
       </c>
       <c r="J204" t="n">
-        <v>18.5284</v>
+        <v>17.5846</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.16</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4459</v>
+        <v>0.4453</v>
       </c>
       <c r="J205" t="n">
-        <v>9.809799999999999</v>
+        <v>9.7966</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.93</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3328</v>
+        <v>-0.3104</v>
       </c>
       <c r="J206" t="n">
-        <v>-7.3216</v>
+        <v>-6.8288</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.18</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4599</v>
+        <v>0.4421</v>
       </c>
       <c r="J207" t="n">
-        <v>10.1178</v>
+        <v>9.7262</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.03</v>
       </c>
       <c r="I208" t="n">
-        <v>0.1324</v>
+        <v>0.1295</v>
       </c>
       <c r="J208" t="n">
-        <v>2.9128</v>
+        <v>2.849</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.87</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1519</v>
+        <v>-0.1687</v>
       </c>
       <c r="J209" t="n">
-        <v>-3.3418</v>
+        <v>-3.7114</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.72</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2989</v>
+        <v>-0.3149</v>
       </c>
       <c r="J210" t="n">
-        <v>-6.5758</v>
+        <v>-6.9278</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.47</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5315</v>
+        <v>-0.5366</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.693</v>
+        <v>-11.8052</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.33</v>
       </c>
       <c r="I212" t="n">
-        <v>0.8592</v>
+        <v>0.8111</v>
       </c>
       <c r="J212" t="n">
-        <v>18.9024</v>
+        <v>17.8442</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.3</v>
       </c>
       <c r="I213" t="n">
-        <v>0.7907999999999999</v>
+        <v>0.7511</v>
       </c>
       <c r="J213" t="n">
-        <v>17.3976</v>
+        <v>16.5242</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.17</v>
       </c>
       <c r="I214" t="n">
-        <v>0.4858</v>
+        <v>0.4783</v>
       </c>
       <c r="J214" t="n">
-        <v>10.6876</v>
+        <v>10.5226</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.14</v>
       </c>
       <c r="I215" t="n">
-        <v>0.4089</v>
+        <v>0.4084</v>
       </c>
       <c r="J215" t="n">
-        <v>8.995799999999999</v>
+        <v>8.9848</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.11</v>
       </c>
       <c r="I216" t="n">
-        <v>0.3281</v>
+        <v>0.3344</v>
       </c>
       <c r="J216" t="n">
-        <v>7.2182</v>
+        <v>7.3568</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.99</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.0008</v>
+        <v>-0.01</v>
       </c>
       <c r="J217" t="n">
-        <v>-0.0176</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.97</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.0318</v>
+        <v>-0.0442</v>
       </c>
       <c r="J218" t="n">
-        <v>-0.6996</v>
+        <v>-0.9724</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.91</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1073</v>
+        <v>-0.1234</v>
       </c>
       <c r="J219" t="n">
-        <v>-2.3606</v>
+        <v>-2.7148</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.77</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2496</v>
+        <v>-0.2668</v>
       </c>
       <c r="J220" t="n">
-        <v>-5.4912</v>
+        <v>-5.8696</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.59</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4204</v>
+        <v>-0.4318</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.248799999999999</v>
+        <v>-9.499599999999999</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.68</v>
       </c>
       <c r="I222" t="n">
-        <v>1.3116</v>
+        <v>1.2955</v>
       </c>
       <c r="J222" t="n">
-        <v>28.8552</v>
+        <v>28.501</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.57</v>
       </c>
       <c r="I223" t="n">
-        <v>1.1824</v>
+        <v>1.1571</v>
       </c>
       <c r="J223" t="n">
-        <v>26.0128</v>
+        <v>25.4562</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.52</v>
       </c>
       <c r="I224" t="n">
-        <v>1.123</v>
+        <v>1.0931</v>
       </c>
       <c r="J224" t="n">
-        <v>24.706</v>
+        <v>24.0482</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.5</v>
       </c>
       <c r="I225" t="n">
-        <v>1.0992</v>
+        <v>1.067</v>
       </c>
       <c r="J225" t="n">
-        <v>24.1824</v>
+        <v>23.474</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.93</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3673</v>
+        <v>-0.3347</v>
       </c>
       <c r="J226" t="n">
-        <v>-8.0806</v>
+        <v>-7.3634</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.1754</v>
+        <v>-0.201</v>
       </c>
       <c r="J227" t="n">
-        <v>-3.8588</v>
+        <v>-4.422</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.68</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.3086</v>
+        <v>-0.3299</v>
       </c>
       <c r="J228" t="n">
-        <v>-6.7892</v>
+        <v>-7.2578</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.61</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3711</v>
+        <v>-0.3902</v>
       </c>
       <c r="J229" t="n">
-        <v>-8.164199999999999</v>
+        <v>-8.5844</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.58</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3987</v>
+        <v>-0.4164</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.7714</v>
+        <v>-9.1608</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.55</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4266</v>
+        <v>-0.4428</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.385199999999999</v>
+        <v>-9.7416</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.07</v>
       </c>
       <c r="I232" t="n">
-        <v>0.2216</v>
+        <v>0.2111</v>
       </c>
       <c r="J232" t="n">
-        <v>5.3184</v>
+        <v>5.0664</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.77</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.2373</v>
+        <v>-0.2575</v>
       </c>
       <c r="J233" t="n">
-        <v>-5.6952</v>
+        <v>-6.18</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.73</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.2742</v>
+        <v>-0.2939</v>
       </c>
       <c r="J234" t="n">
-        <v>-6.5808</v>
+        <v>-7.0536</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.57</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.4234</v>
+        <v>-0.4372</v>
       </c>
       <c r="J235" t="n">
-        <v>-10.1616</v>
+        <v>-10.4928</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.55</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4421</v>
+        <v>-0.4549</v>
       </c>
       <c r="J236" t="n">
-        <v>-10.6104</v>
+        <v>-10.9176</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.46</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5579</v>
+        <v>0.5675</v>
       </c>
       <c r="J237" t="n">
-        <v>13.3896</v>
+        <v>13.62</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.46</v>
       </c>
       <c r="I238" t="n">
-        <v>0.5579</v>
+        <v>0.5675</v>
       </c>
       <c r="J238" t="n">
-        <v>13.3896</v>
+        <v>13.62</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.31</v>
       </c>
       <c r="I239" t="n">
-        <v>0.3974</v>
+        <v>0.4143</v>
       </c>
       <c r="J239" t="n">
-        <v>9.537599999999999</v>
+        <v>9.943199999999999</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.29</v>
       </c>
       <c r="I240" t="n">
-        <v>0.3751</v>
+        <v>0.3928</v>
       </c>
       <c r="J240" t="n">
-        <v>9.0024</v>
+        <v>9.427199999999999</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>1.15</v>
       </c>
       <c r="I241" t="n">
-        <v>0.2049</v>
+        <v>0.2266</v>
       </c>
       <c r="J241" t="n">
-        <v>4.9176</v>
+        <v>5.4384</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.65</v>
       </c>
       <c r="I242" t="n">
-        <v>1.2988</v>
+        <v>1.2776</v>
       </c>
       <c r="J242" t="n">
-        <v>28.5736</v>
+        <v>28.1072</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.45</v>
       </c>
       <c r="I243" t="n">
-        <v>1.0532</v>
+        <v>1.0097</v>
       </c>
       <c r="J243" t="n">
-        <v>23.1704</v>
+        <v>22.2134</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.24</v>
       </c>
       <c r="I244" t="n">
-        <v>0.6328</v>
+        <v>0.6151</v>
       </c>
       <c r="J244" t="n">
-        <v>13.9216</v>
+        <v>13.5322</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.23</v>
       </c>
       <c r="I245" t="n">
-        <v>0.6091</v>
+        <v>0.594</v>
       </c>
       <c r="J245" t="n">
-        <v>13.4002</v>
+        <v>13.068</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>1.05</v>
       </c>
       <c r="I246" t="n">
-        <v>0.1227</v>
+        <v>0.1488</v>
       </c>
       <c r="J246" t="n">
-        <v>2.6994</v>
+        <v>3.2736</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.08</v>
       </c>
       <c r="I247" t="n">
-        <v>0.2743</v>
+        <v>0.2632</v>
       </c>
       <c r="J247" t="n">
-        <v>6.0346</v>
+        <v>5.7904</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.86</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.1564</v>
+        <v>-0.1747</v>
       </c>
       <c r="J248" t="n">
-        <v>-3.4408</v>
+        <v>-3.8434</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2067</v>
+        <v>-0.2253</v>
       </c>
       <c r="J249" t="n">
-        <v>-4.5474</v>
+        <v>-4.9566</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.67</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3398</v>
+        <v>-0.3557</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.4756</v>
+        <v>-7.8254</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.61</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3962</v>
+        <v>-0.4097</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.7164</v>
+        <v>-9.013400000000001</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.69</v>
       </c>
       <c r="I252" t="n">
-        <v>1.0672</v>
+        <v>1.1762</v>
       </c>
       <c r="J252" t="n">
-        <v>24.5456</v>
+        <v>27.0526</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.38</v>
       </c>
       <c r="I253" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="J253" t="n">
-        <v>15.847</v>
+        <v>17.6778</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.26</v>
       </c>
       <c r="I254" t="n">
-        <v>0.5345</v>
+        <v>0.5972</v>
       </c>
       <c r="J254" t="n">
-        <v>12.2935</v>
+        <v>13.7356</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.25</v>
       </c>
       <c r="I255" t="n">
-        <v>0.5208</v>
+        <v>0.5819</v>
       </c>
       <c r="J255" t="n">
-        <v>11.9784</v>
+        <v>13.3837</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1.17</v>
       </c>
       <c r="I256" t="n">
-        <v>0.4056</v>
+        <v>0.4515</v>
       </c>
       <c r="J256" t="n">
-        <v>9.328799999999999</v>
+        <v>10.3845</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.01</v>
       </c>
       <c r="I257" t="n">
-        <v>0.1208</v>
+        <v>0.104</v>
       </c>
       <c r="J257" t="n">
-        <v>2.7784</v>
+        <v>2.392</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.9</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.1013</v>
+        <v>-0.1216</v>
       </c>
       <c r="J258" t="n">
-        <v>-2.3299</v>
+        <v>-2.7968</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.66</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.3413</v>
+        <v>-0.3585</v>
       </c>
       <c r="J259" t="n">
-        <v>-7.8499</v>
+        <v>-8.2455</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.63</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3694</v>
+        <v>-0.3855</v>
       </c>
       <c r="J260" t="n">
-        <v>-8.4962</v>
+        <v>-8.8665</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4349</v>
+        <v>-0.4477</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.0027</v>
+        <v>-10.2971</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.24</v>
       </c>
       <c r="I262" t="n">
-        <v>0.3716</v>
+        <v>0.3971</v>
       </c>
       <c r="J262" t="n">
-        <v>9.6616</v>
+        <v>10.3246</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.19</v>
       </c>
       <c r="I263" t="n">
-        <v>0.3254</v>
+        <v>0.3308</v>
       </c>
       <c r="J263" t="n">
-        <v>8.4604</v>
+        <v>8.6008</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.87</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.1641</v>
+        <v>-0.1781</v>
       </c>
       <c r="J264" t="n">
-        <v>-4.2666</v>
+        <v>-4.6306</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.86</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.1747</v>
+        <v>-0.1888</v>
       </c>
       <c r="J265" t="n">
-        <v>-4.5422</v>
+        <v>-4.9088</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.72</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3144</v>
+        <v>-0.327</v>
       </c>
       <c r="J266" t="n">
-        <v>-8.1744</v>
+        <v>-8.502000000000001</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.41</v>
       </c>
       <c r="I267" t="n">
-        <v>0.4595</v>
+        <v>0.5205</v>
       </c>
       <c r="J267" t="n">
-        <v>11.947</v>
+        <v>13.533</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.08</v>
       </c>
       <c r="I268" t="n">
-        <v>0.1353</v>
+        <v>0.1499</v>
       </c>
       <c r="J268" t="n">
-        <v>3.5178</v>
+        <v>3.8974</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.03</v>
       </c>
       <c r="I269" t="n">
-        <v>0.056</v>
+        <v>0.0674</v>
       </c>
       <c r="J269" t="n">
-        <v>1.456</v>
+        <v>1.7524</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.99</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.0291</v>
+        <v>-0.0318</v>
       </c>
       <c r="J270" t="n">
-        <v>-0.7566000000000001</v>
+        <v>-0.8268</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.95</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.0854</v>
+        <v>-0.0934</v>
       </c>
       <c r="J271" t="n">
-        <v>-2.2204</v>
+        <v>-2.4284</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.67</v>
       </c>
       <c r="I272" t="n">
-        <v>1.1078</v>
+        <v>1.208</v>
       </c>
       <c r="J272" t="n">
-        <v>31.0184</v>
+        <v>33.824</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.16</v>
       </c>
       <c r="I273" t="n">
-        <v>0.4177</v>
+        <v>0.4582</v>
       </c>
       <c r="J273" t="n">
-        <v>11.6956</v>
+        <v>12.8296</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.03</v>
       </c>
       <c r="I274" t="n">
-        <v>0.104</v>
+        <v>0.1177</v>
       </c>
       <c r="J274" t="n">
-        <v>2.912</v>
+        <v>3.2956</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.91</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3539</v>
+        <v>-0.3389</v>
       </c>
       <c r="J275" t="n">
-        <v>-9.9092</v>
+        <v>-9.4892</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.84</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5502</v>
+        <v>-0.5175</v>
       </c>
       <c r="J276" t="n">
-        <v>-15.4056</v>
+        <v>-14.49</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.13</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3282</v>
+        <v>0.3277</v>
       </c>
       <c r="J277" t="n">
-        <v>9.1896</v>
+        <v>9.175599999999999</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.02</v>
       </c>
       <c r="I278" t="n">
-        <v>0.0832</v>
+        <v>0.0857</v>
       </c>
       <c r="J278" t="n">
-        <v>2.3296</v>
+        <v>2.3996</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.87</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.158</v>
+        <v>-0.1733</v>
       </c>
       <c r="J279" t="n">
-        <v>-4.424</v>
+        <v>-4.8524</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.82</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.2095</v>
+        <v>-0.2251</v>
       </c>
       <c r="J280" t="n">
-        <v>-5.866</v>
+        <v>-6.3028</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.77</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.2593</v>
+        <v>-0.2744</v>
       </c>
       <c r="J281" t="n">
-        <v>-7.2604</v>
+        <v>-7.6832</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.75</v>
       </c>
       <c r="I282" t="n">
-        <v>1.1555</v>
+        <v>1.2667</v>
       </c>
       <c r="J282" t="n">
-        <v>33.5095</v>
+        <v>36.7343</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.48</v>
       </c>
       <c r="I283" t="n">
-        <v>0.8246</v>
+        <v>0.914</v>
       </c>
       <c r="J283" t="n">
-        <v>23.9134</v>
+        <v>26.506</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.32</v>
       </c>
       <c r="I284" t="n">
-        <v>0.6199</v>
+        <v>0.6906</v>
       </c>
       <c r="J284" t="n">
-        <v>17.9771</v>
+        <v>20.0274</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.3025</v>
+        <v>-0.2817</v>
       </c>
       <c r="J285" t="n">
-        <v>-8.772500000000001</v>
+        <v>-8.1693</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.92</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3641</v>
+        <v>-0.3394</v>
       </c>
       <c r="J286" t="n">
-        <v>-10.5589</v>
+        <v>-9.842599999999999</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.35</v>
       </c>
       <c r="I287" t="n">
-        <v>0.5967</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="J287" t="n">
-        <v>17.3043</v>
+        <v>19.0153</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.95</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.0599</v>
+        <v>-0.0738</v>
       </c>
       <c r="J288" t="n">
-        <v>-1.7371</v>
+        <v>-2.1402</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.75</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2698</v>
+        <v>-0.2865</v>
       </c>
       <c r="J289" t="n">
-        <v>-7.8242</v>
+        <v>-8.3085</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.73</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2891</v>
+        <v>-0.3053</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.383900000000001</v>
+        <v>-8.8537</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.48</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5222</v>
+        <v>-0.5279</v>
       </c>
       <c r="J291" t="n">
-        <v>-15.1438</v>
+        <v>-15.3091</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.87</v>
       </c>
       <c r="I292" t="n">
-        <v>1.3072</v>
+        <v>1.4246</v>
       </c>
       <c r="J292" t="n">
-        <v>32.68</v>
+        <v>35.615</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.34</v>
       </c>
       <c r="I293" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.7226</v>
       </c>
       <c r="J293" t="n">
-        <v>16.2425</v>
+        <v>18.065</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.33</v>
       </c>
       <c r="I294" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.7081</v>
       </c>
       <c r="J294" t="n">
-        <v>15.915</v>
+        <v>17.7025</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.93</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.3272</v>
+        <v>-0.3064</v>
       </c>
       <c r="J295" t="n">
-        <v>-8.18</v>
+        <v>-7.66</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.8</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.6875</v>
+        <v>-0.6341</v>
       </c>
       <c r="J296" t="n">
-        <v>-17.1875</v>
+        <v>-15.8525</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.02</v>
       </c>
       <c r="I297" t="n">
-        <v>0.1105</v>
+        <v>0.1056</v>
       </c>
       <c r="J297" t="n">
-        <v>2.7625</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.92</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.0948</v>
+        <v>-0.1107</v>
       </c>
       <c r="J298" t="n">
-        <v>-2.37</v>
+        <v>-2.7675</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.85</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1708</v>
+        <v>-0.1883</v>
       </c>
       <c r="J299" t="n">
-        <v>-4.27</v>
+        <v>-4.7075</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.73</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2874</v>
+        <v>-0.3041</v>
       </c>
       <c r="J300" t="n">
-        <v>-7.185</v>
+        <v>-7.6025</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.68</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3352</v>
+        <v>-0.3503</v>
       </c>
       <c r="J301" t="n">
-        <v>-8.380000000000001</v>
+        <v>-8.7575</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.33</v>
       </c>
       <c r="I302" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.7363</v>
       </c>
       <c r="J302" t="n">
-        <v>20.067</v>
+        <v>22.089</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.21</v>
       </c>
       <c r="I303" t="n">
-        <v>0.4974</v>
+        <v>0.5472</v>
       </c>
       <c r="J303" t="n">
-        <v>14.922</v>
+        <v>16.416</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.07</v>
       </c>
       <c r="I304" t="n">
-        <v>0.2402</v>
+        <v>0.2461</v>
       </c>
       <c r="J304" t="n">
-        <v>7.206</v>
+        <v>7.383</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.93</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.2849</v>
+        <v>-0.2768</v>
       </c>
       <c r="J305" t="n">
-        <v>-8.547000000000001</v>
+        <v>-8.304</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.91</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3452</v>
+        <v>-0.3328</v>
       </c>
       <c r="J306" t="n">
-        <v>-10.356</v>
+        <v>-9.984</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.17</v>
       </c>
       <c r="I307" t="n">
-        <v>0.3821</v>
+        <v>0.4055</v>
       </c>
       <c r="J307" t="n">
-        <v>11.463</v>
+        <v>12.165</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.9</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.1248</v>
+        <v>-0.1397</v>
       </c>
       <c r="J308" t="n">
-        <v>-3.744</v>
+        <v>-4.191</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.87</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1565</v>
+        <v>-0.1722</v>
       </c>
       <c r="J309" t="n">
-        <v>-4.695</v>
+        <v>-5.166</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.86</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1669</v>
+        <v>-0.1827</v>
       </c>
       <c r="J310" t="n">
-        <v>-5.007</v>
+        <v>-5.481</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.74</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.2868</v>
+        <v>-0.3017</v>
       </c>
       <c r="J311" t="n">
-        <v>-8.603999999999999</v>
+        <v>-9.051</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.37</v>
       </c>
       <c r="I312" t="n">
-        <v>0.4536</v>
+        <v>0.5079</v>
       </c>
       <c r="J312" t="n">
-        <v>15.876</v>
+        <v>17.7765</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.37</v>
       </c>
       <c r="I313" t="n">
-        <v>0.4536</v>
+        <v>0.5079</v>
       </c>
       <c r="J313" t="n">
-        <v>15.876</v>
+        <v>17.7765</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.06</v>
       </c>
       <c r="I314" t="n">
-        <v>0.1129</v>
+        <v>0.1253</v>
       </c>
       <c r="J314" t="n">
-        <v>3.9515</v>
+        <v>4.3855</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.86</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.1881</v>
+        <v>-0.1992</v>
       </c>
       <c r="J315" t="n">
-        <v>-6.5835</v>
+        <v>-6.972</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.82</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.2295</v>
+        <v>-0.2407</v>
       </c>
       <c r="J316" t="n">
-        <v>-8.032500000000001</v>
+        <v>-8.4245</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.16</v>
       </c>
       <c r="I317" t="n">
-        <v>0.2461</v>
+        <v>0.2606</v>
       </c>
       <c r="J317" t="n">
-        <v>8.6135</v>
+        <v>9.121</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.13</v>
       </c>
       <c r="I318" t="n">
-        <v>0.2062</v>
+        <v>0.2211</v>
       </c>
       <c r="J318" t="n">
-        <v>7.217</v>
+        <v>7.7385</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.06</v>
       </c>
       <c r="I319" t="n">
-        <v>0.1074</v>
+        <v>0.1207</v>
       </c>
       <c r="J319" t="n">
-        <v>3.759</v>
+        <v>4.2245</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.04</v>
       </c>
       <c r="I320" t="n">
-        <v>0.0756</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="J320" t="n">
-        <v>2.646</v>
+        <v>3.059</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.97</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.0571</v>
+        <v>-0.0636</v>
       </c>
       <c r="J321" t="n">
-        <v>-1.9985</v>
+        <v>-2.226</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.67</v>
       </c>
       <c r="I322" t="n">
-        <v>1.0349</v>
+        <v>1.1434</v>
       </c>
       <c r="J322" t="n">
-        <v>21.7329</v>
+        <v>24.0114</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.54</v>
       </c>
       <c r="I323" t="n">
-        <v>0.8798</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="J323" t="n">
-        <v>18.4758</v>
+        <v>20.5233</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.34</v>
       </c>
       <c r="I324" t="n">
-        <v>0.6357</v>
+        <v>0.7106</v>
       </c>
       <c r="J324" t="n">
-        <v>13.3497</v>
+        <v>14.9226</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.21</v>
       </c>
       <c r="I325" t="n">
-        <v>0.4591</v>
+        <v>0.5141</v>
       </c>
       <c r="J325" t="n">
-        <v>9.6411</v>
+        <v>10.7961</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>1.2</v>
       </c>
       <c r="I326" t="n">
-        <v>0.4446</v>
+        <v>0.4979</v>
       </c>
       <c r="J326" t="n">
-        <v>9.336600000000001</v>
+        <v>10.4559</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>0.88</v>
       </c>
       <c r="I327" t="n">
-        <v>-0.1076</v>
+        <v>-0.1317</v>
       </c>
       <c r="J327" t="n">
-        <v>-2.2596</v>
+        <v>-2.7657</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>0.87</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.1193</v>
+        <v>-0.1434</v>
       </c>
       <c r="J328" t="n">
-        <v>-2.5053</v>
+        <v>-3.0114</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.76</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.2382</v>
+        <v>-0.2603</v>
       </c>
       <c r="J329" t="n">
-        <v>-5.0022</v>
+        <v>-5.4663</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.52</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.4617</v>
+        <v>-0.4746</v>
       </c>
       <c r="J330" t="n">
-        <v>-9.6957</v>
+        <v>-9.9666</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.4</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.5741000000000001</v>
+        <v>-0.5794</v>
       </c>
       <c r="J331" t="n">
-        <v>-12.0561</v>
+        <v>-12.1674</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>0.99</v>
       </c>
       <c r="I332" t="n">
-        <v>0.0684</v>
+        <v>0.0342</v>
       </c>
       <c r="J332" t="n">
-        <v>1.4364</v>
+        <v>0.7181999999999999</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>0.72</v>
       </c>
       <c r="I333" t="n">
-        <v>-0.2798</v>
+        <v>-0.3001</v>
       </c>
       <c r="J333" t="n">
-        <v>-5.8758</v>
+        <v>-6.3021</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>0.65</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.343</v>
+        <v>-0.3616</v>
       </c>
       <c r="J334" t="n">
-        <v>-7.203</v>
+        <v>-7.5936</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.61</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.3802</v>
+        <v>-0.3972</v>
       </c>
       <c r="J335" t="n">
-        <v>-7.9842</v>
+        <v>-8.341200000000001</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.54</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.4457</v>
+        <v>-0.4591</v>
       </c>
       <c r="J336" t="n">
-        <v>-9.3597</v>
+        <v>-9.6411</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>2.02</v>
       </c>
       <c r="I337" t="n">
-        <v>1.4395</v>
+        <v>1.569</v>
       </c>
       <c r="J337" t="n">
-        <v>30.2295</v>
+        <v>32.949</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.6</v>
       </c>
       <c r="I338" t="n">
-        <v>0.9520999999999999</v>
+        <v>1.055</v>
       </c>
       <c r="J338" t="n">
-        <v>19.9941</v>
+        <v>22.155</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.18</v>
       </c>
       <c r="I339" t="n">
-        <v>0.4155</v>
+        <v>0.4647</v>
       </c>
       <c r="J339" t="n">
-        <v>8.7255</v>
+        <v>9.758699999999999</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>1.11</v>
       </c>
       <c r="I340" t="n">
-        <v>0.287</v>
+        <v>0.3057</v>
       </c>
       <c r="J340" t="n">
-        <v>6.027</v>
+        <v>6.4197</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>1.04</v>
       </c>
       <c r="I341" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.1068</v>
       </c>
       <c r="J341" t="n">
-        <v>1.5729</v>
+        <v>2.2428</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.24</v>
       </c>
       <c r="I342" t="n">
-        <v>0.4232</v>
+        <v>0.4704</v>
       </c>
       <c r="J342" t="n">
-        <v>17.7744</v>
+        <v>19.7568</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.17</v>
       </c>
       <c r="I343" t="n">
-        <v>0.3497</v>
+        <v>0.3658</v>
       </c>
       <c r="J343" t="n">
-        <v>14.6874</v>
+        <v>15.3636</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.14</v>
       </c>
       <c r="I344" t="n">
-        <v>0.3055</v>
+        <v>0.3136</v>
       </c>
       <c r="J344" t="n">
-        <v>12.831</v>
+        <v>13.1712</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>1.11</v>
       </c>
       <c r="I345" t="n">
-        <v>0.2489</v>
+        <v>0.2591</v>
       </c>
       <c r="J345" t="n">
-        <v>10.4538</v>
+        <v>10.8822</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.77</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.2782</v>
+        <v>-0.2892</v>
       </c>
       <c r="J346" t="n">
-        <v>-11.6844</v>
+        <v>-12.1464</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.54</v>
       </c>
       <c r="I347" t="n">
-        <v>0.9724</v>
+        <v>1.0592</v>
       </c>
       <c r="J347" t="n">
-        <v>40.8408</v>
+        <v>44.4864</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.26</v>
       </c>
       <c r="I348" t="n">
-        <v>0.5838</v>
+        <v>0.64</v>
       </c>
       <c r="J348" t="n">
-        <v>24.5196</v>
+        <v>26.88</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>0.93</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.2694</v>
+        <v>-0.266</v>
       </c>
       <c r="J349" t="n">
-        <v>-11.3148</v>
+        <v>-11.172</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.89</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.3874</v>
+        <v>-0.3751</v>
       </c>
       <c r="J350" t="n">
-        <v>-16.2708</v>
+        <v>-15.7542</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.55</v>
       </c>
       <c r="I351" t="n">
-        <v>-1.2417</v>
+        <v>-1.1241</v>
       </c>
       <c r="J351" t="n">
-        <v>-52.1514</v>
+        <v>-47.2122</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5202/event_5202_evp_summary.xlsx
+++ b/database/event/5202/event_5202_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.657999999999999</v>
+        <v>8.467599999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3836</v>
+        <v>2.3312</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3171</v>
+        <v>3.2516</v>
       </c>
       <c r="E2" t="n">
-        <v>8.657999999999999</v>
+        <v>8.467599999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3849</v>
+        <v>2.334</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2731</v>
+        <v>6.1336</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4948</v>
+        <v>2.3987</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7621</v>
+        <v>2.6656</v>
       </c>
       <c r="J2" t="n">
-        <v>6.2731</v>
+        <v>6.1336</v>
       </c>
       <c r="K2" t="n">
         <v>139</v>
@@ -529,7 +529,7 @@
         <v>250</v>
       </c>
       <c r="M2" t="n">
-        <v>9.0352</v>
+        <v>8.799200000000001</v>
       </c>
       <c r="N2" t="n">
         <v>389</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.4627</v>
+        <v>6.4298</v>
       </c>
       <c r="C3" t="n">
-        <v>1.7792</v>
+        <v>1.7702</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3178</v>
+        <v>2.3233</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4627</v>
+        <v>6.4298</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2922</v>
+        <v>0.2736</v>
       </c>
       <c r="G3" t="n">
-        <v>6.1705</v>
+        <v>6.1562</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2922</v>
+        <v>0.2736</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3075</v>
+        <v>0.2884</v>
       </c>
       <c r="J3" t="n">
-        <v>6.1705</v>
+        <v>6.1562</v>
       </c>
       <c r="K3" t="n">
         <v>57</v>
@@ -575,7 +575,7 @@
         <v>222</v>
       </c>
       <c r="M3" t="n">
-        <v>6.478</v>
+        <v>6.4446</v>
       </c>
       <c r="N3" t="n">
         <v>279</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.7042</v>
+        <v>4.5584</v>
       </c>
       <c r="C4" t="n">
-        <v>1.2951</v>
+        <v>1.255</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5172</v>
+        <v>1.4708</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7042</v>
+        <v>4.5584</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3573</v>
+        <v>0.285</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3469</v>
+        <v>4.2733</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3573</v>
+        <v>0.285</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3665</v>
+        <v>0.2927</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3469</v>
+        <v>4.2733</v>
       </c>
       <c r="K4" t="n">
         <v>75</v>
@@ -621,7 +621,7 @@
         <v>193</v>
       </c>
       <c r="M4" t="n">
-        <v>4.7134</v>
+        <v>4.566</v>
       </c>
       <c r="N4" t="n">
         <v>268</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.2614</v>
+        <v>4.0506</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1732</v>
+        <v>1.1152</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3157</v>
+        <v>1.2395</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2614</v>
+        <v>4.0506</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2576</v>
+        <v>1.0986</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0038</v>
+        <v>2.952</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2576</v>
+        <v>1.0986</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2576</v>
+        <v>1.0986</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0038</v>
+        <v>2.952</v>
       </c>
       <c r="K5" t="n">
         <v>121</v>
@@ -667,7 +667,7 @@
         <v>138</v>
       </c>
       <c r="M5" t="n">
-        <v>4.2614</v>
+        <v>4.0506</v>
       </c>
       <c r="N5" t="n">
         <v>259</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1226</v>
+        <v>3.9578</v>
       </c>
       <c r="C6" t="n">
-        <v>1.135</v>
+        <v>1.0896</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2525</v>
+        <v>1.1972</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1226</v>
+        <v>3.9578</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9586</v>
+        <v>0.8481</v>
       </c>
       <c r="G6" t="n">
-        <v>3.164</v>
+        <v>3.1098</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9586</v>
+        <v>0.8481</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9833</v>
+        <v>0.8707</v>
       </c>
       <c r="J6" t="n">
-        <v>3.164</v>
+        <v>3.1098</v>
       </c>
       <c r="K6" t="n">
         <v>75</v>
@@ -713,7 +713,7 @@
         <v>193</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1473</v>
+        <v>3.9805</v>
       </c>
       <c r="N6" t="n">
         <v>268</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.2164</v>
+        <v>3.2342</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8855</v>
+        <v>0.8904</v>
       </c>
       <c r="D7" t="n">
-        <v>0.84</v>
+        <v>0.8675</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2164</v>
+        <v>3.2342</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1463</v>
+        <v>1.1162</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0701</v>
+        <v>2.118</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1463</v>
+        <v>1.1162</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2061</v>
+        <v>1.1766</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0701</v>
+        <v>2.118</v>
       </c>
       <c r="K7" t="n">
         <v>57</v>
@@ -759,7 +759,7 @@
         <v>222</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2762</v>
+        <v>3.2946</v>
       </c>
       <c r="N7" t="n">
         <v>279</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.1983</v>
+        <v>3.0049</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8804999999999999</v>
+        <v>0.8273</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8317</v>
+        <v>0.7631</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1983</v>
+        <v>3.0049</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7303</v>
+        <v>2.6793</v>
       </c>
       <c r="G8" t="n">
-        <v>0.468</v>
+        <v>0.3256</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2508</v>
+        <v>3.1899</v>
       </c>
       <c r="I8" t="n">
-        <v>3.5991</v>
+        <v>3.5448</v>
       </c>
       <c r="J8" t="n">
-        <v>0.468</v>
+        <v>0.3256</v>
       </c>
       <c r="K8" t="n">
         <v>139</v>
@@ -805,7 +805,7 @@
         <v>250</v>
       </c>
       <c r="M8" t="n">
-        <v>4.0671</v>
+        <v>3.8704</v>
       </c>
       <c r="N8" t="n">
         <v>389</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.6224</v>
+        <v>2.5526</v>
       </c>
       <c r="C9" t="n">
-        <v>0.722</v>
+        <v>0.7027</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5696</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>2.6224</v>
+        <v>2.5526</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2838</v>
+        <v>-0.265</v>
       </c>
       <c r="G9" t="n">
-        <v>2.9062</v>
+        <v>2.8176</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2838</v>
+        <v>-0.265</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2986</v>
+        <v>-0.2794</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9062</v>
+        <v>2.8176</v>
       </c>
       <c r="K9" t="n">
         <v>57</v>
@@ -851,7 +851,7 @@
         <v>222</v>
       </c>
       <c r="M9" t="n">
-        <v>2.6076</v>
+        <v>2.5382</v>
       </c>
       <c r="N9" t="n">
         <v>279</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.3653</v>
+        <v>2.317</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6512</v>
+        <v>0.6379</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4525</v>
+        <v>0.4497</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3653</v>
+        <v>2.317</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0299</v>
+        <v>2.0705</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3354</v>
+        <v>0.2465</v>
       </c>
       <c r="H10" t="n">
-        <v>2.0299</v>
+        <v>2.0705</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1359</v>
+        <v>2.1826</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3354</v>
+        <v>0.2465</v>
       </c>
       <c r="K10" t="n">
         <v>68</v>
@@ -897,7 +897,7 @@
         <v>138</v>
       </c>
       <c r="M10" t="n">
-        <v>2.4713</v>
+        <v>2.4291</v>
       </c>
       <c r="N10" t="n">
         <v>206</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.3437</v>
+        <v>2.3036</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6452</v>
+        <v>0.6342</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4427</v>
+        <v>0.4436</v>
       </c>
       <c r="E11" t="n">
-        <v>2.3437</v>
+        <v>2.3036</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2732</v>
+        <v>1.2086</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0705</v>
+        <v>1.095</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2732</v>
+        <v>1.2086</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3397</v>
+        <v>1.2741</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0705</v>
+        <v>1.095</v>
       </c>
       <c r="K11" t="n">
         <v>57</v>
@@ -943,7 +943,7 @@
         <v>222</v>
       </c>
       <c r="M11" t="n">
-        <v>2.4102</v>
+        <v>2.3691</v>
       </c>
       <c r="N11" t="n">
         <v>279</v>
@@ -952,173 +952,173 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.1276</v>
+        <v>2.141</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5857</v>
+        <v>0.5894</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3443</v>
+        <v>0.3695</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1276</v>
+        <v>2.141</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0295</v>
+        <v>0.5018</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0981</v>
+        <v>1.6392</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0295</v>
+        <v>0.5018</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0832</v>
+        <v>0.5576</v>
       </c>
       <c r="J12" t="n">
-        <v>1.0981</v>
+        <v>1.6392</v>
       </c>
       <c r="K12" t="n">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="L12" t="n">
-        <v>222</v>
+        <v>250</v>
       </c>
       <c r="M12" t="n">
-        <v>2.1813</v>
+        <v>2.1968</v>
       </c>
       <c r="N12" t="n">
-        <v>279</v>
+        <v>389</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.1173</v>
+        <v>2.1183</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5829</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3396</v>
+        <v>0.3592</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1173</v>
+        <v>2.1183</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4373</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>1.68</v>
+        <v>2.7045</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4373</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4842</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>1.68</v>
+        <v>2.7045</v>
       </c>
       <c r="K13" t="n">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="L13" t="n">
-        <v>250</v>
+        <v>138</v>
       </c>
       <c r="M13" t="n">
-        <v>2.1642</v>
+        <v>2.1183</v>
       </c>
       <c r="N13" t="n">
-        <v>389</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.0981</v>
+        <v>2.0285</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5776</v>
+        <v>0.5585</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3309</v>
+        <v>0.3183</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0981</v>
+        <v>2.0285</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5851</v>
+        <v>0.9575</v>
       </c>
       <c r="G14" t="n">
-        <v>1.513</v>
+        <v>1.071</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5851</v>
+        <v>0.9575</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5851</v>
+        <v>1.0094</v>
       </c>
       <c r="J14" t="n">
-        <v>1.513</v>
+        <v>1.071</v>
       </c>
       <c r="K14" t="n">
-        <v>121</v>
+        <v>57</v>
       </c>
       <c r="L14" t="n">
-        <v>138</v>
+        <v>222</v>
       </c>
       <c r="M14" t="n">
-        <v>2.0981</v>
+        <v>2.0804</v>
       </c>
       <c r="N14" t="n">
-        <v>259</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.0732</v>
+        <v>1.9515</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5708</v>
+        <v>0.5373</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3196</v>
+        <v>0.2832</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0732</v>
+        <v>1.9515</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6195000000000001</v>
+        <v>0.5059</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6927</v>
+        <v>1.4456</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6195000000000001</v>
+        <v>0.5059</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6195000000000001</v>
+        <v>0.5059</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6927</v>
+        <v>1.4456</v>
       </c>
       <c r="K15" t="n">
         <v>121</v>
@@ -1127,7 +1127,7 @@
         <v>138</v>
       </c>
       <c r="M15" t="n">
-        <v>2.0732</v>
+        <v>1.9515</v>
       </c>
       <c r="N15" t="n">
         <v>259</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9827</v>
+        <v>1.9285</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5459000000000001</v>
+        <v>0.5309</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2784</v>
+        <v>0.2727</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9827</v>
+        <v>1.9285</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2993</v>
+        <v>1.2981</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6834</v>
+        <v>0.6304</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2993</v>
+        <v>1.2981</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3671</v>
+        <v>1.3684</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6834</v>
+        <v>0.6304</v>
       </c>
       <c r="K16" t="n">
         <v>68</v>
@@ -1173,7 +1173,7 @@
         <v>138</v>
       </c>
       <c r="M16" t="n">
-        <v>2.0505</v>
+        <v>1.9988</v>
       </c>
       <c r="N16" t="n">
         <v>206</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.323</v>
+        <v>1.2248</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3642</v>
+        <v>0.3372</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0219</v>
+        <v>-0.0478</v>
       </c>
       <c r="E17" t="n">
-        <v>1.323</v>
+        <v>1.2248</v>
       </c>
       <c r="F17" t="n">
-        <v>0.741</v>
+        <v>0.6778</v>
       </c>
       <c r="G17" t="n">
-        <v>0.582</v>
+        <v>0.547</v>
       </c>
       <c r="H17" t="n">
-        <v>0.741</v>
+        <v>0.6778</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.7145</v>
       </c>
       <c r="J17" t="n">
-        <v>0.582</v>
+        <v>0.547</v>
       </c>
       <c r="K17" t="n">
         <v>44</v>
@@ -1219,7 +1219,7 @@
         <v>108</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3617</v>
+        <v>1.2615</v>
       </c>
       <c r="N17" t="n">
         <v>152</v>
@@ -1228,35 +1228,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JACKZ</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2724</v>
+        <v>1.1581</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3503</v>
+        <v>0.3188</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.045</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2724</v>
+        <v>1.1581</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3787</v>
+        <v>2.2676</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1063</v>
+        <v>-1.1095</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3787</v>
+        <v>2.2676</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4507</v>
+        <v>2.3904</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1063</v>
+        <v>-1.1095</v>
       </c>
       <c r="K18" t="n">
         <v>68</v>
@@ -1265,7 +1265,7 @@
         <v>138</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3444</v>
+        <v>1.2809</v>
       </c>
       <c r="N18" t="n">
         <v>206</v>
@@ -1274,93 +1274,93 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>JACKZ</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1509</v>
+        <v>1.1567</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3169</v>
+        <v>0.3184</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1003</v>
+        <v>-0.0789</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1509</v>
+        <v>1.1567</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4488</v>
+        <v>1.38</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2979</v>
+        <v>-0.2233</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4488</v>
+        <v>1.38</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5244</v>
+        <v>1.4547</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2979</v>
+        <v>-0.2233</v>
       </c>
       <c r="K19" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="L19" t="n">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2265</v>
+        <v>1.2314</v>
       </c>
       <c r="N19" t="n">
-        <v>152</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.1077</v>
+        <v>1.0617</v>
       </c>
       <c r="C20" t="n">
-        <v>0.305</v>
+        <v>0.2923</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.12</v>
+        <v>-0.1221</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1077</v>
+        <v>1.0617</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2599</v>
+        <v>1.4254</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1522</v>
+        <v>-0.3637</v>
       </c>
       <c r="H20" t="n">
-        <v>2.2599</v>
+        <v>1.4254</v>
       </c>
       <c r="I20" t="n">
-        <v>2.3779</v>
+        <v>1.5026</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1522</v>
+        <v>-0.3637</v>
       </c>
       <c r="K20" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="L20" t="n">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2257</v>
+        <v>1.1389</v>
       </c>
       <c r="N20" t="n">
-        <v>206</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21">
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0371</v>
+        <v>0.9971</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2855</v>
+        <v>0.2745</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1521</v>
+        <v>-0.1516</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0371</v>
+        <v>0.9971</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4214</v>
+        <v>1.3877</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3843</v>
+        <v>-0.3906</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4214</v>
+        <v>1.3877</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4956</v>
+        <v>1.4629</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3843</v>
+        <v>-0.3906</v>
       </c>
       <c r="K21" t="n">
         <v>44</v>
@@ -1403,7 +1403,7 @@
         <v>108</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1113</v>
+        <v>1.0723</v>
       </c>
       <c r="N21" t="n">
         <v>152</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8418</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2318</v>
+        <v>0.2224</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.241</v>
+        <v>-0.2377</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8418</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4735</v>
+        <v>1.4254</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6317</v>
+        <v>-0.6173999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4735</v>
+        <v>1.4254</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5504</v>
+        <v>1.5026</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6317</v>
+        <v>-0.6173999999999999</v>
       </c>
       <c r="K22" t="n">
         <v>44</v>
@@ -1449,7 +1449,7 @@
         <v>108</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9187</v>
+        <v>0.8852</v>
       </c>
       <c r="N22" t="n">
         <v>152</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7774</v>
+        <v>0.8036</v>
       </c>
       <c r="C23" t="n">
-        <v>0.214</v>
+        <v>0.2212</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2703</v>
+        <v>-0.2397</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7774</v>
+        <v>0.8036</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4101</v>
+        <v>-0.377</v>
       </c>
       <c r="G23" t="n">
-        <v>1.1875</v>
+        <v>1.1805</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4101</v>
+        <v>-0.377</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.454</v>
+        <v>-0.4189</v>
       </c>
       <c r="J23" t="n">
-        <v>1.1875</v>
+        <v>1.1805</v>
       </c>
       <c r="K23" t="n">
         <v>139</v>
@@ -1495,7 +1495,7 @@
         <v>250</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7335</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="N23" t="n">
         <v>389</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7027</v>
+        <v>0.676</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1935</v>
+        <v>0.1861</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3043</v>
+        <v>-0.2978</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7027</v>
+        <v>0.676</v>
       </c>
       <c r="F24" t="n">
-        <v>0.26</v>
+        <v>0.2018</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4427</v>
+        <v>0.4742</v>
       </c>
       <c r="H24" t="n">
-        <v>0.26</v>
+        <v>0.2018</v>
       </c>
       <c r="I24" t="n">
-        <v>0.26</v>
+        <v>0.2018</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4427</v>
+        <v>0.4742</v>
       </c>
       <c r="K24" t="n">
         <v>121</v>
@@ -1541,7 +1541,7 @@
         <v>138</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7027</v>
+        <v>0.676</v>
       </c>
       <c r="N24" t="n">
         <v>259</v>
@@ -1550,81 +1550,81 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>Bymas</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2626</v>
+        <v>0.2522</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0723</v>
+        <v>0.0694</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5047</v>
+        <v>-0.4909</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2626</v>
+        <v>0.2522</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1373</v>
+        <v>-0.6271</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3999</v>
+        <v>0.8793</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1373</v>
+        <v>-0.6271</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1373</v>
+        <v>-0.6271</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3999</v>
+        <v>0.8793</v>
       </c>
       <c r="K25" t="n">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="L25" t="n">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2625999999999999</v>
+        <v>0.2522</v>
       </c>
       <c r="N25" t="n">
-        <v>121</v>
+        <v>259</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mantuu</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.231</v>
+        <v>0.188</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0636</v>
+        <v>0.0518</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.519</v>
+        <v>-0.5201</v>
       </c>
       <c r="E26" t="n">
-        <v>0.231</v>
+        <v>0.188</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0103</v>
+        <v>-0.1492</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2207</v>
+        <v>0.3372</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0103</v>
+        <v>-0.1492</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0103</v>
+        <v>-0.1492</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2207</v>
+        <v>0.3372</v>
       </c>
       <c r="K26" t="n">
         <v>44</v>
@@ -1633,7 +1633,7 @@
         <v>77</v>
       </c>
       <c r="M26" t="n">
-        <v>0.231</v>
+        <v>0.188</v>
       </c>
       <c r="N26" t="n">
         <v>121</v>
@@ -1642,47 +1642,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bymas</t>
+          <t>mantuu</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1855</v>
+        <v>0.1321</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0511</v>
+        <v>0.0364</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.5456</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1855</v>
+        <v>0.1321</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.6833</v>
+        <v>-0.0342</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8688</v>
+        <v>0.1663</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.6833</v>
+        <v>-0.0342</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.6833</v>
+        <v>-0.0342</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8688</v>
+        <v>0.1663</v>
       </c>
       <c r="K27" t="n">
+        <v>44</v>
+      </c>
+      <c r="L27" t="n">
+        <v>77</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.1321</v>
+      </c>
+      <c r="N27" t="n">
         <v>121</v>
-      </c>
-      <c r="L27" t="n">
-        <v>138</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.1855</v>
-      </c>
-      <c r="N27" t="n">
-        <v>259</v>
       </c>
     </row>
     <row r="28">
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0476</v>
+        <v>-0.1353</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0131</v>
+        <v>-0.0372</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6459</v>
+        <v>-0.6674</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0476</v>
+        <v>-0.1353</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.4304</v>
+        <v>-0.4472</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3828</v>
+        <v>0.3119</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.4304</v>
+        <v>-0.4472</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.4415</v>
+        <v>-0.4592</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3828</v>
+        <v>0.3119</v>
       </c>
       <c r="K28" t="n">
         <v>68</v>
@@ -1725,7 +1725,7 @@
         <v>86</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.05870000000000003</v>
+        <v>-0.1473</v>
       </c>
       <c r="N28" t="n">
         <v>154</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2236</v>
+        <v>-0.1698</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0616</v>
+        <v>-0.0467</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.726</v>
+        <v>-0.6831</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2236</v>
+        <v>-0.1698</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5195</v>
+        <v>0.4945</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.7431</v>
+        <v>-0.6643</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5195</v>
+        <v>0.4945</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5329</v>
+        <v>0.5077</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.7431</v>
+        <v>-0.6643</v>
       </c>
       <c r="K29" t="n">
         <v>75</v>
@@ -1771,7 +1771,7 @@
         <v>193</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2101999999999999</v>
+        <v>-0.1566</v>
       </c>
       <c r="N29" t="n">
         <v>268</v>
@@ -1780,185 +1780,185 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jamppi</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2506</v>
+        <v>-0.2527</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.0696</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7383</v>
+        <v>-0.7209</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2506</v>
+        <v>-0.2527</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1678</v>
+        <v>-0.3121</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0828</v>
+        <v>0.0594</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1678</v>
+        <v>-0.3121</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1721</v>
+        <v>-0.3204</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.0828</v>
+        <v>0.0594</v>
       </c>
       <c r="K30" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="L30" t="n">
-        <v>86</v>
+        <v>193</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2549</v>
+        <v>-0.261</v>
       </c>
       <c r="N30" t="n">
-        <v>154</v>
+        <v>268</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>Jamppi</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.278</v>
+        <v>-0.2916</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0765</v>
+        <v>-0.0803</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7508</v>
+        <v>-0.7386</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.278</v>
+        <v>-0.2916</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3214</v>
+        <v>-0.1982</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0434</v>
+        <v>-0.0934</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3214</v>
+        <v>-0.1982</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3297</v>
+        <v>-0.2035</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0434</v>
+        <v>-0.0934</v>
       </c>
       <c r="K31" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="L31" t="n">
-        <v>193</v>
+        <v>86</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2863</v>
+        <v>-0.2969</v>
       </c>
       <c r="N31" t="n">
-        <v>268</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3309</v>
+        <v>-0.3689</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0911</v>
+        <v>-0.1016</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7748</v>
+        <v>-0.7738</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3309</v>
+        <v>-0.3689</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1915</v>
+        <v>-0.1568</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.1394</v>
+        <v>-0.2121</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1915</v>
+        <v>-0.1568</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1964</v>
+        <v>-0.1568</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.1394</v>
+        <v>-0.2121</v>
       </c>
       <c r="K32" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="L32" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3358</v>
+        <v>-0.3689</v>
       </c>
       <c r="N32" t="n">
-        <v>154</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4062</v>
+        <v>-0.3823</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1118</v>
+        <v>-0.1052</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8091</v>
+        <v>-0.7799</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4062</v>
+        <v>-0.3823</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1787</v>
+        <v>-0.2236</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.2275</v>
+        <v>-0.1587</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.1787</v>
+        <v>-0.2236</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1787</v>
+        <v>-0.2296</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.2275</v>
+        <v>-0.1587</v>
       </c>
       <c r="K33" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="L33" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4062</v>
+        <v>-0.3883</v>
       </c>
       <c r="N33" t="n">
-        <v>121</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34">
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1489</v>
+        <v>-0.1708</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8704</v>
+        <v>-0.8885</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4039</v>
+        <v>0.3016</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.9447</v>
+        <v>-0.9221</v>
       </c>
       <c r="H34" t="n">
-        <v>0.4039</v>
+        <v>0.3016</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4143</v>
+        <v>0.3096</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.9447</v>
+        <v>-0.9221</v>
       </c>
       <c r="K34" t="n">
         <v>68</v>
@@ -2001,7 +2001,7 @@
         <v>86</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.5304</v>
+        <v>-0.6125</v>
       </c>
       <c r="N34" t="n">
         <v>154</v>
@@ -2010,93 +2010,93 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>sergej</t>
+          <t>hampus</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.6423</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1886</v>
+        <v>-0.1768</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.8984</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.6423</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.1151</v>
+        <v>0.4887</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.5699</v>
+        <v>-1.131</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.1151</v>
+        <v>0.4887</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1181</v>
+        <v>0.5152</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.5699</v>
+        <v>-1.131</v>
       </c>
       <c r="K35" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="L35" t="n">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6879999999999999</v>
+        <v>-0.6158</v>
       </c>
       <c r="N35" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>hampus</t>
+          <t>sergej</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7255</v>
+        <v>-0.7262999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1997</v>
+        <v>-0.2</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9545</v>
+        <v>-0.9367</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7255</v>
+        <v>-0.7262999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4759</v>
+        <v>-0.1566</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.2014</v>
+        <v>-0.5697</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4759</v>
+        <v>-0.1566</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5007</v>
+        <v>-0.1608</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.2014</v>
+        <v>-0.5697</v>
       </c>
       <c r="K36" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="L36" t="n">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7007</v>
+        <v>-0.7304999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="37">
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0854</v>
+        <v>-1.0092</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2988</v>
+        <v>-0.2778</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1183</v>
+        <v>-1.0655</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0854</v>
+        <v>-1.0092</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.3591</v>
+        <v>-0.3327</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.6765</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.3591</v>
+        <v>-0.3327</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.3591</v>
+        <v>-0.3327</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.6765</v>
       </c>
       <c r="K37" t="n">
         <v>44</v>
@@ -2139,7 +2139,7 @@
         <v>77</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.0854</v>
+        <v>-1.0092</v>
       </c>
       <c r="N37" t="n">
         <v>121</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1829</v>
+        <v>-1.1802</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3257</v>
+        <v>-0.3249</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1627</v>
+        <v>-1.1434</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1829</v>
+        <v>-1.1802</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.66</v>
+        <v>-0.6496</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.5229</v>
+        <v>-0.5306</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.66</v>
+        <v>-0.6496</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.66</v>
+        <v>-0.6496</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.5229</v>
+        <v>-0.5306</v>
       </c>
       <c r="K38" t="n">
         <v>44</v>
@@ -2185,7 +2185,7 @@
         <v>77</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.1829</v>
+        <v>-1.1802</v>
       </c>
       <c r="N38" t="n">
         <v>121</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3583</v>
+        <v>-1.328</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3739</v>
+        <v>-0.3656</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2425</v>
+        <v>-1.2108</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3583</v>
+        <v>-1.328</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.609</v>
+        <v>-0.5953000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.7493</v>
+        <v>-0.7327</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.609</v>
+        <v>-0.5953000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.6408</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.7493</v>
+        <v>-0.7327</v>
       </c>
       <c r="K39" t="n">
         <v>68</v>
@@ -2231,7 +2231,7 @@
         <v>138</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.3901</v>
+        <v>-1.3602</v>
       </c>
       <c r="N39" t="n">
         <v>206</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.7889</v>
+        <v>-1.6526</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4925</v>
+        <v>-0.455</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4385</v>
+        <v>-1.3586</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.7889</v>
+        <v>-1.6526</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.9599</v>
+        <v>-0.9246</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.829</v>
+        <v>-0.728</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.9599</v>
+        <v>-0.9246</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.9846</v>
+        <v>-0.9493</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.829</v>
+        <v>-0.728</v>
       </c>
       <c r="K40" t="n">
         <v>75</v>
@@ -2277,7 +2277,7 @@
         <v>193</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.8136</v>
+        <v>-1.6773</v>
       </c>
       <c r="N40" t="n">
         <v>268</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.9501</v>
+        <v>-1.8096</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5369</v>
+        <v>-0.4982</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5119</v>
+        <v>-1.4301</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.9501</v>
+        <v>-1.8096</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.2355</v>
+        <v>-1.1485</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.7146</v>
+        <v>-0.6611</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.2355</v>
+        <v>-1.1485</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.3679</v>
+        <v>-1.2763</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.7146</v>
+        <v>-0.6611</v>
       </c>
       <c r="K41" t="n">
         <v>139</v>
@@ -2323,7 +2323,7 @@
         <v>250</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.0825</v>
+        <v>-1.9374</v>
       </c>
       <c r="N41" t="n">
         <v>389</v>
@@ -2429,10 +2429,10 @@
         <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1854</v>
+        <v>0.191</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3372</v>
+        <v>3.438</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.82</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1939</v>
+        <v>-0.1781</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.4902</v>
+        <v>-3.2058</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.49</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4978</v>
+        <v>-0.4957</v>
       </c>
       <c r="J4" t="n">
-        <v>-8.9604</v>
+        <v>-8.922599999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.49</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4978</v>
+        <v>-0.4957</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.9604</v>
+        <v>-8.922599999999999</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.47</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5154</v>
+        <v>-0.5153</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.277200000000001</v>
+        <v>-9.275399999999999</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>2.01</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0606</v>
+        <v>0.9976</v>
       </c>
       <c r="J7" t="n">
-        <v>19.0908</v>
+        <v>17.9568</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.51</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6069</v>
+        <v>0.539</v>
       </c>
       <c r="J8" t="n">
-        <v>10.9242</v>
+        <v>9.702</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.3</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3956</v>
+        <v>0.3393</v>
       </c>
       <c r="J9" t="n">
-        <v>7.1208</v>
+        <v>6.1074</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.29</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3845</v>
+        <v>0.329</v>
       </c>
       <c r="J10" t="n">
-        <v>6.921</v>
+        <v>5.922</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.12</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1771</v>
+        <v>0.1399</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1878</v>
+        <v>2.5182</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.26</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6796</v>
+        <v>0.647</v>
       </c>
       <c r="J12" t="n">
-        <v>23.786</v>
+        <v>22.645</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.17</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4842</v>
+        <v>0.4471</v>
       </c>
       <c r="J13" t="n">
-        <v>16.947</v>
+        <v>15.6485</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.15</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4392</v>
+        <v>0.4023</v>
       </c>
       <c r="J14" t="n">
-        <v>15.372</v>
+        <v>14.0805</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.1</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3175</v>
+        <v>0.2832</v>
       </c>
       <c r="J15" t="n">
-        <v>11.1125</v>
+        <v>9.912000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.09</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2912</v>
+        <v>0.2579</v>
       </c>
       <c r="J16" t="n">
-        <v>10.192</v>
+        <v>9.0265</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.58</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0563</v>
+        <v>1.0377</v>
       </c>
       <c r="J17" t="n">
-        <v>36.9705</v>
+        <v>36.3195</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.89</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1505</v>
+        <v>-0.1323</v>
       </c>
       <c r="J18" t="n">
-        <v>-5.2675</v>
+        <v>-4.6305</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.84</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2033</v>
+        <v>-0.1835</v>
       </c>
       <c r="J19" t="n">
-        <v>-7.1155</v>
+        <v>-6.4225</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.76</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2824</v>
+        <v>-0.2636</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.884</v>
+        <v>-9.226000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.46</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5495</v>
+        <v>-0.5571</v>
       </c>
       <c r="J21" t="n">
-        <v>-19.2325</v>
+        <v>-19.4985</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.67</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4771</v>
+        <v>1.5168</v>
       </c>
       <c r="J22" t="n">
-        <v>41.3588</v>
+        <v>42.4704</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.25</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6663</v>
+        <v>0.6319</v>
       </c>
       <c r="J23" t="n">
-        <v>18.6564</v>
+        <v>17.6932</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.01</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0408</v>
+        <v>0.0301</v>
       </c>
       <c r="J24" t="n">
-        <v>1.1424</v>
+        <v>0.8428</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.85</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4924</v>
+        <v>-0.451</v>
       </c>
       <c r="J25" t="n">
-        <v>-13.7872</v>
+        <v>-12.628</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5877</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>-16.4556</v>
+        <v>-15.3972</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.26</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5278</v>
+        <v>0.4683</v>
       </c>
       <c r="J27" t="n">
-        <v>14.7784</v>
+        <v>13.1124</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.13</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3055</v>
+        <v>0.2548</v>
       </c>
       <c r="J28" t="n">
-        <v>8.554</v>
+        <v>7.1344</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.11</v>
       </c>
       <c r="I29" t="n">
-        <v>0.268</v>
+        <v>0.2204</v>
       </c>
       <c r="J29" t="n">
-        <v>7.504</v>
+        <v>6.1712</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.86</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1929</v>
+        <v>-0.1722</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.4012</v>
+        <v>-4.8216</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.75</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3029</v>
+        <v>-0.2853</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.481199999999999</v>
+        <v>-7.9884</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.24</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4921</v>
+        <v>0.433</v>
       </c>
       <c r="J32" t="n">
-        <v>16.7314</v>
+        <v>14.722</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.03</v>
       </c>
       <c r="I33" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0723</v>
       </c>
       <c r="J33" t="n">
-        <v>3.2878</v>
+        <v>2.4582</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.99</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0275</v>
+        <v>-0.0195</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.9350000000000001</v>
+        <v>-0.663</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.96</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.0603</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.5602</v>
+        <v>-2.0502</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.96</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.0603</v>
       </c>
       <c r="J36" t="n">
-        <v>-2.5602</v>
+        <v>-2.0502</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.36</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9222</v>
+        <v>0.9081</v>
       </c>
       <c r="J37" t="n">
-        <v>31.3548</v>
+        <v>30.8754</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.02</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0959</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>3.2606</v>
+        <v>2.5432</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.01</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0552</v>
+        <v>0.0411</v>
       </c>
       <c r="J39" t="n">
-        <v>1.8768</v>
+        <v>1.3974</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.96</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1744</v>
+        <v>-0.1415</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.9296</v>
+        <v>-4.811</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5709</v>
+        <v>-0.5311</v>
       </c>
       <c r="J41" t="n">
-        <v>-19.4106</v>
+        <v>-18.0574</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.27</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5323</v>
+        <v>0.4727</v>
       </c>
       <c r="J42" t="n">
-        <v>15.969</v>
+        <v>14.181</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.26</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5165</v>
+        <v>0.4571</v>
       </c>
       <c r="J43" t="n">
-        <v>15.495</v>
+        <v>13.713</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.05</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1406</v>
+        <v>0.11</v>
       </c>
       <c r="J44" t="n">
-        <v>4.218</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.95</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.09180000000000001</v>
+        <v>-0.0751</v>
       </c>
       <c r="J45" t="n">
-        <v>-2.754</v>
+        <v>-2.253</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.83</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2285</v>
+        <v>-0.2083</v>
       </c>
       <c r="J46" t="n">
-        <v>-6.855</v>
+        <v>-6.249</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.26</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7053</v>
+        <v>0.672</v>
       </c>
       <c r="J47" t="n">
-        <v>21.159</v>
+        <v>20.16</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.17</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5031</v>
+        <v>0.4618</v>
       </c>
       <c r="J48" t="n">
-        <v>15.093</v>
+        <v>13.854</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.06</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2218</v>
+        <v>0.1881</v>
       </c>
       <c r="J49" t="n">
-        <v>6.654</v>
+        <v>5.643</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.89</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3787</v>
+        <v>-0.3357</v>
       </c>
       <c r="J50" t="n">
-        <v>-11.361</v>
+        <v>-10.071</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.88</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4045</v>
+        <v>-0.3614</v>
       </c>
       <c r="J51" t="n">
-        <v>-12.135</v>
+        <v>-10.842</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.47</v>
       </c>
       <c r="I52" t="n">
-        <v>0.617</v>
+        <v>0.5467</v>
       </c>
       <c r="J52" t="n">
-        <v>16.042</v>
+        <v>14.2142</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.06</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1204</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>3.1304</v>
+        <v>2.3478</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.99</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.0305</v>
+        <v>-0.0218</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.793</v>
+        <v>-0.5668</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1052</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="J55" t="n">
-        <v>-2.7352</v>
+        <v>-2.275</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.92</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.13</v>
+        <v>-0.1108</v>
       </c>
       <c r="J56" t="n">
-        <v>-3.38</v>
+        <v>-2.8808</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5141</v>
+        <v>0.526</v>
       </c>
       <c r="J57" t="n">
-        <v>13.3666</v>
+        <v>13.676</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.32</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4898</v>
+        <v>0.4982</v>
       </c>
       <c r="J58" t="n">
-        <v>12.7348</v>
+        <v>12.9532</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.17</v>
       </c>
       <c r="I59" t="n">
-        <v>0.297</v>
+        <v>0.2847</v>
       </c>
       <c r="J59" t="n">
-        <v>7.722</v>
+        <v>7.4022</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.67</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3761</v>
+        <v>-0.3637</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.778600000000001</v>
+        <v>-9.456200000000001</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4728</v>
+        <v>-0.471</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.2928</v>
+        <v>-12.246</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.22</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5007</v>
+        <v>0.4455</v>
       </c>
       <c r="J62" t="n">
-        <v>11.0154</v>
+        <v>9.801</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.08</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2369</v>
+        <v>0.1923</v>
       </c>
       <c r="J63" t="n">
-        <v>5.2118</v>
+        <v>4.2306</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.79</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2516</v>
+        <v>-0.2322</v>
       </c>
       <c r="J64" t="n">
-        <v>-5.5352</v>
+        <v>-5.1084</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.77</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.271</v>
+        <v>-0.252</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.962</v>
+        <v>-5.544</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.58</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4448</v>
+        <v>-0.4381</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.785600000000001</v>
+        <v>-9.638199999999999</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.7</v>
       </c>
       <c r="I67" t="n">
-        <v>1.3552</v>
+        <v>1.378</v>
       </c>
       <c r="J67" t="n">
-        <v>29.8144</v>
+        <v>30.316</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.37</v>
       </c>
       <c r="I68" t="n">
-        <v>0.8792</v>
+        <v>0.8626</v>
       </c>
       <c r="J68" t="n">
-        <v>19.3424</v>
+        <v>18.9772</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.24</v>
       </c>
       <c r="I69" t="n">
-        <v>0.6231</v>
+        <v>0.5939</v>
       </c>
       <c r="J69" t="n">
-        <v>13.7082</v>
+        <v>13.0658</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.1</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3001</v>
+        <v>0.2684</v>
       </c>
       <c r="J70" t="n">
-        <v>6.6022</v>
+        <v>5.9048</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.9</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3906</v>
+        <v>-0.3512</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.5932</v>
+        <v>-7.7264</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.44</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.7652</v>
       </c>
       <c r="J72" t="n">
-        <v>22.005</v>
+        <v>20.6604</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.09</v>
       </c>
       <c r="I73" t="n">
-        <v>0.2348</v>
+        <v>0.1899</v>
       </c>
       <c r="J73" t="n">
-        <v>6.3396</v>
+        <v>5.1273</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.91</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1344</v>
+        <v>-0.1154</v>
       </c>
       <c r="J74" t="n">
-        <v>-3.6288</v>
+        <v>-3.1158</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.87</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1791</v>
+        <v>-0.1587</v>
       </c>
       <c r="J75" t="n">
-        <v>-4.8357</v>
+        <v>-4.2849</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.63</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4098</v>
+        <v>-0.4004</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.0646</v>
+        <v>-10.8108</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.32</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8237</v>
+        <v>0.7989000000000001</v>
       </c>
       <c r="J77" t="n">
-        <v>22.2399</v>
+        <v>21.5703</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.22</v>
       </c>
       <c r="I78" t="n">
-        <v>0.6101</v>
+        <v>0.5724</v>
       </c>
       <c r="J78" t="n">
-        <v>16.4727</v>
+        <v>15.4548</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.98</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1131</v>
+        <v>-0.0868</v>
       </c>
       <c r="J79" t="n">
-        <v>-3.0537</v>
+        <v>-2.3436</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2456</v>
+        <v>-0.2069</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.6312</v>
+        <v>-5.5863</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2456</v>
+        <v>-0.2069</v>
       </c>
       <c r="J81" t="n">
-        <v>-6.6312</v>
+        <v>-5.5863</v>
       </c>
     </row>
     <row r="82">
@@ -5669,10 +5669,10 @@
         <v>1.3</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7533</v>
+        <v>0.7261</v>
       </c>
       <c r="J83" t="n">
-        <v>20.3391</v>
+        <v>19.6047</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.22</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5877</v>
+        <v>0.5542</v>
       </c>
       <c r="J84" t="n">
-        <v>15.8679</v>
+        <v>14.9634</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.04</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1381</v>
+        <v>0.1145</v>
       </c>
       <c r="J85" t="n">
-        <v>3.7287</v>
+        <v>3.0915</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.99</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.093</v>
+        <v>-0.0721</v>
       </c>
       <c r="J86" t="n">
-        <v>-2.511</v>
+        <v>-1.9467</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.17</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4209</v>
+        <v>0.3678</v>
       </c>
       <c r="J87" t="n">
-        <v>11.3643</v>
+        <v>9.9306</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.95</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0751</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="J88" t="n">
-        <v>-2.0277</v>
+        <v>-1.6956</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.84</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1996</v>
+        <v>-0.1808</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.3892</v>
+        <v>-4.8816</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.72</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3157</v>
+        <v>-0.2985</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.523899999999999</v>
+        <v>-8.0595</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.63</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3979</v>
+        <v>-0.3863</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.7433</v>
+        <v>-10.4301</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.21</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5864</v>
+        <v>0.548</v>
       </c>
       <c r="J92" t="n">
-        <v>17.592</v>
+        <v>16.44</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.17</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4955</v>
+        <v>0.4552</v>
       </c>
       <c r="J93" t="n">
-        <v>14.865</v>
+        <v>13.656</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.13</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4005</v>
+        <v>0.3605</v>
       </c>
       <c r="J94" t="n">
-        <v>12.015</v>
+        <v>10.815</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.05</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1885</v>
+        <v>0.159</v>
       </c>
       <c r="J95" t="n">
-        <v>5.655</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.87</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4367</v>
+        <v>-0.3939</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.101</v>
+        <v>-11.817</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.24</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5104</v>
+        <v>0.452</v>
       </c>
       <c r="J97" t="n">
-        <v>15.312</v>
+        <v>13.56</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.08</v>
       </c>
       <c r="I98" t="n">
-        <v>0.219</v>
+        <v>0.1754</v>
       </c>
       <c r="J98" t="n">
-        <v>6.57</v>
+        <v>5.262</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.88</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1661</v>
+        <v>-0.1462</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.983</v>
+        <v>-4.386</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.86</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1877</v>
+        <v>-0.1673</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.631</v>
+        <v>-5.019</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.76</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2881</v>
+        <v>-0.2694</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.643000000000001</v>
+        <v>-8.082000000000001</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.08</v>
       </c>
       <c r="I102" t="n">
-        <v>0.2574</v>
+        <v>0.2141</v>
       </c>
       <c r="J102" t="n">
-        <v>6.435</v>
+        <v>5.3525</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.2261</v>
+        <v>-0.2081</v>
       </c>
       <c r="J103" t="n">
-        <v>-5.6525</v>
+        <v>-5.2025</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.76</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2739</v>
+        <v>-0.2559</v>
       </c>
       <c r="J104" t="n">
-        <v>-6.8475</v>
+        <v>-6.3975</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.74</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2928</v>
+        <v>-0.2752</v>
       </c>
       <c r="J105" t="n">
-        <v>-7.32</v>
+        <v>-6.88</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.72</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3115</v>
+        <v>-0.2945</v>
       </c>
       <c r="J106" t="n">
-        <v>-7.7875</v>
+        <v>-7.3625</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.63</v>
       </c>
       <c r="I107" t="n">
-        <v>1.1358</v>
+        <v>1.13</v>
       </c>
       <c r="J107" t="n">
-        <v>28.395</v>
+        <v>28.25</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.27</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6276</v>
+        <v>0.616</v>
       </c>
       <c r="J108" t="n">
-        <v>15.69</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.21</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5342</v>
+        <v>0.526</v>
       </c>
       <c r="J109" t="n">
-        <v>13.355</v>
+        <v>13.15</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2653</v>
+        <v>-0.2269</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.6325</v>
+        <v>-5.6725</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.88</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4299</v>
+        <v>-0.3887</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.7475</v>
+        <v>-9.717499999999999</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.15</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3505</v>
+        <v>0.2966</v>
       </c>
       <c r="J112" t="n">
-        <v>10.1645</v>
+        <v>8.6014</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.13</v>
       </c>
       <c r="I113" t="n">
-        <v>0.3137</v>
+        <v>0.2621</v>
       </c>
       <c r="J113" t="n">
-        <v>9.097300000000001</v>
+        <v>7.6009</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.06</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1734</v>
+        <v>0.1354</v>
       </c>
       <c r="J114" t="n">
-        <v>5.0286</v>
+        <v>3.9266</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.83</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2204</v>
+        <v>-0.1999</v>
       </c>
       <c r="J115" t="n">
-        <v>-6.3916</v>
+        <v>-5.7971</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.73</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.318</v>
+        <v>-0.301</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.222</v>
+        <v>-8.728999999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.73</v>
       </c>
       <c r="I117" t="n">
-        <v>1.2775</v>
+        <v>1.2835</v>
       </c>
       <c r="J117" t="n">
-        <v>37.0475</v>
+        <v>37.2215</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.07</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2367</v>
+        <v>0.2058</v>
       </c>
       <c r="J118" t="n">
-        <v>6.8643</v>
+        <v>5.9682</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.02</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0761</v>
+        <v>0.0595</v>
       </c>
       <c r="J119" t="n">
-        <v>2.2069</v>
+        <v>1.7255</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.97</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1629</v>
+        <v>-0.1313</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.7241</v>
+        <v>-3.8077</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.97</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1629</v>
+        <v>-0.1313</v>
       </c>
       <c r="J121" t="n">
-        <v>-4.7241</v>
+        <v>-3.8077</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.1</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3241</v>
+        <v>0.2824</v>
       </c>
       <c r="J122" t="n">
-        <v>6.1579</v>
+        <v>5.3656</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.77</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.2597</v>
+        <v>-0.2434</v>
       </c>
       <c r="J123" t="n">
-        <v>-4.9343</v>
+        <v>-4.6246</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.75</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2777</v>
+        <v>-0.2614</v>
       </c>
       <c r="J124" t="n">
-        <v>-5.2763</v>
+        <v>-4.9666</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.6</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4135</v>
+        <v>-0.4031</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.8565</v>
+        <v>-7.6589</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.59</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4224</v>
+        <v>-0.4128</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.025600000000001</v>
+        <v>-7.8432</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.74</v>
       </c>
       <c r="I127" t="n">
-        <v>1.2342</v>
+        <v>1.2323</v>
       </c>
       <c r="J127" t="n">
-        <v>23.4498</v>
+        <v>23.4137</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.57</v>
       </c>
       <c r="I128" t="n">
-        <v>1.0188</v>
+        <v>1.0082</v>
       </c>
       <c r="J128" t="n">
-        <v>19.3572</v>
+        <v>19.1558</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.37</v>
       </c>
       <c r="I129" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.7438</v>
       </c>
       <c r="J129" t="n">
-        <v>14.3165</v>
+        <v>14.1322</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.29</v>
       </c>
       <c r="I130" t="n">
-        <v>0.6399</v>
+        <v>0.6339</v>
       </c>
       <c r="J130" t="n">
-        <v>12.1581</v>
+        <v>12.0441</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.9</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4079</v>
+        <v>-0.3719</v>
       </c>
       <c r="J131" t="n">
-        <v>-7.7501</v>
+        <v>-7.0661</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.43</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5365</v>
+        <v>0.4988</v>
       </c>
       <c r="J132" t="n">
-        <v>14.4855</v>
+        <v>13.4676</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.21</v>
       </c>
       <c r="I133" t="n">
-        <v>0.321</v>
+        <v>0.2639</v>
       </c>
       <c r="J133" t="n">
-        <v>8.667</v>
+        <v>7.1253</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.03</v>
       </c>
       <c r="I134" t="n">
-        <v>0.0674</v>
+        <v>0.0483</v>
       </c>
       <c r="J134" t="n">
-        <v>1.8198</v>
+        <v>1.3041</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.98</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0495</v>
+        <v>-0.0376</v>
       </c>
       <c r="J135" t="n">
-        <v>-1.3365</v>
+        <v>-1.0152</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2504</v>
+        <v>-0.2309</v>
       </c>
       <c r="J136" t="n">
-        <v>-6.7608</v>
+        <v>-6.2343</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.08</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1752</v>
+        <v>0.1578</v>
       </c>
       <c r="J137" t="n">
-        <v>4.7304</v>
+        <v>4.2606</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.07</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1586</v>
+        <v>0.1412</v>
       </c>
       <c r="J138" t="n">
-        <v>4.2822</v>
+        <v>3.8124</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.01</v>
       </c>
       <c r="I139" t="n">
-        <v>0.0402</v>
+        <v>0.0303</v>
       </c>
       <c r="J139" t="n">
-        <v>1.0854</v>
+        <v>0.8181</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.91</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1307</v>
+        <v>-0.1127</v>
       </c>
       <c r="J140" t="n">
-        <v>-3.5289</v>
+        <v>-3.0429</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.64</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3968</v>
+        <v>-0.3857</v>
       </c>
       <c r="J141" t="n">
-        <v>-10.7136</v>
+        <v>-10.4139</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.03</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1066</v>
+        <v>0.0784</v>
       </c>
       <c r="J142" t="n">
-        <v>3.0914</v>
+        <v>2.2736</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.02</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0795</v>
+        <v>0.0565</v>
       </c>
       <c r="J143" t="n">
-        <v>2.3055</v>
+        <v>1.6385</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.95</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.4099</v>
+        <v>-1.9894</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0958</v>
+        <v>-0.08</v>
       </c>
       <c r="J145" t="n">
-        <v>-2.7782</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.84</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2079</v>
+        <v>-0.1875</v>
       </c>
       <c r="J146" t="n">
-        <v>-6.0291</v>
+        <v>-5.4375</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.5</v>
       </c>
       <c r="I147" t="n">
-        <v>0.984</v>
+        <v>0.9727</v>
       </c>
       <c r="J147" t="n">
-        <v>28.536</v>
+        <v>28.2083</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.14</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4224</v>
+        <v>0.3836</v>
       </c>
       <c r="J148" t="n">
-        <v>12.2496</v>
+        <v>11.1244</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.07</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2458</v>
+        <v>0.2124</v>
       </c>
       <c r="J149" t="n">
-        <v>7.1282</v>
+        <v>6.1596</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.89</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3866</v>
+        <v>-0.3437</v>
       </c>
       <c r="J150" t="n">
-        <v>-11.2114</v>
+        <v>-9.9673</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.86</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4628</v>
+        <v>-0.4204</v>
       </c>
       <c r="J151" t="n">
-        <v>-13.4212</v>
+        <v>-12.1916</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.26</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5179</v>
+        <v>0.4868</v>
       </c>
       <c r="J152" t="n">
-        <v>13.9833</v>
+        <v>13.1436</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.96</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.0568</v>
       </c>
       <c r="J153" t="n">
-        <v>-1.89</v>
+        <v>-1.5336</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.93</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1081</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="J154" t="n">
-        <v>-2.9187</v>
+        <v>-2.4651</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.89</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1544</v>
+        <v>-0.135</v>
       </c>
       <c r="J155" t="n">
-        <v>-4.1688</v>
+        <v>-3.645</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.74</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3063</v>
+        <v>-0.2886</v>
       </c>
       <c r="J156" t="n">
-        <v>-8.270099999999999</v>
+        <v>-7.7922</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.34</v>
       </c>
       <c r="I157" t="n">
-        <v>0.747</v>
+        <v>0.731</v>
       </c>
       <c r="J157" t="n">
-        <v>20.169</v>
+        <v>19.737</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.25</v>
       </c>
       <c r="I158" t="n">
-        <v>0.6083</v>
+        <v>0.5957</v>
       </c>
       <c r="J158" t="n">
-        <v>16.4241</v>
+        <v>16.0839</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.08</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2709</v>
+        <v>0.2368</v>
       </c>
       <c r="J159" t="n">
-        <v>7.3143</v>
+        <v>6.3936</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.04</v>
       </c>
       <c r="I160" t="n">
-        <v>0.1533</v>
+        <v>0.1277</v>
       </c>
       <c r="J160" t="n">
-        <v>4.1391</v>
+        <v>3.4479</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.84</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5152</v>
+        <v>-0.4743</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.9104</v>
+        <v>-12.8061</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.1</v>
       </c>
       <c r="I162" t="n">
-        <v>0.2644</v>
+        <v>0.2165</v>
       </c>
       <c r="J162" t="n">
-        <v>6.61</v>
+        <v>5.4125</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.95</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0825</v>
+        <v>-0.0683</v>
       </c>
       <c r="J163" t="n">
-        <v>-2.0625</v>
+        <v>-1.7075</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0951</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="J164" t="n">
-        <v>-2.3775</v>
+        <v>-1.9925</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.93</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1072</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="J165" t="n">
-        <v>-2.68</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.79</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2569</v>
+        <v>-0.2371</v>
       </c>
       <c r="J166" t="n">
-        <v>-6.4225</v>
+        <v>-5.9275</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.49</v>
       </c>
       <c r="I167" t="n">
-        <v>0.9530999999999999</v>
+        <v>0.9394</v>
       </c>
       <c r="J167" t="n">
-        <v>23.8275</v>
+        <v>23.485</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.16</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4548</v>
+        <v>0.4246</v>
       </c>
       <c r="J168" t="n">
-        <v>11.37</v>
+        <v>10.615</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.08</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2639</v>
+        <v>0.2318</v>
       </c>
       <c r="J169" t="n">
-        <v>6.5975</v>
+        <v>5.795</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.06</v>
       </c>
       <c r="I170" t="n">
-        <v>0.2071</v>
+        <v>0.1781</v>
       </c>
       <c r="J170" t="n">
-        <v>5.1775</v>
+        <v>4.4525</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.99</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.0856</v>
+        <v>-0.0646</v>
       </c>
       <c r="J171" t="n">
-        <v>-2.14</v>
+        <v>-1.615</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.86</v>
       </c>
       <c r="I172" t="n">
-        <v>0.819</v>
+        <v>0.7668</v>
       </c>
       <c r="J172" t="n">
-        <v>17.199</v>
+        <v>16.1028</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.71</v>
       </c>
       <c r="I173" t="n">
-        <v>0.7161</v>
+        <v>0.6695</v>
       </c>
       <c r="J173" t="n">
-        <v>15.0381</v>
+        <v>14.0595</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.08</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1316</v>
+        <v>0.1011</v>
       </c>
       <c r="J174" t="n">
-        <v>2.7636</v>
+        <v>2.1231</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.96</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.0956</v>
+        <v>-0.0806</v>
       </c>
       <c r="J175" t="n">
-        <v>-2.0076</v>
+        <v>-1.6926</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.9</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1706</v>
+        <v>-0.1522</v>
       </c>
       <c r="J176" t="n">
-        <v>-3.5826</v>
+        <v>-3.1962</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.24</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4215</v>
+        <v>0.4268</v>
       </c>
       <c r="J177" t="n">
-        <v>8.8515</v>
+        <v>8.9628</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.99</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.0142</v>
+        <v>-0.0098</v>
       </c>
       <c r="J178" t="n">
-        <v>-0.2982</v>
+        <v>-0.2058</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.83</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2108</v>
+        <v>-0.1915</v>
       </c>
       <c r="J179" t="n">
-        <v>-4.4268</v>
+        <v>-4.0215</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.71</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3265</v>
+        <v>-0.3098</v>
       </c>
       <c r="J180" t="n">
-        <v>-6.8565</v>
+        <v>-6.5058</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.61</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4171</v>
+        <v>-0.4075</v>
       </c>
       <c r="J181" t="n">
-        <v>-8.7591</v>
+        <v>-8.557499999999999</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.98</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.0181</v>
+        <v>-0.0104</v>
       </c>
       <c r="J182" t="n">
-        <v>-0.4344</v>
+        <v>-0.2496</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.87</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1614</v>
+        <v>-0.1455</v>
       </c>
       <c r="J183" t="n">
-        <v>-3.8736</v>
+        <v>-3.492</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.78</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2519</v>
+        <v>-0.2349</v>
       </c>
       <c r="J184" t="n">
-        <v>-6.0456</v>
+        <v>-5.6376</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.7</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.326</v>
+        <v>-0.3101</v>
       </c>
       <c r="J185" t="n">
-        <v>-7.824</v>
+        <v>-7.4424</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.6</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4163</v>
+        <v>-0.4062</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.991199999999999</v>
+        <v>-9.748799999999999</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.57</v>
       </c>
       <c r="I187" t="n">
-        <v>1.036</v>
+        <v>1.0247</v>
       </c>
       <c r="J187" t="n">
-        <v>24.864</v>
+        <v>24.5928</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.56</v>
       </c>
       <c r="I188" t="n">
-        <v>1.0228</v>
+        <v>1.011</v>
       </c>
       <c r="J188" t="n">
-        <v>24.5472</v>
+        <v>24.264</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.14</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3984</v>
+        <v>0.366</v>
       </c>
       <c r="J189" t="n">
-        <v>9.5616</v>
+        <v>8.784000000000001</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.09</v>
       </c>
       <c r="I190" t="n">
-        <v>0.2716</v>
+        <v>0.2406</v>
       </c>
       <c r="J190" t="n">
-        <v>6.5184</v>
+        <v>5.7744</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.01</v>
       </c>
       <c r="I191" t="n">
-        <v>0.0136</v>
+        <v>0.0033</v>
       </c>
       <c r="J191" t="n">
-        <v>0.3264</v>
+        <v>0.07920000000000001</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>0.67</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.3123</v>
+        <v>-0.3015</v>
       </c>
       <c r="J192" t="n">
-        <v>-5.9337</v>
+        <v>-5.7285</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.55</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.4265</v>
+        <v>-0.4233</v>
       </c>
       <c r="J193" t="n">
-        <v>-8.1035</v>
+        <v>-8.0427</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.48</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.485</v>
+        <v>-0.4837</v>
       </c>
       <c r="J194" t="n">
-        <v>-9.215</v>
+        <v>-9.190300000000001</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.45</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.5112</v>
+        <v>-0.5115</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.7128</v>
+        <v>-9.718500000000001</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.45</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5112</v>
+        <v>-0.5115</v>
       </c>
       <c r="J196" t="n">
-        <v>-9.7128</v>
+        <v>-9.718500000000001</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>2.35</v>
       </c>
       <c r="I197" t="n">
-        <v>1.8921</v>
+        <v>1.9505</v>
       </c>
       <c r="J197" t="n">
-        <v>35.9499</v>
+        <v>37.0595</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.63</v>
       </c>
       <c r="I198" t="n">
-        <v>1.0687</v>
+        <v>1.0656</v>
       </c>
       <c r="J198" t="n">
-        <v>20.3053</v>
+        <v>20.2464</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.6</v>
       </c>
       <c r="I199" t="n">
-        <v>1.033</v>
+        <v>1.0293</v>
       </c>
       <c r="J199" t="n">
-        <v>19.627</v>
+        <v>19.5567</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.39</v>
       </c>
       <c r="I200" t="n">
-        <v>0.7609</v>
+        <v>0.7563</v>
       </c>
       <c r="J200" t="n">
-        <v>14.4571</v>
+        <v>14.3697</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.04</v>
       </c>
       <c r="I201" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0471</v>
       </c>
       <c r="J201" t="n">
-        <v>1.4763</v>
+        <v>0.8949</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.52</v>
       </c>
       <c r="I202" t="n">
-        <v>1.116</v>
+        <v>1.1283</v>
       </c>
       <c r="J202" t="n">
-        <v>24.552</v>
+        <v>24.8226</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.45</v>
       </c>
       <c r="I203" t="n">
-        <v>1.0173</v>
+        <v>1.0188</v>
       </c>
       <c r="J203" t="n">
-        <v>22.3806</v>
+        <v>22.4136</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.33</v>
       </c>
       <c r="I204" t="n">
-        <v>0.7993</v>
+        <v>0.7784</v>
       </c>
       <c r="J204" t="n">
-        <v>17.5846</v>
+        <v>17.1248</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.16</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4453</v>
+        <v>0.4132</v>
       </c>
       <c r="J205" t="n">
-        <v>9.7966</v>
+        <v>9.090400000000001</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.93</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3104</v>
+        <v>-0.2726</v>
       </c>
       <c r="J206" t="n">
-        <v>-6.8288</v>
+        <v>-5.9972</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.18</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4421</v>
+        <v>0.3892</v>
       </c>
       <c r="J207" t="n">
-        <v>9.7262</v>
+        <v>8.5624</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.03</v>
       </c>
       <c r="I208" t="n">
-        <v>0.1295</v>
+        <v>0.099</v>
       </c>
       <c r="J208" t="n">
-        <v>2.849</v>
+        <v>2.178</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.87</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1687</v>
+        <v>-0.1511</v>
       </c>
       <c r="J209" t="n">
-        <v>-3.7114</v>
+        <v>-3.3242</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.72</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3149</v>
+        <v>-0.2977</v>
       </c>
       <c r="J210" t="n">
-        <v>-6.9278</v>
+        <v>-6.5494</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.47</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5366</v>
+        <v>-0.5415</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.8052</v>
+        <v>-11.913</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.33</v>
       </c>
       <c r="I212" t="n">
-        <v>0.8111</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="J212" t="n">
-        <v>17.8442</v>
+        <v>17.3316</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.3</v>
       </c>
       <c r="I213" t="n">
-        <v>0.7511</v>
+        <v>0.7242</v>
       </c>
       <c r="J213" t="n">
-        <v>16.5242</v>
+        <v>15.9324</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.17</v>
       </c>
       <c r="I214" t="n">
-        <v>0.4783</v>
+        <v>0.4441</v>
       </c>
       <c r="J214" t="n">
-        <v>10.5226</v>
+        <v>9.770200000000001</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.14</v>
       </c>
       <c r="I215" t="n">
-        <v>0.4084</v>
+        <v>0.3743</v>
       </c>
       <c r="J215" t="n">
-        <v>8.9848</v>
+        <v>8.2346</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.11</v>
       </c>
       <c r="I216" t="n">
-        <v>0.3344</v>
+        <v>0.3013</v>
       </c>
       <c r="J216" t="n">
-        <v>7.3568</v>
+        <v>6.6286</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.99</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.01</v>
+        <v>-0.0057</v>
       </c>
       <c r="J217" t="n">
-        <v>-0.22</v>
+        <v>-0.1254</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.97</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.0442</v>
+        <v>-0.035</v>
       </c>
       <c r="J218" t="n">
-        <v>-0.9724</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.91</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1234</v>
+        <v>-0.1081</v>
       </c>
       <c r="J219" t="n">
-        <v>-2.7148</v>
+        <v>-2.3782</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.77</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2668</v>
+        <v>-0.2482</v>
       </c>
       <c r="J220" t="n">
-        <v>-5.8696</v>
+        <v>-5.4604</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.59</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4318</v>
+        <v>-0.4234</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.499599999999999</v>
+        <v>-9.3148</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.68</v>
       </c>
       <c r="I222" t="n">
-        <v>1.2955</v>
+        <v>1.3157</v>
       </c>
       <c r="J222" t="n">
-        <v>28.501</v>
+        <v>28.9454</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.57</v>
       </c>
       <c r="I223" t="n">
-        <v>1.1571</v>
+        <v>1.1736</v>
       </c>
       <c r="J223" t="n">
-        <v>25.4562</v>
+        <v>25.8192</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.52</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0931</v>
+        <v>1.1084</v>
       </c>
       <c r="J224" t="n">
-        <v>24.0482</v>
+        <v>24.3848</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.5</v>
       </c>
       <c r="I225" t="n">
-        <v>1.067</v>
+        <v>1.0804</v>
       </c>
       <c r="J225" t="n">
-        <v>23.474</v>
+        <v>23.7688</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.93</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3347</v>
+        <v>-0.3017</v>
       </c>
       <c r="J226" t="n">
-        <v>-7.3634</v>
+        <v>-6.6374</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.201</v>
+        <v>-0.1853</v>
       </c>
       <c r="J227" t="n">
-        <v>-4.422</v>
+        <v>-4.0766</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.68</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.3299</v>
+        <v>-0.3185</v>
       </c>
       <c r="J228" t="n">
-        <v>-7.2578</v>
+        <v>-7.007</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.61</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3902</v>
+        <v>-0.3801</v>
       </c>
       <c r="J229" t="n">
-        <v>-8.5844</v>
+        <v>-8.3622</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.58</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4164</v>
+        <v>-0.4075</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.1608</v>
+        <v>-8.965</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.55</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4428</v>
+        <v>-0.4356</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.7416</v>
+        <v>-9.5832</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.07</v>
       </c>
       <c r="I232" t="n">
-        <v>0.2111</v>
+        <v>0.2054</v>
       </c>
       <c r="J232" t="n">
-        <v>5.0664</v>
+        <v>4.9296</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.77</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.2575</v>
+        <v>-0.2421</v>
       </c>
       <c r="J233" t="n">
-        <v>-6.18</v>
+        <v>-5.8104</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.73</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.2939</v>
+        <v>-0.2785</v>
       </c>
       <c r="J234" t="n">
-        <v>-7.0536</v>
+        <v>-6.684</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.57</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.4372</v>
+        <v>-0.4289</v>
       </c>
       <c r="J235" t="n">
-        <v>-10.4928</v>
+        <v>-10.2936</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.55</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4549</v>
+        <v>-0.4483</v>
       </c>
       <c r="J236" t="n">
-        <v>-10.9176</v>
+        <v>-10.7592</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.46</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5675</v>
+        <v>0.4987</v>
       </c>
       <c r="J237" t="n">
-        <v>13.62</v>
+        <v>11.9688</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.46</v>
       </c>
       <c r="I238" t="n">
-        <v>0.5675</v>
+        <v>0.4987</v>
       </c>
       <c r="J238" t="n">
-        <v>13.62</v>
+        <v>11.9688</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.31</v>
       </c>
       <c r="I239" t="n">
-        <v>0.4143</v>
+        <v>0.3547</v>
       </c>
       <c r="J239" t="n">
-        <v>9.943199999999999</v>
+        <v>8.5128</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.29</v>
       </c>
       <c r="I240" t="n">
-        <v>0.3928</v>
+        <v>0.3348</v>
       </c>
       <c r="J240" t="n">
-        <v>9.427199999999999</v>
+        <v>8.0352</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>1.15</v>
       </c>
       <c r="I241" t="n">
-        <v>0.2266</v>
+        <v>0.1841</v>
       </c>
       <c r="J241" t="n">
-        <v>5.4384</v>
+        <v>4.4184</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.65</v>
       </c>
       <c r="I242" t="n">
-        <v>1.2776</v>
+        <v>1.2958</v>
       </c>
       <c r="J242" t="n">
-        <v>28.1072</v>
+        <v>28.5076</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.45</v>
       </c>
       <c r="I243" t="n">
-        <v>1.0097</v>
+        <v>1.0114</v>
       </c>
       <c r="J243" t="n">
-        <v>22.2134</v>
+        <v>22.2508</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.24</v>
       </c>
       <c r="I244" t="n">
-        <v>0.6151</v>
+        <v>0.5884</v>
       </c>
       <c r="J244" t="n">
-        <v>13.5322</v>
+        <v>12.9448</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.23</v>
       </c>
       <c r="I245" t="n">
-        <v>0.594</v>
+        <v>0.5665</v>
       </c>
       <c r="J245" t="n">
-        <v>13.068</v>
+        <v>12.463</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>1.05</v>
       </c>
       <c r="I246" t="n">
-        <v>0.1488</v>
+        <v>0.1225</v>
       </c>
       <c r="J246" t="n">
-        <v>3.2736</v>
+        <v>2.695</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.08</v>
       </c>
       <c r="I247" t="n">
-        <v>0.2632</v>
+        <v>0.2206</v>
       </c>
       <c r="J247" t="n">
-        <v>5.7904</v>
+        <v>4.8532</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.86</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.1747</v>
+        <v>-0.1582</v>
       </c>
       <c r="J248" t="n">
-        <v>-3.8434</v>
+        <v>-3.4804</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2253</v>
+        <v>-0.2077</v>
       </c>
       <c r="J249" t="n">
-        <v>-4.9566</v>
+        <v>-4.5694</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.67</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3557</v>
+        <v>-0.341</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.8254</v>
+        <v>-7.502</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.61</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4097</v>
+        <v>-0.399</v>
       </c>
       <c r="J251" t="n">
-        <v>-9.013400000000001</v>
+        <v>-8.778</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.69</v>
       </c>
       <c r="I252" t="n">
-        <v>1.1762</v>
+        <v>1.1711</v>
       </c>
       <c r="J252" t="n">
-        <v>27.0526</v>
+        <v>26.9353</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.38</v>
       </c>
       <c r="I253" t="n">
-        <v>0.7685999999999999</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="J253" t="n">
-        <v>17.6778</v>
+        <v>17.4248</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.26</v>
       </c>
       <c r="I254" t="n">
-        <v>0.5972</v>
+        <v>0.5924</v>
       </c>
       <c r="J254" t="n">
-        <v>13.7356</v>
+        <v>13.6252</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.25</v>
       </c>
       <c r="I255" t="n">
-        <v>0.5819</v>
+        <v>0.5778</v>
       </c>
       <c r="J255" t="n">
-        <v>13.3837</v>
+        <v>13.2894</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1.17</v>
       </c>
       <c r="I256" t="n">
-        <v>0.4515</v>
+        <v>0.4266</v>
       </c>
       <c r="J256" t="n">
-        <v>10.3845</v>
+        <v>9.8118</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.01</v>
       </c>
       <c r="I257" t="n">
-        <v>0.104</v>
+        <v>0.0867</v>
       </c>
       <c r="J257" t="n">
-        <v>2.392</v>
+        <v>1.9941</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.9</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.1216</v>
+        <v>-0.1066</v>
       </c>
       <c r="J258" t="n">
-        <v>-2.7968</v>
+        <v>-2.4518</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.66</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.3585</v>
+        <v>-0.3446</v>
       </c>
       <c r="J259" t="n">
-        <v>-8.2455</v>
+        <v>-7.9258</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.63</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3855</v>
+        <v>-0.3731</v>
       </c>
       <c r="J260" t="n">
-        <v>-8.8665</v>
+        <v>-8.581300000000001</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4477</v>
+        <v>-0.4405</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.2971</v>
+        <v>-10.1315</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.24</v>
       </c>
       <c r="I262" t="n">
-        <v>0.3971</v>
+        <v>0.3942</v>
       </c>
       <c r="J262" t="n">
-        <v>10.3246</v>
+        <v>10.2492</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.19</v>
       </c>
       <c r="I263" t="n">
-        <v>0.3308</v>
+        <v>0.3212</v>
       </c>
       <c r="J263" t="n">
-        <v>8.6008</v>
+        <v>8.3512</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.87</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.1781</v>
+        <v>-0.1578</v>
       </c>
       <c r="J264" t="n">
-        <v>-4.6306</v>
+        <v>-4.1028</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.86</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.1888</v>
+        <v>-0.1683</v>
       </c>
       <c r="J265" t="n">
-        <v>-4.9088</v>
+        <v>-4.3758</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.72</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.327</v>
+        <v>-0.3106</v>
       </c>
       <c r="J266" t="n">
-        <v>-8.502000000000001</v>
+        <v>-8.0756</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.41</v>
       </c>
       <c r="I267" t="n">
-        <v>0.5205</v>
+        <v>0.4792</v>
       </c>
       <c r="J267" t="n">
-        <v>13.533</v>
+        <v>12.4592</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.08</v>
       </c>
       <c r="I268" t="n">
-        <v>0.1499</v>
+        <v>0.1149</v>
       </c>
       <c r="J268" t="n">
-        <v>3.8974</v>
+        <v>2.9874</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.03</v>
       </c>
       <c r="I269" t="n">
-        <v>0.0674</v>
+        <v>0.0483</v>
       </c>
       <c r="J269" t="n">
-        <v>1.7524</v>
+        <v>1.2558</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.99</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.0318</v>
+        <v>-0.0229</v>
       </c>
       <c r="J270" t="n">
-        <v>-0.8268</v>
+        <v>-0.5954</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.95</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.0934</v>
+        <v>-0.0766</v>
       </c>
       <c r="J271" t="n">
-        <v>-2.4284</v>
+        <v>-1.9916</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.67</v>
       </c>
       <c r="I272" t="n">
-        <v>1.208</v>
+        <v>1.2096</v>
       </c>
       <c r="J272" t="n">
-        <v>33.824</v>
+        <v>33.8688</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.16</v>
       </c>
       <c r="I273" t="n">
-        <v>0.4582</v>
+        <v>0.427</v>
       </c>
       <c r="J273" t="n">
-        <v>12.8296</v>
+        <v>11.956</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.03</v>
       </c>
       <c r="I274" t="n">
-        <v>0.1177</v>
+        <v>0.096</v>
       </c>
       <c r="J274" t="n">
-        <v>3.2956</v>
+        <v>2.688</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.91</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3389</v>
+        <v>-0.297</v>
       </c>
       <c r="J275" t="n">
-        <v>-9.4892</v>
+        <v>-8.316000000000001</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.84</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5175</v>
+        <v>-0.4769</v>
       </c>
       <c r="J276" t="n">
-        <v>-14.49</v>
+        <v>-13.3532</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.13</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3277</v>
+        <v>0.2757</v>
       </c>
       <c r="J277" t="n">
-        <v>9.175599999999999</v>
+        <v>7.7196</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.02</v>
       </c>
       <c r="I278" t="n">
-        <v>0.0857</v>
+        <v>0.0614</v>
       </c>
       <c r="J278" t="n">
-        <v>2.3996</v>
+        <v>1.7192</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.87</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.1733</v>
+        <v>-0.1538</v>
       </c>
       <c r="J279" t="n">
-        <v>-4.8524</v>
+        <v>-4.3064</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.82</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.2251</v>
+        <v>-0.205</v>
       </c>
       <c r="J280" t="n">
-        <v>-6.3028</v>
+        <v>-5.74</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.77</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.2744</v>
+        <v>-0.2553</v>
       </c>
       <c r="J281" t="n">
-        <v>-7.6832</v>
+        <v>-7.1484</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.75</v>
       </c>
       <c r="I282" t="n">
-        <v>1.2667</v>
+        <v>1.2677</v>
       </c>
       <c r="J282" t="n">
-        <v>36.7343</v>
+        <v>36.7633</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.48</v>
       </c>
       <c r="I283" t="n">
-        <v>0.914</v>
+        <v>0.9001</v>
       </c>
       <c r="J283" t="n">
-        <v>26.506</v>
+        <v>26.1029</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.32</v>
       </c>
       <c r="I284" t="n">
-        <v>0.6906</v>
+        <v>0.6796</v>
       </c>
       <c r="J284" t="n">
-        <v>20.0274</v>
+        <v>19.7084</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2817</v>
+        <v>-0.2451</v>
       </c>
       <c r="J285" t="n">
-        <v>-8.1693</v>
+        <v>-7.1079</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.92</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3394</v>
+        <v>-0.301</v>
       </c>
       <c r="J286" t="n">
-        <v>-9.842599999999999</v>
+        <v>-8.728999999999999</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.35</v>
       </c>
       <c r="I287" t="n">
-        <v>0.6556999999999999</v>
+        <v>0.6328</v>
       </c>
       <c r="J287" t="n">
-        <v>19.0153</v>
+        <v>18.3512</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.95</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.0738</v>
+        <v>-0.0617</v>
       </c>
       <c r="J288" t="n">
-        <v>-2.1402</v>
+        <v>-1.7893</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.75</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2865</v>
+        <v>-0.2682</v>
       </c>
       <c r="J289" t="n">
-        <v>-8.3085</v>
+        <v>-7.7778</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.73</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3053</v>
+        <v>-0.2878</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.8537</v>
+        <v>-8.3462</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.48</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5279</v>
+        <v>-0.5315</v>
       </c>
       <c r="J291" t="n">
-        <v>-15.3091</v>
+        <v>-15.4135</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.87</v>
       </c>
       <c r="I292" t="n">
-        <v>1.4246</v>
+        <v>1.4398</v>
       </c>
       <c r="J292" t="n">
-        <v>35.615</v>
+        <v>35.995</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.34</v>
       </c>
       <c r="I293" t="n">
-        <v>0.7226</v>
+        <v>0.7095</v>
       </c>
       <c r="J293" t="n">
-        <v>18.065</v>
+        <v>17.7375</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.33</v>
       </c>
       <c r="I294" t="n">
-        <v>0.7081</v>
+        <v>0.6955</v>
       </c>
       <c r="J294" t="n">
-        <v>17.7025</v>
+        <v>17.3875</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.93</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.3064</v>
+        <v>-0.2681</v>
       </c>
       <c r="J295" t="n">
-        <v>-7.66</v>
+        <v>-6.7025</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.8</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.6341</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="J296" t="n">
-        <v>-15.8525</v>
+        <v>-15.0575</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.02</v>
       </c>
       <c r="I297" t="n">
-        <v>0.1056</v>
+        <v>0.0799</v>
       </c>
       <c r="J297" t="n">
-        <v>2.64</v>
+        <v>1.9975</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.92</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.1107</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="J298" t="n">
-        <v>-2.7675</v>
+        <v>-2.405</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.85</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1883</v>
+        <v>-0.1705</v>
       </c>
       <c r="J299" t="n">
-        <v>-4.7075</v>
+        <v>-4.2625</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.73</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3041</v>
+        <v>-0.2866</v>
       </c>
       <c r="J300" t="n">
-        <v>-7.6025</v>
+        <v>-7.165</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.68</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3503</v>
+        <v>-0.3351</v>
       </c>
       <c r="J301" t="n">
-        <v>-8.7575</v>
+        <v>-8.3775</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.33</v>
       </c>
       <c r="I302" t="n">
-        <v>0.7363</v>
+        <v>0.7204</v>
       </c>
       <c r="J302" t="n">
-        <v>22.089</v>
+        <v>21.612</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.21</v>
       </c>
       <c r="I303" t="n">
-        <v>0.5472</v>
+        <v>0.5364</v>
       </c>
       <c r="J303" t="n">
-        <v>16.416</v>
+        <v>16.092</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.07</v>
       </c>
       <c r="I304" t="n">
-        <v>0.2461</v>
+        <v>0.2125</v>
       </c>
       <c r="J304" t="n">
-        <v>7.383</v>
+        <v>6.375</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.93</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.2768</v>
+        <v>-0.2366</v>
       </c>
       <c r="J305" t="n">
-        <v>-8.304</v>
+        <v>-7.098</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.91</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3328</v>
+        <v>-0.2907</v>
       </c>
       <c r="J306" t="n">
-        <v>-9.984</v>
+        <v>-8.721</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.17</v>
       </c>
       <c r="I307" t="n">
-        <v>0.4055</v>
+        <v>0.3508</v>
       </c>
       <c r="J307" t="n">
-        <v>12.165</v>
+        <v>10.524</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.9</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.1397</v>
+        <v>-0.122</v>
       </c>
       <c r="J308" t="n">
-        <v>-4.191</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.87</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1722</v>
+        <v>-0.153</v>
       </c>
       <c r="J309" t="n">
-        <v>-5.166</v>
+        <v>-4.59</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.86</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1827</v>
+        <v>-0.1633</v>
       </c>
       <c r="J310" t="n">
-        <v>-5.481</v>
+        <v>-4.899</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.74</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3017</v>
+        <v>-0.2837</v>
       </c>
       <c r="J311" t="n">
-        <v>-9.051</v>
+        <v>-8.510999999999999</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.37</v>
       </c>
       <c r="I312" t="n">
-        <v>0.5079</v>
+        <v>0.5353</v>
       </c>
       <c r="J312" t="n">
-        <v>17.7765</v>
+        <v>18.7355</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.37</v>
       </c>
       <c r="I313" t="n">
-        <v>0.5079</v>
+        <v>0.5353</v>
       </c>
       <c r="J313" t="n">
-        <v>17.7765</v>
+        <v>18.7355</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.06</v>
       </c>
       <c r="I314" t="n">
-        <v>0.1253</v>
+        <v>0.1119</v>
       </c>
       <c r="J314" t="n">
-        <v>4.3855</v>
+        <v>3.9165</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.86</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.1992</v>
+        <v>-0.1787</v>
       </c>
       <c r="J315" t="n">
-        <v>-6.972</v>
+        <v>-6.2545</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.82</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.2407</v>
+        <v>-0.2209</v>
       </c>
       <c r="J316" t="n">
-        <v>-8.4245</v>
+        <v>-7.7315</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.16</v>
       </c>
       <c r="I317" t="n">
-        <v>0.2606</v>
+        <v>0.2095</v>
       </c>
       <c r="J317" t="n">
-        <v>9.121</v>
+        <v>7.3325</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.13</v>
       </c>
       <c r="I318" t="n">
-        <v>0.2211</v>
+        <v>0.1748</v>
       </c>
       <c r="J318" t="n">
-        <v>7.7385</v>
+        <v>6.118</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.06</v>
       </c>
       <c r="I319" t="n">
-        <v>0.1207</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="J319" t="n">
-        <v>4.2245</v>
+        <v>3.164</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.04</v>
       </c>
       <c r="I320" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="J320" t="n">
-        <v>3.059</v>
+        <v>2.2295</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.97</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.0636</v>
+        <v>-0.0498</v>
       </c>
       <c r="J321" t="n">
-        <v>-2.226</v>
+        <v>-1.743</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.67</v>
       </c>
       <c r="I322" t="n">
-        <v>1.1434</v>
+        <v>1.1371</v>
       </c>
       <c r="J322" t="n">
-        <v>24.0114</v>
+        <v>23.8791</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.54</v>
       </c>
       <c r="I323" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9665</v>
       </c>
       <c r="J323" t="n">
-        <v>20.5233</v>
+        <v>20.2965</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.34</v>
       </c>
       <c r="I324" t="n">
-        <v>0.7106</v>
+        <v>0.7027</v>
       </c>
       <c r="J324" t="n">
-        <v>14.9226</v>
+        <v>14.7567</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.21</v>
       </c>
       <c r="I325" t="n">
-        <v>0.5141</v>
+        <v>0.5093</v>
       </c>
       <c r="J325" t="n">
-        <v>10.7961</v>
+        <v>10.6953</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>1.2</v>
       </c>
       <c r="I326" t="n">
-        <v>0.4979</v>
+        <v>0.489</v>
       </c>
       <c r="J326" t="n">
-        <v>10.4559</v>
+        <v>10.269</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>0.88</v>
       </c>
       <c r="I327" t="n">
-        <v>-0.1317</v>
+        <v>-0.1152</v>
       </c>
       <c r="J327" t="n">
-        <v>-2.7657</v>
+        <v>-2.4192</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>0.87</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.1434</v>
+        <v>-0.1271</v>
       </c>
       <c r="J328" t="n">
-        <v>-3.0114</v>
+        <v>-2.6691</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.76</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.2603</v>
+        <v>-0.2462</v>
       </c>
       <c r="J329" t="n">
-        <v>-5.4663</v>
+        <v>-5.1702</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.52</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.4746</v>
+        <v>-0.4701</v>
       </c>
       <c r="J330" t="n">
-        <v>-9.9666</v>
+        <v>-9.8721</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.4</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.5794</v>
+        <v>-0.5886</v>
       </c>
       <c r="J331" t="n">
-        <v>-12.1674</v>
+        <v>-12.3606</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>0.99</v>
       </c>
       <c r="I332" t="n">
-        <v>0.0342</v>
+        <v>0.0467</v>
       </c>
       <c r="J332" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.9807</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>0.72</v>
       </c>
       <c r="I333" t="n">
-        <v>-0.3001</v>
+        <v>-0.2862</v>
       </c>
       <c r="J333" t="n">
-        <v>-6.3021</v>
+        <v>-6.0102</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>0.65</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.3616</v>
+        <v>-0.3488</v>
       </c>
       <c r="J334" t="n">
-        <v>-7.5936</v>
+        <v>-7.3248</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.61</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.3972</v>
+        <v>-0.3861</v>
       </c>
       <c r="J335" t="n">
-        <v>-8.341200000000001</v>
+        <v>-8.1081</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.54</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.4591</v>
+        <v>-0.453</v>
       </c>
       <c r="J336" t="n">
-        <v>-9.6411</v>
+        <v>-9.513</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>2.02</v>
       </c>
       <c r="I337" t="n">
-        <v>1.569</v>
+        <v>1.5946</v>
       </c>
       <c r="J337" t="n">
-        <v>32.949</v>
+        <v>33.4866</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.6</v>
       </c>
       <c r="I338" t="n">
-        <v>1.055</v>
+        <v>1.0456</v>
       </c>
       <c r="J338" t="n">
-        <v>22.155</v>
+        <v>21.9576</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.18</v>
       </c>
       <c r="I339" t="n">
-        <v>0.4647</v>
+        <v>0.4441</v>
       </c>
       <c r="J339" t="n">
-        <v>9.758699999999999</v>
+        <v>9.3261</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>1.11</v>
       </c>
       <c r="I340" t="n">
-        <v>0.3057</v>
+        <v>0.2735</v>
       </c>
       <c r="J340" t="n">
-        <v>6.4197</v>
+        <v>5.7435</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>1.04</v>
       </c>
       <c r="I341" t="n">
-        <v>0.1068</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="J341" t="n">
-        <v>2.2428</v>
+        <v>1.7136</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.24</v>
       </c>
       <c r="I342" t="n">
-        <v>0.4704</v>
+        <v>0.4233</v>
       </c>
       <c r="J342" t="n">
-        <v>19.7568</v>
+        <v>17.7786</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.17</v>
       </c>
       <c r="I343" t="n">
-        <v>0.3658</v>
+        <v>0.3124</v>
       </c>
       <c r="J343" t="n">
-        <v>15.3636</v>
+        <v>13.1208</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.14</v>
       </c>
       <c r="I344" t="n">
-        <v>0.3136</v>
+        <v>0.2638</v>
       </c>
       <c r="J344" t="n">
-        <v>13.1712</v>
+        <v>11.0796</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>1.11</v>
       </c>
       <c r="I345" t="n">
-        <v>0.2591</v>
+        <v>0.2143</v>
       </c>
       <c r="J345" t="n">
-        <v>10.8822</v>
+        <v>9.0006</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.77</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.2892</v>
+        <v>-0.2713</v>
       </c>
       <c r="J346" t="n">
-        <v>-12.1464</v>
+        <v>-11.3946</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.54</v>
       </c>
       <c r="I347" t="n">
-        <v>1.0592</v>
+        <v>1.0546</v>
       </c>
       <c r="J347" t="n">
-        <v>44.4864</v>
+        <v>44.2932</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.26</v>
       </c>
       <c r="I348" t="n">
-        <v>0.64</v>
+        <v>0.6257</v>
       </c>
       <c r="J348" t="n">
-        <v>26.88</v>
+        <v>26.2794</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>0.93</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.266</v>
+        <v>-0.2265</v>
       </c>
       <c r="J349" t="n">
-        <v>-11.172</v>
+        <v>-9.513</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.89</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.3751</v>
+        <v>-0.3322</v>
       </c>
       <c r="J350" t="n">
-        <v>-15.7542</v>
+        <v>-13.9524</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.55</v>
       </c>
       <c r="I351" t="n">
-        <v>-1.1241</v>
+        <v>-1.138</v>
       </c>
       <c r="J351" t="n">
-        <v>-47.2122</v>
+        <v>-47.796</v>
       </c>
     </row>
   </sheetData>
